--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124490097</v>
+        <v>124491320</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525147</v>
+        <v>525017</v>
       </c>
       <c r="R2" t="n">
-        <v>6845208</v>
+        <v>6845257</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124498936</v>
+        <v>124491246</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524415</v>
+        <v>525065</v>
       </c>
       <c r="R3" t="n">
-        <v>6845335</v>
+        <v>6845243</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124489748</v>
+        <v>124491765</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525230</v>
+        <v>524904</v>
       </c>
       <c r="R4" t="n">
-        <v>6845187</v>
+        <v>6845207</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124499480</v>
+        <v>124492513</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,50 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524365</v>
+        <v>524774</v>
       </c>
       <c r="R5" t="n">
-        <v>6845400</v>
+        <v>6845100</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124504485</v>
+        <v>124500965</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,47 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524261</v>
+        <v>524308</v>
       </c>
       <c r="R6" t="n">
-        <v>6844909</v>
+        <v>6845471</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1217,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124504973</v>
+        <v>124505389</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1252,7 +1220,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1266,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524210</v>
+        <v>524115</v>
       </c>
       <c r="R7" t="n">
-        <v>6844954</v>
+        <v>6845050</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1328,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124491822</v>
+        <v>124501563</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,37 +1312,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524857</v>
+        <v>524245</v>
       </c>
       <c r="R8" t="n">
-        <v>6845201</v>
+        <v>6845371</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124498529</v>
+        <v>124489748</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,38 +1410,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524365</v>
+        <v>525230</v>
       </c>
       <c r="R9" t="n">
-        <v>6845310</v>
+        <v>6845187</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124489002</v>
+        <v>124487293</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,38 +1521,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525277</v>
+        <v>524948</v>
       </c>
       <c r="R10" t="n">
-        <v>6845196</v>
+        <v>6845179</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1608,11 +1594,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124487293</v>
+        <v>124498544</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,50 +1632,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524948</v>
+        <v>524364</v>
       </c>
       <c r="R11" t="n">
-        <v>6845179</v>
+        <v>6845312</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,22 +1710,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124499475</v>
+        <v>124491917</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,50 +1734,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524510</v>
+        <v>524852</v>
       </c>
       <c r="R12" t="n">
-        <v>6845430</v>
+        <v>6845214</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,22 +1812,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124501719</v>
+        <v>124487317</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,37 +1840,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524232</v>
+        <v>524829</v>
       </c>
       <c r="R13" t="n">
-        <v>6845349</v>
+        <v>6845141</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1951,22 +1914,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124491531</v>
+        <v>124491428</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,41 +1938,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524919</v>
+        <v>524954</v>
       </c>
       <c r="R14" t="n">
-        <v>6845253</v>
+        <v>6845241</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2065,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124487467</v>
+        <v>124491822</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2105,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524805</v>
+        <v>524857</v>
       </c>
       <c r="R15" t="n">
-        <v>6845150</v>
+        <v>6845201</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2155,22 +2127,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124500867</v>
+        <v>124498936</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,13 +2179,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524343</v>
+        <v>524415</v>
       </c>
       <c r="R16" t="n">
-        <v>6845433</v>
+        <v>6845335</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2269,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124492807</v>
+        <v>124490165</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2309,13 +2281,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524696</v>
+        <v>525151</v>
       </c>
       <c r="R17" t="n">
-        <v>6845140</v>
+        <v>6845190</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,22 +2331,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124504945</v>
+        <v>124487283</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2359,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524203</v>
+        <v>524836</v>
       </c>
       <c r="R18" t="n">
-        <v>6844991</v>
+        <v>6845119</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2473,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124504651</v>
+        <v>124500926</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,47 +2457,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524234</v>
+        <v>524345</v>
       </c>
       <c r="R19" t="n">
-        <v>6844921</v>
+        <v>6845461</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124487514</v>
+        <v>124504916</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,41 +2559,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525016</v>
+        <v>524219</v>
       </c>
       <c r="R20" t="n">
-        <v>6845190</v>
+        <v>6844970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2674,19 +2646,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124492000</v>
+        <v>124504662</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2722,17 +2694,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524901</v>
+        <v>524244</v>
       </c>
       <c r="R21" t="n">
-        <v>6845216</v>
+        <v>6844920</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124487283</v>
+        <v>124499480</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,38 +2772,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524836</v>
+        <v>524365</v>
       </c>
       <c r="R22" t="n">
-        <v>6845119</v>
+        <v>6845400</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2864,6 +2845,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,10 +2876,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124492032</v>
+        <v>124491387</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,50 +2888,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524881</v>
+        <v>524949</v>
       </c>
       <c r="R23" t="n">
-        <v>6845143</v>
+        <v>6845252</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2989,22 +2966,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124499895</v>
+        <v>124498794</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3013,47 +2990,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524362</v>
+        <v>524383</v>
       </c>
       <c r="R24" t="n">
-        <v>6845391</v>
+        <v>6845264</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3086,11 +3054,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3117,7 +3080,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124488923</v>
+        <v>124502522</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3153,17 +3116,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525312</v>
+        <v>524234</v>
       </c>
       <c r="R25" t="n">
-        <v>6845166</v>
+        <v>6845053</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3207,22 +3170,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124490978</v>
+        <v>124502783</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,41 +3194,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525086</v>
+        <v>524254</v>
       </c>
       <c r="R26" t="n">
-        <v>6845224</v>
+        <v>6845067</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3309,22 +3281,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124487771</v>
+        <v>124504089</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,38 +3305,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524761</v>
+        <v>524238</v>
       </c>
       <c r="R27" t="n">
-        <v>6845213</v>
+        <v>6844930</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3411,22 +3392,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124490165</v>
+        <v>124504485</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,38 +3416,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525151</v>
+        <v>524261</v>
       </c>
       <c r="R28" t="n">
-        <v>6845190</v>
+        <v>6844909</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3525,7 +3515,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124500794</v>
+        <v>124504513</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3558,20 +3548,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524370</v>
+        <v>524245</v>
       </c>
       <c r="R29" t="n">
-        <v>6845393</v>
+        <v>6844924</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3615,22 +3614,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124503504</v>
+        <v>124500069</v>
       </c>
       <c r="B30" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,38 +3638,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524511</v>
+        <v>524370</v>
       </c>
       <c r="R30" t="n">
-        <v>6845029</v>
+        <v>6845396</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3703,6 +3711,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,10 +3742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124499838</v>
+        <v>124505582</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3741,47 +3754,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524478</v>
+        <v>524121</v>
       </c>
       <c r="R31" t="n">
-        <v>6845426</v>
+        <v>6845117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,22 +3832,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124504054</v>
+        <v>124503027</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3852,47 +3856,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524683</v>
+        <v>524345</v>
       </c>
       <c r="R32" t="n">
-        <v>6844956</v>
+        <v>6845032</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3951,10 +3946,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124491477</v>
+        <v>124503785</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3967,34 +3962,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524920</v>
+        <v>524244</v>
       </c>
       <c r="R33" t="n">
-        <v>6845260</v>
+        <v>6845004</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4041,19 +4036,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124492194</v>
+        <v>124491427</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4093,13 +4088,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524798</v>
+        <v>524946</v>
       </c>
       <c r="R34" t="n">
-        <v>6845206</v>
+        <v>6845286</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4143,19 +4138,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124491548</v>
+        <v>124491805</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4195,10 +4190,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524916</v>
+        <v>524880</v>
       </c>
       <c r="R35" t="n">
-        <v>6845244</v>
+        <v>6845212</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4257,7 +4252,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124488535</v>
+        <v>124490720</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4297,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525311</v>
+        <v>525133</v>
       </c>
       <c r="R36" t="n">
-        <v>6845039</v>
+        <v>6845307</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4359,7 +4354,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124490555</v>
+        <v>124502605</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4395,14 +4390,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525142</v>
+        <v>524259</v>
       </c>
       <c r="R37" t="n">
-        <v>6845241</v>
+        <v>6845061</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4435,11 +4430,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4466,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124492635</v>
+        <v>124486962</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4478,38 +4468,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524790</v>
+        <v>524859</v>
       </c>
       <c r="R38" t="n">
-        <v>6845219</v>
+        <v>6845148</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4542,11 +4541,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4573,7 +4567,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124504860</v>
+        <v>124490091</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4609,14 +4603,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524224</v>
+        <v>525149</v>
       </c>
       <c r="R39" t="n">
-        <v>6844971</v>
+        <v>6845210</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4675,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124505582</v>
+        <v>124492717</v>
       </c>
       <c r="B40" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4691,37 +4685,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524121</v>
+        <v>524757</v>
       </c>
       <c r="R40" t="n">
-        <v>6845117</v>
+        <v>6845190</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4777,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124503388</v>
+        <v>124491294</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4789,47 +4783,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524214</v>
+        <v>525063</v>
       </c>
       <c r="R41" t="n">
-        <v>6844996</v>
+        <v>6845234</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4876,22 +4861,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124504565</v>
+        <v>124498165</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,47 +4885,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524227</v>
+        <v>524349</v>
       </c>
       <c r="R42" t="n">
-        <v>6844932</v>
+        <v>6845225</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4999,10 +4975,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124501577</v>
+        <v>124488326</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5011,47 +4987,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524252</v>
+        <v>524734</v>
       </c>
       <c r="R43" t="n">
-        <v>6845387</v>
+        <v>6845219</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5110,10 +5077,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124502910</v>
+        <v>124499873</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,47 +5089,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524247</v>
+        <v>524451</v>
       </c>
       <c r="R44" t="n">
-        <v>6845069</v>
+        <v>6845435</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5221,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124499832</v>
+        <v>124502991</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,47 +5191,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524327</v>
+        <v>524280</v>
       </c>
       <c r="R45" t="n">
-        <v>6845386</v>
+        <v>6845054</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5320,22 +5269,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124487374</v>
+        <v>124504945</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5348,37 +5297,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524974</v>
+        <v>524203</v>
       </c>
       <c r="R46" t="n">
-        <v>6845191</v>
+        <v>6844991</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5422,22 +5371,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124492513</v>
+        <v>124504054</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5446,41 +5395,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524774</v>
+        <v>524683</v>
       </c>
       <c r="R47" t="n">
-        <v>6845100</v>
+        <v>6844956</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5524,22 +5482,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124487775</v>
+        <v>124503388</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5548,41 +5506,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525079</v>
+        <v>524214</v>
       </c>
       <c r="R48" t="n">
-        <v>6845164</v>
+        <v>6844996</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5638,10 +5605,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124498165</v>
+        <v>124506146</v>
       </c>
       <c r="B49" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5650,38 +5617,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524349</v>
+        <v>524148</v>
       </c>
       <c r="R49" t="n">
-        <v>6845225</v>
+        <v>6845027</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5740,7 +5716,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124501831</v>
+        <v>124487604</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5776,17 +5752,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524268</v>
+        <v>524781</v>
       </c>
       <c r="R50" t="n">
-        <v>6845351</v>
+        <v>6845167</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5830,19 +5806,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124504662</v>
+        <v>124487121</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5878,17 +5854,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524244</v>
+        <v>524844</v>
       </c>
       <c r="R51" t="n">
-        <v>6844920</v>
+        <v>6845169</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5944,10 +5920,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124506146</v>
+        <v>124486832</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5956,47 +5932,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524148</v>
+        <v>524856</v>
       </c>
       <c r="R52" t="n">
-        <v>6845027</v>
+        <v>6845111</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6055,7 +6022,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124502522</v>
+        <v>124488535</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6091,17 +6058,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524234</v>
+        <v>525311</v>
       </c>
       <c r="R53" t="n">
-        <v>6845053</v>
+        <v>6845039</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6145,22 +6112,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124487039</v>
+        <v>124497941</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6169,50 +6136,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524908</v>
+        <v>524344</v>
       </c>
       <c r="R54" t="n">
-        <v>6845155</v>
+        <v>6845182</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6256,22 +6214,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124504545</v>
+        <v>124489866</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6280,50 +6238,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524237</v>
+        <v>525217</v>
       </c>
       <c r="R55" t="n">
-        <v>6844919</v>
+        <v>6845195</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6367,19 +6316,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124487689</v>
+        <v>124490978</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6419,10 +6368,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524780</v>
+        <v>525086</v>
       </c>
       <c r="R56" t="n">
-        <v>6845188</v>
+        <v>6845224</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6481,10 +6430,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124504250</v>
+        <v>124492194</v>
       </c>
       <c r="B57" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6493,38 +6442,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524436</v>
+        <v>524798</v>
       </c>
       <c r="R57" t="n">
-        <v>6844930</v>
+        <v>6845206</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6557,11 +6506,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6588,10 +6532,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124503027</v>
+        <v>124486895</v>
       </c>
       <c r="B58" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6604,34 +6548,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524345</v>
+        <v>524856</v>
       </c>
       <c r="R58" t="n">
-        <v>6845032</v>
+        <v>6845128</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6690,7 +6634,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124500865</v>
+        <v>124487374</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6726,14 +6670,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524350</v>
+        <v>524974</v>
       </c>
       <c r="R59" t="n">
-        <v>6845399</v>
+        <v>6845191</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6792,10 +6736,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124498544</v>
+        <v>124487039</v>
       </c>
       <c r="B60" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,41 +6748,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524364</v>
+        <v>524908</v>
       </c>
       <c r="R60" t="n">
-        <v>6845312</v>
+        <v>6845155</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6882,22 +6835,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124491917</v>
+        <v>124499838</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6906,41 +6859,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524852</v>
+        <v>524478</v>
       </c>
       <c r="R61" t="n">
-        <v>6845214</v>
+        <v>6845426</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6984,19 +6946,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124489983</v>
+        <v>124500909</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7032,17 +6994,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525195</v>
+        <v>524346</v>
       </c>
       <c r="R62" t="n">
-        <v>6845198</v>
+        <v>6845458</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7098,7 +7060,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499873</v>
+        <v>124501516</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7138,10 +7100,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524451</v>
+        <v>524237</v>
       </c>
       <c r="R63" t="n">
-        <v>6845435</v>
+        <v>6845433</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7200,7 +7162,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124492072</v>
+        <v>124504545</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7235,7 +7197,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7245,14 +7207,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524828</v>
+        <v>524237</v>
       </c>
       <c r="R64" t="n">
-        <v>6845147</v>
+        <v>6844919</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7311,7 +7273,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124486962</v>
+        <v>124492072</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7346,7 +7308,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7360,10 +7322,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524859</v>
+        <v>524828</v>
       </c>
       <c r="R65" t="n">
-        <v>6845148</v>
+        <v>6845147</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7422,10 +7384,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124487604</v>
+        <v>124502910</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7434,41 +7396,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524781</v>
+        <v>524247</v>
       </c>
       <c r="R66" t="n">
-        <v>6845167</v>
+        <v>6845069</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7512,22 +7483,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124492717</v>
+        <v>124500201</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7536,38 +7507,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524757</v>
+        <v>524390</v>
       </c>
       <c r="R67" t="n">
-        <v>6845190</v>
+        <v>6845406</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7600,6 +7580,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7626,7 +7611,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124489815</v>
+        <v>124492000</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7666,10 +7651,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525208</v>
+        <v>524901</v>
       </c>
       <c r="R68" t="n">
-        <v>6845169</v>
+        <v>6845216</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7728,7 +7713,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124486832</v>
+        <v>124490428</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7768,10 +7753,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524856</v>
+        <v>525133</v>
       </c>
       <c r="R69" t="n">
-        <v>6845111</v>
+        <v>6845201</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7830,10 +7815,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124493358</v>
+        <v>124486839</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7846,21 +7831,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7870,13 +7855,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524793</v>
+        <v>524872</v>
       </c>
       <c r="R70" t="n">
-        <v>6845243</v>
+        <v>6845107</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7920,22 +7905,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124503785</v>
+        <v>124487514</v>
       </c>
       <c r="B71" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7948,37 +7933,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524244</v>
+        <v>525016</v>
       </c>
       <c r="R71" t="n">
-        <v>6845004</v>
+        <v>6845190</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8034,10 +8019,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124500069</v>
+        <v>124491619</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8046,47 +8031,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524370</v>
+        <v>524906</v>
       </c>
       <c r="R72" t="n">
-        <v>6845396</v>
+        <v>6845220</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8119,11 +8095,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,7 +8121,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124502783</v>
+        <v>124501577</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8185,7 +8156,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8199,13 +8170,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524254</v>
+        <v>524252</v>
       </c>
       <c r="R73" t="n">
-        <v>6845067</v>
+        <v>6845387</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8249,22 +8220,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124501662</v>
+        <v>124503276</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8273,50 +8244,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524272</v>
+        <v>524472</v>
       </c>
       <c r="R74" t="n">
-        <v>6845365</v>
+        <v>6845023</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8360,22 +8322,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124505389</v>
+        <v>124492635</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8384,47 +8346,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524115</v>
+        <v>524790</v>
       </c>
       <c r="R75" t="n">
-        <v>6845050</v>
+        <v>6845219</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8457,6 +8410,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8483,10 +8441,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124504151</v>
+        <v>124493358</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8495,41 +8453,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524256</v>
+        <v>524793</v>
       </c>
       <c r="R76" t="n">
-        <v>6844925</v>
+        <v>6845243</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8573,22 +8531,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124490091</v>
+        <v>124489792</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8597,38 +8555,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525149</v>
+        <v>525215</v>
       </c>
       <c r="R77" t="n">
-        <v>6845210</v>
+        <v>6845178</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8687,7 +8654,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124488103</v>
+        <v>124491477</v>
       </c>
       <c r="B78" t="n">
         <v>78810</v>
@@ -8727,13 +8694,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525146</v>
+        <v>524920</v>
       </c>
       <c r="R78" t="n">
-        <v>6845150</v>
+        <v>6845260</v>
       </c>
       <c r="S78" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8777,19 +8744,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124491619</v>
+        <v>124487467</v>
       </c>
       <c r="B79" t="n">
         <v>78810</v>
@@ -8829,10 +8796,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524906</v>
+        <v>524805</v>
       </c>
       <c r="R79" t="n">
-        <v>6845220</v>
+        <v>6845150</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8891,7 +8858,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124490720</v>
+        <v>124487771</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8931,13 +8898,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525133</v>
+        <v>524761</v>
       </c>
       <c r="R80" t="n">
-        <v>6845307</v>
+        <v>6845213</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8981,22 +8948,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124490692</v>
+        <v>124488103</v>
       </c>
       <c r="B81" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9005,25 +8972,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9033,13 +9000,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525103</v>
+        <v>525146</v>
       </c>
       <c r="R81" t="n">
-        <v>6845194</v>
+        <v>6845150</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9083,22 +9050,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124499713</v>
+        <v>124490097</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9111,37 +9078,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524311</v>
+        <v>525147</v>
       </c>
       <c r="R82" t="n">
-        <v>6845368</v>
+        <v>6845208</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9185,22 +9152,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124490527</v>
+        <v>124504151</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9209,43 +9176,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525139</v>
+        <v>524256</v>
       </c>
       <c r="R83" t="n">
-        <v>6845241</v>
+        <v>6844925</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9278,11 +9240,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9309,10 +9266,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124500926</v>
+        <v>124503504</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9325,21 +9282,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9349,13 +9306,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524345</v>
+        <v>524511</v>
       </c>
       <c r="R84" t="n">
-        <v>6845461</v>
+        <v>6845029</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9411,10 +9368,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124504704</v>
+        <v>124504860</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9423,47 +9380,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524238</v>
+        <v>524224</v>
       </c>
       <c r="R85" t="n">
-        <v>6844943</v>
+        <v>6844971</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9522,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124491246</v>
+        <v>124492807</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9538,21 +9486,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9562,13 +9510,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525065</v>
+        <v>524696</v>
       </c>
       <c r="R86" t="n">
-        <v>6845243</v>
+        <v>6845140</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9612,19 +9560,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124491765</v>
+        <v>124498070</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9660,14 +9608,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524904</v>
+        <v>524353</v>
       </c>
       <c r="R87" t="n">
-        <v>6845207</v>
+        <v>6845201</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9726,7 +9674,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124491387</v>
+        <v>124498760</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9762,14 +9710,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524949</v>
+        <v>524388</v>
       </c>
       <c r="R88" t="n">
-        <v>6845252</v>
+        <v>6845283</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9828,10 +9776,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124488157</v>
+        <v>124490555</v>
       </c>
       <c r="B89" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9844,21 +9792,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9868,13 +9816,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524731</v>
+        <v>525142</v>
       </c>
       <c r="R89" t="n">
-        <v>6845235</v>
+        <v>6845241</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9904,6 +9852,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9918,22 +9871,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124491294</v>
+        <v>124499895</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9942,38 +9895,47 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525063</v>
+        <v>524362</v>
       </c>
       <c r="R90" t="n">
-        <v>6845234</v>
+        <v>6845391</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -10006,6 +9968,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10032,7 +9999,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124486895</v>
+        <v>124491531</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -10072,13 +10039,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524856</v>
+        <v>524919</v>
       </c>
       <c r="R91" t="n">
-        <v>6845128</v>
+        <v>6845253</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10134,7 +10101,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124502475</v>
+        <v>124488657</v>
       </c>
       <c r="B92" t="n">
         <v>78810</v>
@@ -10170,14 +10137,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524197</v>
+        <v>525312</v>
       </c>
       <c r="R92" t="n">
-        <v>6845056</v>
+        <v>6845117</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10236,10 +10203,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124503227</v>
+        <v>124491548</v>
       </c>
       <c r="B93" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10252,37 +10219,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524472</v>
+        <v>524916</v>
       </c>
       <c r="R93" t="n">
-        <v>6845023</v>
+        <v>6845244</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10338,10 +10305,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124497941</v>
+        <v>124499127</v>
       </c>
       <c r="B94" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10354,21 +10321,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10378,13 +10345,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524344</v>
+        <v>524559</v>
       </c>
       <c r="R94" t="n">
-        <v>6845182</v>
+        <v>6845427</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10428,22 +10395,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124489866</v>
+        <v>124493108</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10456,21 +10423,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10480,13 +10447,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525217</v>
+        <v>524776</v>
       </c>
       <c r="R95" t="n">
-        <v>6845195</v>
+        <v>6845248</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10516,6 +10483,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10530,19 +10502,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124487564</v>
+        <v>124501831</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10578,17 +10550,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524773</v>
+        <v>524268</v>
       </c>
       <c r="R96" t="n">
-        <v>6845141</v>
+        <v>6845351</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10632,19 +10604,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124490965</v>
+        <v>124502475</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10680,14 +10652,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525081</v>
+        <v>524197</v>
       </c>
       <c r="R97" t="n">
-        <v>6845283</v>
+        <v>6845056</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10746,7 +10718,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124491428</v>
+        <v>124504973</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10781,7 +10753,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10791,14 +10763,14 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524954</v>
+        <v>524210</v>
       </c>
       <c r="R98" t="n">
-        <v>6845241</v>
+        <v>6844954</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10857,7 +10829,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124504354</v>
+        <v>124504651</v>
       </c>
       <c r="B99" t="n">
         <v>98101</v>
@@ -10892,7 +10864,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10906,13 +10878,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524274</v>
+        <v>524234</v>
       </c>
       <c r="R99" t="n">
-        <v>6844889</v>
+        <v>6844921</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10956,22 +10928,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124498070</v>
+        <v>124504704</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10980,38 +10952,47 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524353</v>
+        <v>524238</v>
       </c>
       <c r="R100" t="n">
-        <v>6845201</v>
+        <v>6844943</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -11070,10 +11051,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124487317</v>
+        <v>124499475</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11082,41 +11063,50 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524829</v>
+        <v>524510</v>
       </c>
       <c r="R101" t="n">
-        <v>6845141</v>
+        <v>6845430</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11160,22 +11150,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124488326</v>
+        <v>124503002</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11188,34 +11178,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524734</v>
+        <v>524333</v>
       </c>
       <c r="R102" t="n">
-        <v>6845219</v>
+        <v>6845022</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11274,10 +11264,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124502991</v>
+        <v>124501719</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11290,21 +11280,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11314,13 +11304,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524280</v>
+        <v>524232</v>
       </c>
       <c r="R103" t="n">
-        <v>6845054</v>
+        <v>6845349</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11376,10 +11366,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124500112</v>
+        <v>124503680</v>
       </c>
       <c r="B104" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11392,21 +11382,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11416,13 +11406,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524447</v>
+        <v>524648</v>
       </c>
       <c r="R104" t="n">
-        <v>6845417</v>
+        <v>6845029</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11466,22 +11456,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124493648</v>
+        <v>124504250</v>
       </c>
       <c r="B105" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11494,46 +11484,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524762</v>
+        <v>524436</v>
       </c>
       <c r="R105" t="n">
-        <v>6845231</v>
+        <v>6844930</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11563,6 +11544,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11577,22 +11563,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124503276</v>
+        <v>124499713</v>
       </c>
       <c r="B106" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11605,21 +11591,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11629,13 +11615,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524472</v>
+        <v>524311</v>
       </c>
       <c r="R106" t="n">
-        <v>6845023</v>
+        <v>6845368</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11691,10 +11677,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124501039</v>
+        <v>124489815</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11703,50 +11689,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524281</v>
+        <v>525208</v>
       </c>
       <c r="R107" t="n">
-        <v>6845383</v>
+        <v>6845169</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11790,19 +11767,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124491805</v>
+        <v>124491300</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11842,13 +11819,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524880</v>
+        <v>525015</v>
       </c>
       <c r="R108" t="n">
-        <v>6845212</v>
+        <v>6845263</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11892,19 +11869,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124502605</v>
+        <v>124498466</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -11944,13 +11921,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524259</v>
+        <v>524369</v>
       </c>
       <c r="R109" t="n">
-        <v>6845061</v>
+        <v>6845293</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11994,22 +11971,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124491320</v>
+        <v>124499832</v>
       </c>
       <c r="B110" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12018,38 +11995,47 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>525017</v>
+        <v>524327</v>
       </c>
       <c r="R110" t="n">
-        <v>6845257</v>
+        <v>6845386</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -12096,22 +12082,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124501563</v>
+        <v>124504769</v>
       </c>
       <c r="B111" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12120,41 +12106,50 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524245</v>
+        <v>524231</v>
       </c>
       <c r="R111" t="n">
-        <v>6845371</v>
+        <v>6844957</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12198,19 +12193,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124500201</v>
+        <v>124504565</v>
       </c>
       <c r="B112" t="n">
         <v>98101</v>
@@ -12245,7 +12240,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -12259,10 +12254,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524390</v>
+        <v>524227</v>
       </c>
       <c r="R112" t="n">
-        <v>6845406</v>
+        <v>6844932</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12295,11 +12290,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12326,7 +12316,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124489792</v>
+        <v>124500794</v>
       </c>
       <c r="B113" t="n">
         <v>98101</v>
@@ -12359,29 +12349,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>525215</v>
+        <v>524370</v>
       </c>
       <c r="R113" t="n">
-        <v>6845178</v>
+        <v>6845393</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12425,22 +12406,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124490428</v>
+        <v>124493648</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12449,41 +12430,50 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>525133</v>
+        <v>524762</v>
       </c>
       <c r="R114" t="n">
-        <v>6845201</v>
+        <v>6845231</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12527,22 +12517,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124488657</v>
+        <v>124489670</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12551,38 +12541,47 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>525312</v>
+        <v>525247</v>
       </c>
       <c r="R115" t="n">
-        <v>6845117</v>
+        <v>6845194</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12641,10 +12640,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124499127</v>
+        <v>124492032</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12653,38 +12652,47 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524559</v>
+        <v>524881</v>
       </c>
       <c r="R116" t="n">
-        <v>6845427</v>
+        <v>6845143</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12743,10 +12751,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124501516</v>
+        <v>124490527</v>
       </c>
       <c r="B117" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12759,34 +12767,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524237</v>
+        <v>525139</v>
       </c>
       <c r="R117" t="n">
-        <v>6845433</v>
+        <v>6845241</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12819,6 +12832,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12845,7 +12863,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124504769</v>
+        <v>124501662</v>
       </c>
       <c r="B118" t="n">
         <v>98101</v>
@@ -12880,7 +12898,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -12894,10 +12912,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524231</v>
+        <v>524272</v>
       </c>
       <c r="R118" t="n">
-        <v>6844957</v>
+        <v>6845365</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12944,22 +12962,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124504513</v>
+        <v>124500112</v>
       </c>
       <c r="B119" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12968,50 +12986,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524245</v>
+        <v>524447</v>
       </c>
       <c r="R119" t="n">
-        <v>6844924</v>
+        <v>6845417</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13055,19 +13064,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124504916</v>
+        <v>124501039</v>
       </c>
       <c r="B120" t="n">
         <v>98101</v>
@@ -13116,13 +13125,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524219</v>
+        <v>524281</v>
       </c>
       <c r="R120" t="n">
-        <v>6844970</v>
+        <v>6845383</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13166,22 +13175,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124487567</v>
+        <v>124498529</v>
       </c>
       <c r="B121" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13194,37 +13203,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>525000</v>
+        <v>524365</v>
       </c>
       <c r="R121" t="n">
-        <v>6845201</v>
+        <v>6845310</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13268,22 +13277,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124498794</v>
+        <v>124487564</v>
       </c>
       <c r="B122" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13292,38 +13301,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524383</v>
+        <v>524773</v>
       </c>
       <c r="R122" t="n">
-        <v>6845264</v>
+        <v>6845141</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13382,10 +13391,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124493108</v>
+        <v>124487775</v>
       </c>
       <c r="B123" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13398,21 +13407,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13422,13 +13431,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524776</v>
+        <v>525079</v>
       </c>
       <c r="R123" t="n">
-        <v>6845248</v>
+        <v>6845164</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13458,11 +13467,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13477,19 +13481,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124503680</v>
+        <v>124490965</v>
       </c>
       <c r="B124" t="n">
         <v>78810</v>
@@ -13525,17 +13529,17 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524648</v>
+        <v>525081</v>
       </c>
       <c r="R124" t="n">
-        <v>6845029</v>
+        <v>6845283</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13579,22 +13583,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124504321</v>
+        <v>124488157</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13607,37 +13611,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524276</v>
+        <v>524731</v>
       </c>
       <c r="R125" t="n">
-        <v>6844888</v>
+        <v>6845235</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13681,22 +13685,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124489670</v>
+        <v>124489983</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13705,50 +13709,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>525247</v>
+        <v>525195</v>
       </c>
       <c r="R126" t="n">
-        <v>6845194</v>
+        <v>6845198</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13792,22 +13787,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124504089</v>
+        <v>124490692</v>
       </c>
       <c r="B127" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13816,47 +13811,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524238</v>
+        <v>525103</v>
       </c>
       <c r="R127" t="n">
-        <v>6844930</v>
+        <v>6845194</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13903,19 +13889,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124486839</v>
+        <v>124504321</v>
       </c>
       <c r="B128" t="n">
         <v>78810</v>
@@ -13951,14 +13937,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524872</v>
+        <v>524276</v>
       </c>
       <c r="R128" t="n">
-        <v>6845107</v>
+        <v>6844888</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14017,10 +14003,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124491427</v>
+        <v>124503227</v>
       </c>
       <c r="B129" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14033,37 +14019,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524946</v>
+        <v>524472</v>
       </c>
       <c r="R129" t="n">
-        <v>6845286</v>
+        <v>6845023</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14107,19 +14093,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124498760</v>
+        <v>124500865</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14159,13 +14145,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524388</v>
+        <v>524350</v>
       </c>
       <c r="R130" t="n">
-        <v>6845283</v>
+        <v>6845399</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14209,19 +14195,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124487121</v>
+        <v>124500867</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14257,17 +14243,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524844</v>
+        <v>524343</v>
       </c>
       <c r="R131" t="n">
-        <v>6845169</v>
+        <v>6845433</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14323,10 +14309,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124491300</v>
+        <v>124504354</v>
       </c>
       <c r="B132" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14335,41 +14321,50 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>525015</v>
+        <v>524274</v>
       </c>
       <c r="R132" t="n">
-        <v>6845263</v>
+        <v>6844889</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14425,7 +14420,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124498466</v>
+        <v>124488923</v>
       </c>
       <c r="B133" t="n">
         <v>78810</v>
@@ -14461,17 +14456,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524369</v>
+        <v>525312</v>
       </c>
       <c r="R133" t="n">
-        <v>6845293</v>
+        <v>6845166</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14515,19 +14510,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124500965</v>
+        <v>124487689</v>
       </c>
       <c r="B134" t="n">
         <v>78810</v>
@@ -14563,14 +14558,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524308</v>
+        <v>524780</v>
       </c>
       <c r="R134" t="n">
-        <v>6845471</v>
+        <v>6845188</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14629,7 +14624,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124500909</v>
+        <v>124489002</v>
       </c>
       <c r="B135" t="n">
         <v>78810</v>
@@ -14665,17 +14660,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524346</v>
+        <v>525277</v>
       </c>
       <c r="R135" t="n">
-        <v>6845458</v>
+        <v>6845196</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14705,6 +14700,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14719,22 +14719,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124503002</v>
+        <v>124487567</v>
       </c>
       <c r="B136" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14747,37 +14747,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524333</v>
+        <v>525000</v>
       </c>
       <c r="R136" t="n">
-        <v>6845022</v>
+        <v>6845201</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14821,12 +14821,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124491320</v>
+        <v>124490097</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525017</v>
+        <v>525147</v>
       </c>
       <c r="R2" t="n">
-        <v>6845257</v>
+        <v>6845208</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124491246</v>
+        <v>124488657</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525065</v>
+        <v>525312</v>
       </c>
       <c r="R3" t="n">
-        <v>6845243</v>
+        <v>6845117</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124491765</v>
+        <v>124492000</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524904</v>
+        <v>524901</v>
       </c>
       <c r="R4" t="n">
-        <v>6845207</v>
+        <v>6845216</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124492513</v>
+        <v>124499127</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524774</v>
+        <v>524559</v>
       </c>
       <c r="R5" t="n">
-        <v>6845100</v>
+        <v>6845427</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124500965</v>
+        <v>124499873</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524308</v>
+        <v>524451</v>
       </c>
       <c r="R6" t="n">
-        <v>6845471</v>
+        <v>6845435</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124505389</v>
+        <v>124501039</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524115</v>
+        <v>524281</v>
       </c>
       <c r="R7" t="n">
-        <v>6845050</v>
+        <v>6845383</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1284,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124501563</v>
+        <v>124504485</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,41 +1308,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524245</v>
+        <v>524261</v>
       </c>
       <c r="R8" t="n">
-        <v>6845371</v>
+        <v>6844909</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124489748</v>
+        <v>124502991</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,47 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525230</v>
+        <v>524280</v>
       </c>
       <c r="R9" t="n">
-        <v>6845187</v>
+        <v>6845054</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1497,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124487293</v>
+        <v>124500965</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,50 +1521,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524948</v>
+        <v>524308</v>
       </c>
       <c r="R10" t="n">
-        <v>6845179</v>
+        <v>6845471</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,22 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124498544</v>
+        <v>124488923</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,37 +1627,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524364</v>
+        <v>525312</v>
       </c>
       <c r="R11" t="n">
-        <v>6845312</v>
+        <v>6845166</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,19 +1701,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124491917</v>
+        <v>124489866</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1762,13 +1753,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524852</v>
+        <v>525217</v>
       </c>
       <c r="R12" t="n">
-        <v>6845214</v>
+        <v>6845195</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,19 +1803,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124487317</v>
+        <v>124498529</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1860,14 +1851,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524829</v>
+        <v>524365</v>
       </c>
       <c r="R13" t="n">
-        <v>6845141</v>
+        <v>6845310</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1926,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124491428</v>
+        <v>124492194</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,47 +1929,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524954</v>
+        <v>524798</v>
       </c>
       <c r="R14" t="n">
-        <v>6845241</v>
+        <v>6845206</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2037,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124491822</v>
+        <v>124504973</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,38 +2031,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524857</v>
+        <v>524210</v>
       </c>
       <c r="R15" t="n">
-        <v>6845201</v>
+        <v>6844954</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2127,22 +2118,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124498936</v>
+        <v>124492513</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,37 +2146,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524415</v>
+        <v>524774</v>
       </c>
       <c r="R16" t="n">
-        <v>6845335</v>
+        <v>6845100</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2229,19 +2220,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124490165</v>
+        <v>124487467</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2281,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525151</v>
+        <v>524805</v>
       </c>
       <c r="R17" t="n">
-        <v>6845190</v>
+        <v>6845150</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2343,10 +2334,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124487283</v>
+        <v>124498544</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,34 +2350,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524836</v>
+        <v>524364</v>
       </c>
       <c r="R18" t="n">
-        <v>6845119</v>
+        <v>6845312</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2445,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124500926</v>
+        <v>124502783</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,41 +2448,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524345</v>
+        <v>524254</v>
       </c>
       <c r="R19" t="n">
-        <v>6845461</v>
+        <v>6845067</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2535,22 +2535,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124504916</v>
+        <v>124487567</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2559,50 +2559,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524219</v>
+        <v>525000</v>
       </c>
       <c r="R20" t="n">
-        <v>6844970</v>
+        <v>6845201</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2646,22 +2637,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124504662</v>
+        <v>124487293</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,41 +2661,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524244</v>
+        <v>524948</v>
       </c>
       <c r="R21" t="n">
-        <v>6844920</v>
+        <v>6845179</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,19 +2748,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124499480</v>
+        <v>124492032</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524365</v>
+        <v>524881</v>
       </c>
       <c r="R22" t="n">
-        <v>6845400</v>
+        <v>6845143</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2845,11 +2845,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,22 +2859,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124491387</v>
+        <v>124493108</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2892,21 +2887,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2916,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524949</v>
+        <v>524776</v>
       </c>
       <c r="R23" t="n">
-        <v>6845252</v>
+        <v>6845248</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2952,6 +2947,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2978,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124498794</v>
+        <v>124501563</v>
       </c>
       <c r="B24" t="n">
-        <v>92293</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2990,25 +2990,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524383</v>
+        <v>524245</v>
       </c>
       <c r="R24" t="n">
-        <v>6845264</v>
+        <v>6845371</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3068,22 +3068,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124502522</v>
+        <v>124499480</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3092,38 +3092,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524234</v>
+        <v>524365</v>
       </c>
       <c r="R25" t="n">
-        <v>6845053</v>
+        <v>6845400</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3156,6 +3165,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3182,7 +3196,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124502783</v>
+        <v>124499832</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3217,7 +3231,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3231,13 +3245,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524254</v>
+        <v>524327</v>
       </c>
       <c r="R26" t="n">
-        <v>6845067</v>
+        <v>6845386</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3281,22 +3295,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124504089</v>
+        <v>124491917</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3305,47 +3319,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524238</v>
+        <v>524852</v>
       </c>
       <c r="R27" t="n">
-        <v>6844930</v>
+        <v>6845214</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3392,22 +3397,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124504485</v>
+        <v>124498760</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3416,47 +3421,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524261</v>
+        <v>524388</v>
       </c>
       <c r="R28" t="n">
-        <v>6844909</v>
+        <v>6845283</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3515,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124504513</v>
+        <v>124487374</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,50 +3523,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524245</v>
+        <v>524974</v>
       </c>
       <c r="R29" t="n">
-        <v>6844924</v>
+        <v>6845191</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,19 +3601,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124500069</v>
+        <v>124504354</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3661,7 +3648,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3675,13 +3662,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524370</v>
+        <v>524274</v>
       </c>
       <c r="R30" t="n">
-        <v>6845396</v>
+        <v>6844889</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,11 +3698,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,22 +3712,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124505582</v>
+        <v>124500794</v>
       </c>
       <c r="B31" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,25 +3736,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3782,13 +3764,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524121</v>
+        <v>524370</v>
       </c>
       <c r="R31" t="n">
-        <v>6845117</v>
+        <v>6845393</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3832,22 +3814,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124503027</v>
+        <v>124504151</v>
       </c>
       <c r="B32" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,25 +3838,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3884,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524345</v>
+        <v>524256</v>
       </c>
       <c r="R32" t="n">
-        <v>6845032</v>
+        <v>6844925</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3934,22 +3916,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124503785</v>
+        <v>124504916</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,38 +3940,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524244</v>
+        <v>524219</v>
       </c>
       <c r="R33" t="n">
-        <v>6845004</v>
+        <v>6844970</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4036,19 +4027,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124491427</v>
+        <v>124491805</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4088,13 +4079,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524946</v>
+        <v>524880</v>
       </c>
       <c r="R34" t="n">
-        <v>6845286</v>
+        <v>6845212</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4138,22 +4129,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124491805</v>
+        <v>124498794</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4162,38 +4153,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524880</v>
+        <v>524383</v>
       </c>
       <c r="R35" t="n">
-        <v>6845212</v>
+        <v>6845264</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4252,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124490720</v>
+        <v>124503027</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4268,37 +4259,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525133</v>
+        <v>524345</v>
       </c>
       <c r="R36" t="n">
-        <v>6845307</v>
+        <v>6845032</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4342,22 +4333,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124502605</v>
+        <v>124499895</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,41 +4357,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524259</v>
+        <v>524362</v>
       </c>
       <c r="R37" t="n">
-        <v>6845061</v>
+        <v>6845391</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4430,6 +4430,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4444,19 +4449,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124486962</v>
+        <v>124504545</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4491,7 +4496,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4501,14 +4506,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524859</v>
+        <v>524237</v>
       </c>
       <c r="R38" t="n">
-        <v>6845148</v>
+        <v>6844919</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4567,7 +4572,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124490091</v>
+        <v>124487775</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4607,13 +4612,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525149</v>
+        <v>525079</v>
       </c>
       <c r="R39" t="n">
-        <v>6845210</v>
+        <v>6845164</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4657,22 +4662,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124492717</v>
+        <v>124503002</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4685,34 +4690,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524757</v>
+        <v>524333</v>
       </c>
       <c r="R40" t="n">
-        <v>6845190</v>
+        <v>6845022</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4771,10 +4776,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124491294</v>
+        <v>124501662</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,38 +4788,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525063</v>
+        <v>524272</v>
       </c>
       <c r="R41" t="n">
-        <v>6845234</v>
+        <v>6845365</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4861,22 +4875,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124498165</v>
+        <v>124504513</v>
       </c>
       <c r="B42" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4885,38 +4899,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524349</v>
+        <v>524245</v>
       </c>
       <c r="R42" t="n">
-        <v>6845225</v>
+        <v>6844924</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4975,7 +4998,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124488326</v>
+        <v>124490978</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5015,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524734</v>
+        <v>525086</v>
       </c>
       <c r="R43" t="n">
-        <v>6845219</v>
+        <v>6845224</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5077,7 +5100,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124499873</v>
+        <v>124491300</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5113,17 +5136,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524451</v>
+        <v>525015</v>
       </c>
       <c r="R44" t="n">
-        <v>6845435</v>
+        <v>6845263</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5179,10 +5202,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124502991</v>
+        <v>124490527</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5195,37 +5218,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524280</v>
+        <v>525139</v>
       </c>
       <c r="R45" t="n">
-        <v>6845054</v>
+        <v>6845241</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5255,6 +5283,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5281,7 +5314,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124504945</v>
+        <v>124503785</v>
       </c>
       <c r="B46" t="n">
         <v>57666</v>
@@ -5321,10 +5354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524203</v>
+        <v>524244</v>
       </c>
       <c r="R46" t="n">
-        <v>6844991</v>
+        <v>6845004</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5371,22 +5404,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124504054</v>
+        <v>124504662</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5395,50 +5428,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524683</v>
+        <v>524244</v>
       </c>
       <c r="R47" t="n">
-        <v>6844956</v>
+        <v>6844920</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5494,10 +5518,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124503388</v>
+        <v>124500926</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5506,50 +5530,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524214</v>
+        <v>524345</v>
       </c>
       <c r="R48" t="n">
-        <v>6844996</v>
+        <v>6845461</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5593,22 +5608,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124506146</v>
+        <v>124491246</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5617,47 +5632,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524148</v>
+        <v>525065</v>
       </c>
       <c r="R49" t="n">
-        <v>6845027</v>
+        <v>6845243</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5716,7 +5722,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124487604</v>
+        <v>124491548</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5756,10 +5762,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524781</v>
+        <v>524916</v>
       </c>
       <c r="R50" t="n">
-        <v>6845167</v>
+        <v>6845244</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5818,7 +5824,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124487121</v>
+        <v>124489002</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5858,13 +5864,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524844</v>
+        <v>525277</v>
       </c>
       <c r="R51" t="n">
-        <v>6845169</v>
+        <v>6845196</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5894,6 +5900,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5908,22 +5919,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124486832</v>
+        <v>124502910</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5932,41 +5943,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524856</v>
+        <v>524247</v>
       </c>
       <c r="R52" t="n">
-        <v>6845111</v>
+        <v>6845069</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6010,22 +6030,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124488535</v>
+        <v>124503504</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6038,37 +6058,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525311</v>
+        <v>524511</v>
       </c>
       <c r="R53" t="n">
-        <v>6845039</v>
+        <v>6845029</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6112,22 +6132,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124497941</v>
+        <v>124491428</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6136,41 +6156,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524344</v>
+        <v>524954</v>
       </c>
       <c r="R54" t="n">
-        <v>6845182</v>
+        <v>6845241</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6226,10 +6255,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124489866</v>
+        <v>124498165</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6242,37 +6271,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525217</v>
+        <v>524349</v>
       </c>
       <c r="R55" t="n">
-        <v>6845195</v>
+        <v>6845225</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6316,22 +6345,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124490978</v>
+        <v>124490692</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6340,25 +6369,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6368,10 +6397,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525086</v>
+        <v>525103</v>
       </c>
       <c r="R56" t="n">
-        <v>6845224</v>
+        <v>6845194</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6430,10 +6459,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124492194</v>
+        <v>124491320</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6442,25 +6471,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6470,10 +6499,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524798</v>
+        <v>525017</v>
       </c>
       <c r="R57" t="n">
-        <v>6845206</v>
+        <v>6845257</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6520,19 +6549,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124486895</v>
+        <v>124486839</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6572,13 +6601,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524856</v>
+        <v>524872</v>
       </c>
       <c r="R58" t="n">
-        <v>6845128</v>
+        <v>6845107</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6622,19 +6651,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124487374</v>
+        <v>124490720</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6674,10 +6703,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524974</v>
+        <v>525133</v>
       </c>
       <c r="R59" t="n">
-        <v>6845191</v>
+        <v>6845307</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6736,10 +6765,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124487039</v>
+        <v>124500867</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6748,50 +6777,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524908</v>
+        <v>524343</v>
       </c>
       <c r="R60" t="n">
-        <v>6845155</v>
+        <v>6845433</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6835,19 +6855,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124499838</v>
+        <v>124504089</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6882,7 +6902,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6896,13 +6916,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524478</v>
+        <v>524238</v>
       </c>
       <c r="R61" t="n">
-        <v>6845426</v>
+        <v>6844930</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6958,10 +6978,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124500909</v>
+        <v>124504054</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6970,41 +6990,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524346</v>
+        <v>524683</v>
       </c>
       <c r="R62" t="n">
-        <v>6845458</v>
+        <v>6844956</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7060,10 +7089,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124501516</v>
+        <v>124504565</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7072,41 +7101,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524237</v>
+        <v>524227</v>
       </c>
       <c r="R63" t="n">
-        <v>6845433</v>
+        <v>6844932</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7150,19 +7188,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124504545</v>
+        <v>124504704</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7197,7 +7235,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7211,10 +7249,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524237</v>
+        <v>524238</v>
       </c>
       <c r="R64" t="n">
-        <v>6844919</v>
+        <v>6844943</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7273,7 +7311,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124492072</v>
+        <v>124489748</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7308,7 +7346,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7322,10 +7360,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524828</v>
+        <v>525230</v>
       </c>
       <c r="R65" t="n">
-        <v>6845147</v>
+        <v>6845187</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7384,10 +7422,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124502910</v>
+        <v>124504945</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7396,50 +7434,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524247</v>
+        <v>524203</v>
       </c>
       <c r="R66" t="n">
-        <v>6845069</v>
+        <v>6844991</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7483,22 +7512,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124500201</v>
+        <v>124490428</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7507,47 +7536,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524390</v>
+        <v>525133</v>
       </c>
       <c r="R67" t="n">
-        <v>6845406</v>
+        <v>6845201</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7580,11 +7600,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7611,7 +7626,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124492000</v>
+        <v>124491387</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7651,10 +7666,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524901</v>
+        <v>524949</v>
       </c>
       <c r="R68" t="n">
-        <v>6845216</v>
+        <v>6845252</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7713,7 +7728,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124490428</v>
+        <v>124487121</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7753,10 +7768,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525133</v>
+        <v>524844</v>
       </c>
       <c r="R69" t="n">
-        <v>6845201</v>
+        <v>6845169</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7815,7 +7830,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124486839</v>
+        <v>124489815</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7855,13 +7870,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524872</v>
+        <v>525208</v>
       </c>
       <c r="R70" t="n">
-        <v>6845107</v>
+        <v>6845169</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7905,19 +7920,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124487514</v>
+        <v>124487283</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7957,13 +7972,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525016</v>
+        <v>524836</v>
       </c>
       <c r="R71" t="n">
-        <v>6845190</v>
+        <v>6845119</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8007,22 +8022,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124491619</v>
+        <v>124492635</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8035,21 +8050,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8059,10 +8074,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524906</v>
+        <v>524790</v>
       </c>
       <c r="R72" t="n">
-        <v>6845220</v>
+        <v>6845219</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8095,6 +8110,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8121,10 +8141,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124501577</v>
+        <v>124502475</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8133,50 +8153,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524252</v>
+        <v>524197</v>
       </c>
       <c r="R73" t="n">
-        <v>6845387</v>
+        <v>6845056</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8220,22 +8231,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124503276</v>
+        <v>124492717</v>
       </c>
       <c r="B74" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8248,37 +8259,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524472</v>
+        <v>524757</v>
       </c>
       <c r="R74" t="n">
-        <v>6845023</v>
+        <v>6845190</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8334,10 +8345,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124492635</v>
+        <v>124488326</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8350,21 +8361,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8374,7 +8385,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524790</v>
+        <v>524734</v>
       </c>
       <c r="R75" t="n">
         <v>6845219</v>
@@ -8410,11 +8421,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8441,10 +8447,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124493358</v>
+        <v>124492072</v>
       </c>
       <c r="B76" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8453,38 +8459,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524793</v>
+        <v>524828</v>
       </c>
       <c r="R76" t="n">
-        <v>6845243</v>
+        <v>6845147</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8543,7 +8558,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124489792</v>
+        <v>124486962</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8578,7 +8593,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8592,10 +8607,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525215</v>
+        <v>524859</v>
       </c>
       <c r="R77" t="n">
-        <v>6845178</v>
+        <v>6845148</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8654,10 +8669,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124491477</v>
+        <v>124500201</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8666,38 +8681,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524920</v>
+        <v>524390</v>
       </c>
       <c r="R78" t="n">
-        <v>6845260</v>
+        <v>6845406</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8730,6 +8754,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8756,7 +8785,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124487467</v>
+        <v>124498070</v>
       </c>
       <c r="B79" t="n">
         <v>78810</v>
@@ -8792,14 +8821,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524805</v>
+        <v>524353</v>
       </c>
       <c r="R79" t="n">
-        <v>6845150</v>
+        <v>6845201</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8858,7 +8887,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124487771</v>
+        <v>124486895</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8898,10 +8927,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524761</v>
+        <v>524856</v>
       </c>
       <c r="R80" t="n">
-        <v>6845213</v>
+        <v>6845128</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8960,7 +8989,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124488103</v>
+        <v>124487689</v>
       </c>
       <c r="B81" t="n">
         <v>78810</v>
@@ -9000,13 +9029,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525146</v>
+        <v>524780</v>
       </c>
       <c r="R81" t="n">
-        <v>6845150</v>
+        <v>6845188</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9050,19 +9079,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124490097</v>
+        <v>124490555</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9102,10 +9131,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525147</v>
+        <v>525142</v>
       </c>
       <c r="R82" t="n">
-        <v>6845208</v>
+        <v>6845241</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9138,6 +9167,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9164,7 +9198,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124504151</v>
+        <v>124500069</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9197,20 +9231,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524256</v>
+        <v>524370</v>
       </c>
       <c r="R83" t="n">
-        <v>6844925</v>
+        <v>6845396</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9240,6 +9283,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9254,22 +9302,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124503504</v>
+        <v>124492807</v>
       </c>
       <c r="B84" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9282,37 +9330,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524511</v>
+        <v>524696</v>
       </c>
       <c r="R84" t="n">
-        <v>6845029</v>
+        <v>6845140</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9356,22 +9404,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124504860</v>
+        <v>124501719</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9384,21 +9432,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9408,13 +9456,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524224</v>
+        <v>524232</v>
       </c>
       <c r="R85" t="n">
-        <v>6844971</v>
+        <v>6845349</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9458,22 +9506,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124492807</v>
+        <v>124499713</v>
       </c>
       <c r="B86" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9486,37 +9534,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524696</v>
+        <v>524311</v>
       </c>
       <c r="R86" t="n">
-        <v>6845140</v>
+        <v>6845368</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9560,19 +9608,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124498070</v>
+        <v>124487514</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9608,17 +9656,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524353</v>
+        <v>525016</v>
       </c>
       <c r="R87" t="n">
-        <v>6845201</v>
+        <v>6845190</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9662,19 +9710,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124498760</v>
+        <v>124487317</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9710,14 +9758,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524388</v>
+        <v>524829</v>
       </c>
       <c r="R88" t="n">
-        <v>6845283</v>
+        <v>6845141</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9776,10 +9824,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124490555</v>
+        <v>124493358</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9792,21 +9840,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9816,13 +9864,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525142</v>
+        <v>524793</v>
       </c>
       <c r="R89" t="n">
-        <v>6845241</v>
+        <v>6845243</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9852,11 +9900,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9871,19 +9914,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124499895</v>
+        <v>124499475</v>
       </c>
       <c r="B90" t="n">
         <v>98101</v>
@@ -9918,7 +9961,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9932,13 +9975,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524362</v>
+        <v>524510</v>
       </c>
       <c r="R90" t="n">
-        <v>6845391</v>
+        <v>6845430</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9968,11 +10011,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9987,22 +10025,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124491531</v>
+        <v>124489792</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10011,41 +10049,50 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524919</v>
+        <v>525215</v>
       </c>
       <c r="R91" t="n">
-        <v>6845253</v>
+        <v>6845178</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10101,10 +10148,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124488657</v>
+        <v>124504769</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10113,41 +10160,50 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525312</v>
+        <v>524231</v>
       </c>
       <c r="R92" t="n">
-        <v>6845117</v>
+        <v>6844957</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10191,22 +10247,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124491548</v>
+        <v>124506146</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10215,38 +10271,47 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524916</v>
+        <v>524148</v>
       </c>
       <c r="R93" t="n">
-        <v>6845244</v>
+        <v>6845027</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10305,10 +10370,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124499127</v>
+        <v>124488157</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10321,37 +10386,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524559</v>
+        <v>524731</v>
       </c>
       <c r="R94" t="n">
-        <v>6845427</v>
+        <v>6845235</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10395,22 +10460,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124493108</v>
+        <v>124488103</v>
       </c>
       <c r="B95" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10423,21 +10488,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10447,13 +10512,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524776</v>
+        <v>525146</v>
       </c>
       <c r="R95" t="n">
-        <v>6845248</v>
+        <v>6845150</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10483,11 +10548,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10502,19 +10562,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124501831</v>
+        <v>124491619</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10550,17 +10610,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524268</v>
+        <v>524906</v>
       </c>
       <c r="R96" t="n">
-        <v>6845351</v>
+        <v>6845220</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10604,19 +10664,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124502475</v>
+        <v>124501831</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10656,10 +10716,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524197</v>
+        <v>524268</v>
       </c>
       <c r="R97" t="n">
-        <v>6845056</v>
+        <v>6845351</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10718,7 +10778,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124504973</v>
+        <v>124489670</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10753,7 +10813,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10763,17 +10823,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524210</v>
+        <v>525247</v>
       </c>
       <c r="R98" t="n">
-        <v>6844954</v>
+        <v>6845194</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10817,22 +10877,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124504651</v>
+        <v>124491765</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10841,50 +10901,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524234</v>
+        <v>524904</v>
       </c>
       <c r="R99" t="n">
-        <v>6844921</v>
+        <v>6845207</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10940,10 +10991,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124504704</v>
+        <v>124487771</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10952,47 +11003,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524238</v>
+        <v>524761</v>
       </c>
       <c r="R100" t="n">
-        <v>6844943</v>
+        <v>6845213</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -11051,10 +11093,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124499475</v>
+        <v>124490965</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11063,47 +11105,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524510</v>
+        <v>525081</v>
       </c>
       <c r="R101" t="n">
-        <v>6845430</v>
+        <v>6845283</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11162,10 +11195,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124503002</v>
+        <v>124488535</v>
       </c>
       <c r="B102" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11178,37 +11211,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524333</v>
+        <v>525311</v>
       </c>
       <c r="R102" t="n">
-        <v>6845022</v>
+        <v>6845039</v>
       </c>
       <c r="S102" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11252,22 +11285,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124501719</v>
+        <v>124500909</v>
       </c>
       <c r="B103" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11280,21 +11313,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11304,13 +11337,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524232</v>
+        <v>524346</v>
       </c>
       <c r="R103" t="n">
-        <v>6845349</v>
+        <v>6845458</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11354,19 +11387,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124503680</v>
+        <v>124501516</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11406,13 +11439,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524648</v>
+        <v>524237</v>
       </c>
       <c r="R104" t="n">
-        <v>6845029</v>
+        <v>6845433</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11456,22 +11489,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124504250</v>
+        <v>124502522</v>
       </c>
       <c r="B105" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11480,25 +11513,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11508,10 +11541,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524436</v>
+        <v>524234</v>
       </c>
       <c r="R105" t="n">
-        <v>6844930</v>
+        <v>6845053</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11544,11 +11577,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11575,10 +11603,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124499713</v>
+        <v>124503276</v>
       </c>
       <c r="B106" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11591,21 +11619,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11615,13 +11643,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524311</v>
+        <v>524472</v>
       </c>
       <c r="R106" t="n">
-        <v>6845368</v>
+        <v>6845023</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11677,10 +11705,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124489815</v>
+        <v>124505582</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11693,37 +11721,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>525208</v>
+        <v>524121</v>
       </c>
       <c r="R107" t="n">
-        <v>6845169</v>
+        <v>6845117</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11779,10 +11807,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124491300</v>
+        <v>124500112</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11795,37 +11823,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>525015</v>
+        <v>524447</v>
       </c>
       <c r="R108" t="n">
-        <v>6845263</v>
+        <v>6845417</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11881,10 +11909,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124498466</v>
+        <v>124499838</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11893,41 +11921,50 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524369</v>
+        <v>524478</v>
       </c>
       <c r="R109" t="n">
-        <v>6845293</v>
+        <v>6845426</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11971,19 +12008,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124499832</v>
+        <v>124501577</v>
       </c>
       <c r="B110" t="n">
         <v>98101</v>
@@ -12018,7 +12055,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12032,10 +12069,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524327</v>
+        <v>524252</v>
       </c>
       <c r="R110" t="n">
-        <v>6845386</v>
+        <v>6845387</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -12094,7 +12131,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124504769</v>
+        <v>124504651</v>
       </c>
       <c r="B111" t="n">
         <v>98101</v>
@@ -12129,7 +12166,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -12143,13 +12180,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524231</v>
+        <v>524234</v>
       </c>
       <c r="R111" t="n">
-        <v>6844957</v>
+        <v>6844921</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12205,10 +12242,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124504565</v>
+        <v>124487604</v>
       </c>
       <c r="B112" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12217,47 +12254,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524227</v>
+        <v>524781</v>
       </c>
       <c r="R112" t="n">
-        <v>6844932</v>
+        <v>6845167</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12316,10 +12344,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124500794</v>
+        <v>124502605</v>
       </c>
       <c r="B113" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12328,25 +12356,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12356,10 +12384,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524370</v>
+        <v>524259</v>
       </c>
       <c r="R113" t="n">
-        <v>6845393</v>
+        <v>6845061</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12418,10 +12446,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124493648</v>
+        <v>124487039</v>
       </c>
       <c r="B114" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12430,35 +12458,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -12467,10 +12495,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524762</v>
+        <v>524908</v>
       </c>
       <c r="R114" t="n">
-        <v>6845231</v>
+        <v>6845155</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12529,10 +12557,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124489670</v>
+        <v>124504250</v>
       </c>
       <c r="B115" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12541,50 +12569,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>525247</v>
+        <v>524436</v>
       </c>
       <c r="R115" t="n">
-        <v>6845194</v>
+        <v>6844930</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12614,6 +12633,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12628,22 +12652,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124492032</v>
+        <v>124500865</v>
       </c>
       <c r="B116" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12652,47 +12676,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524881</v>
+        <v>524350</v>
       </c>
       <c r="R116" t="n">
-        <v>6845143</v>
+        <v>6845399</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12751,10 +12766,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124490527</v>
+        <v>124503680</v>
       </c>
       <c r="B117" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12767,42 +12782,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>525139</v>
+        <v>524648</v>
       </c>
       <c r="R117" t="n">
-        <v>6845241</v>
+        <v>6845029</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12832,11 +12842,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12851,22 +12856,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124501662</v>
+        <v>124504321</v>
       </c>
       <c r="B118" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12875,50 +12880,41 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524272</v>
+        <v>524276</v>
       </c>
       <c r="R118" t="n">
-        <v>6845365</v>
+        <v>6844888</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12974,10 +12970,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124500112</v>
+        <v>124491294</v>
       </c>
       <c r="B119" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12990,37 +12986,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524447</v>
+        <v>525063</v>
       </c>
       <c r="R119" t="n">
-        <v>6845417</v>
+        <v>6845234</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13064,22 +13060,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124501039</v>
+        <v>124498936</v>
       </c>
       <c r="B120" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13088,50 +13084,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524281</v>
+        <v>524415</v>
       </c>
       <c r="R120" t="n">
-        <v>6845383</v>
+        <v>6845335</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13175,19 +13162,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124498529</v>
+        <v>124498466</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13227,10 +13214,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524365</v>
+        <v>524369</v>
       </c>
       <c r="R121" t="n">
-        <v>6845310</v>
+        <v>6845293</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13289,10 +13276,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124487564</v>
+        <v>124503227</v>
       </c>
       <c r="B122" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13305,37 +13292,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524773</v>
+        <v>524472</v>
       </c>
       <c r="R122" t="n">
-        <v>6845141</v>
+        <v>6845023</v>
       </c>
       <c r="S122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13391,7 +13378,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124487775</v>
+        <v>124491427</v>
       </c>
       <c r="B123" t="n">
         <v>78810</v>
@@ -13431,10 +13418,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>525079</v>
+        <v>524946</v>
       </c>
       <c r="R123" t="n">
-        <v>6845164</v>
+        <v>6845286</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13493,7 +13480,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124490965</v>
+        <v>124491531</v>
       </c>
       <c r="B124" t="n">
         <v>78810</v>
@@ -13533,13 +13520,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>525081</v>
+        <v>524919</v>
       </c>
       <c r="R124" t="n">
-        <v>6845283</v>
+        <v>6845253</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13583,22 +13570,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124488157</v>
+        <v>124486832</v>
       </c>
       <c r="B125" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13611,21 +13598,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13635,10 +13622,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524731</v>
+        <v>524856</v>
       </c>
       <c r="R125" t="n">
-        <v>6845235</v>
+        <v>6845111</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13697,10 +13684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124489983</v>
+        <v>124497941</v>
       </c>
       <c r="B126" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13713,37 +13700,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>525195</v>
+        <v>524344</v>
       </c>
       <c r="R126" t="n">
-        <v>6845198</v>
+        <v>6845182</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13799,10 +13786,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124490692</v>
+        <v>124490091</v>
       </c>
       <c r="B127" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13811,25 +13798,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13839,10 +13826,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>525103</v>
+        <v>525149</v>
       </c>
       <c r="R127" t="n">
-        <v>6845194</v>
+        <v>6845210</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13901,7 +13888,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124504321</v>
+        <v>124491477</v>
       </c>
       <c r="B128" t="n">
         <v>78810</v>
@@ -13937,17 +13924,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524276</v>
+        <v>524920</v>
       </c>
       <c r="R128" t="n">
-        <v>6844888</v>
+        <v>6845260</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13991,22 +13978,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124503227</v>
+        <v>124491822</v>
       </c>
       <c r="B129" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14019,37 +14006,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524472</v>
+        <v>524857</v>
       </c>
       <c r="R129" t="n">
-        <v>6845023</v>
+        <v>6845201</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14093,19 +14080,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124500865</v>
+        <v>124489983</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14141,17 +14128,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524350</v>
+        <v>525195</v>
       </c>
       <c r="R130" t="n">
-        <v>6845399</v>
+        <v>6845198</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14195,19 +14182,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124500867</v>
+        <v>124504860</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14247,13 +14234,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524343</v>
+        <v>524224</v>
       </c>
       <c r="R131" t="n">
-        <v>6845433</v>
+        <v>6844971</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14309,7 +14296,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124504354</v>
+        <v>124503388</v>
       </c>
       <c r="B132" t="n">
         <v>98101</v>
@@ -14344,7 +14331,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14358,13 +14345,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524274</v>
+        <v>524214</v>
       </c>
       <c r="R132" t="n">
-        <v>6844889</v>
+        <v>6844996</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14420,10 +14407,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124488923</v>
+        <v>124505389</v>
       </c>
       <c r="B133" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14432,41 +14419,50 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>525312</v>
+        <v>524115</v>
       </c>
       <c r="R133" t="n">
-        <v>6845166</v>
+        <v>6845050</v>
       </c>
       <c r="S133" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14510,19 +14506,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124487689</v>
+        <v>124487564</v>
       </c>
       <c r="B134" t="n">
         <v>78810</v>
@@ -14562,10 +14558,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524780</v>
+        <v>524773</v>
       </c>
       <c r="R134" t="n">
-        <v>6845188</v>
+        <v>6845141</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14624,10 +14620,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124489002</v>
+        <v>124493648</v>
       </c>
       <c r="B135" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14636,38 +14632,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>525277</v>
+        <v>524762</v>
       </c>
       <c r="R135" t="n">
-        <v>6845196</v>
+        <v>6845231</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14700,11 +14705,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14731,10 +14731,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124487567</v>
+        <v>124490165</v>
       </c>
       <c r="B136" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14747,21 +14747,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14771,13 +14771,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>525000</v>
+        <v>525151</v>
       </c>
       <c r="R136" t="n">
-        <v>6845201</v>
+        <v>6845190</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14821,12 +14821,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124490097</v>
+        <v>124491428</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525147</v>
+        <v>524954</v>
       </c>
       <c r="R2" t="n">
-        <v>6845208</v>
+        <v>6845241</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124488657</v>
+        <v>124500794</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525312</v>
+        <v>524370</v>
       </c>
       <c r="R3" t="n">
-        <v>6845117</v>
+        <v>6845393</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124492000</v>
+        <v>124490091</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524901</v>
+        <v>525149</v>
       </c>
       <c r="R4" t="n">
-        <v>6845216</v>
+        <v>6845210</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124499127</v>
+        <v>124492717</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1017,17 +1026,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524559</v>
+        <v>524757</v>
       </c>
       <c r="R5" t="n">
-        <v>6845427</v>
+        <v>6845190</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1080,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124499873</v>
+        <v>124490720</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1119,14 +1128,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524451</v>
+        <v>525133</v>
       </c>
       <c r="R6" t="n">
-        <v>6845435</v>
+        <v>6845307</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124501039</v>
+        <v>124487317</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,50 +1206,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524281</v>
+        <v>524829</v>
       </c>
       <c r="R7" t="n">
-        <v>6845383</v>
+        <v>6845141</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1284,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124504485</v>
+        <v>124504860</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,47 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524261</v>
+        <v>524224</v>
       </c>
       <c r="R8" t="n">
-        <v>6844909</v>
+        <v>6844971</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1509,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124500965</v>
+        <v>124501831</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1549,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524308</v>
+        <v>524268</v>
       </c>
       <c r="R10" t="n">
-        <v>6845471</v>
+        <v>6845351</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,19 +1590,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124488923</v>
+        <v>124500965</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1647,17 +1638,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525312</v>
+        <v>524308</v>
       </c>
       <c r="R11" t="n">
-        <v>6845166</v>
+        <v>6845471</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124489866</v>
+        <v>124491320</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525217</v>
+        <v>525017</v>
       </c>
       <c r="R12" t="n">
-        <v>6845195</v>
+        <v>6845257</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124498529</v>
+        <v>124498936</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524365</v>
+        <v>524415</v>
       </c>
       <c r="R13" t="n">
-        <v>6845310</v>
+        <v>6845335</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1917,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124492194</v>
+        <v>124492807</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524798</v>
+        <v>524696</v>
       </c>
       <c r="R14" t="n">
-        <v>6845206</v>
+        <v>6845140</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2007,19 +1998,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124504973</v>
+        <v>124501039</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2054,7 +2045,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2068,13 +2059,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524210</v>
+        <v>524281</v>
       </c>
       <c r="R15" t="n">
-        <v>6844954</v>
+        <v>6845383</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2118,19 +2109,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124492513</v>
+        <v>124498529</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2166,17 +2157,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524774</v>
+        <v>524365</v>
       </c>
       <c r="R16" t="n">
-        <v>6845100</v>
+        <v>6845310</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,19 +2211,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124487467</v>
+        <v>124491387</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2272,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524805</v>
+        <v>524949</v>
       </c>
       <c r="R17" t="n">
-        <v>6845150</v>
+        <v>6845252</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2334,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124498544</v>
+        <v>124498794</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>92293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,25 +2337,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2374,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524364</v>
+        <v>524383</v>
       </c>
       <c r="R18" t="n">
-        <v>6845312</v>
+        <v>6845264</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2436,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124502783</v>
+        <v>124486839</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,47 +2439,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524254</v>
+        <v>524872</v>
       </c>
       <c r="R19" t="n">
-        <v>6845067</v>
+        <v>6845107</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2547,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124487567</v>
+        <v>124487514</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2587,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525000</v>
+        <v>525016</v>
       </c>
       <c r="R20" t="n">
-        <v>6845201</v>
+        <v>6845190</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2649,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124487293</v>
+        <v>124499127</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2661,47 +2643,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524948</v>
+        <v>524559</v>
       </c>
       <c r="R21" t="n">
-        <v>6845179</v>
+        <v>6845427</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2760,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124492032</v>
+        <v>124489002</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2772,47 +2745,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524881</v>
+        <v>525277</v>
       </c>
       <c r="R22" t="n">
-        <v>6845143</v>
+        <v>6845196</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2845,6 +2809,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2871,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124493108</v>
+        <v>124499832</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,38 +2852,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524776</v>
+        <v>524327</v>
       </c>
       <c r="R23" t="n">
-        <v>6845248</v>
+        <v>6845386</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2947,11 +2925,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2978,7 +2951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124501563</v>
+        <v>124501719</v>
       </c>
       <c r="B24" t="n">
         <v>79891</v>
@@ -3018,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524245</v>
+        <v>524232</v>
       </c>
       <c r="R24" t="n">
-        <v>6845371</v>
+        <v>6845349</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3080,10 +3053,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124499480</v>
+        <v>124505582</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3092,50 +3065,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524365</v>
+        <v>524121</v>
       </c>
       <c r="R25" t="n">
-        <v>6845400</v>
+        <v>6845117</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3165,11 +3129,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3196,10 +3155,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124499832</v>
+        <v>124502475</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3208,50 +3167,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524327</v>
+        <v>524197</v>
       </c>
       <c r="R26" t="n">
-        <v>6845386</v>
+        <v>6845056</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3295,22 +3245,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124491917</v>
+        <v>124504769</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,38 +3269,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524852</v>
+        <v>524231</v>
       </c>
       <c r="R27" t="n">
-        <v>6845214</v>
+        <v>6844957</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3409,7 +3368,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124498760</v>
+        <v>124491805</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3445,14 +3404,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524388</v>
+        <v>524880</v>
       </c>
       <c r="R28" t="n">
-        <v>6845283</v>
+        <v>6845212</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3511,7 +3470,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124487374</v>
+        <v>124488103</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3551,13 +3510,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524974</v>
+        <v>525146</v>
       </c>
       <c r="R29" t="n">
-        <v>6845191</v>
+        <v>6845150</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3613,7 +3572,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124504354</v>
+        <v>124499838</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3648,7 +3607,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3662,13 +3621,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524274</v>
+        <v>524478</v>
       </c>
       <c r="R30" t="n">
-        <v>6844889</v>
+        <v>6845426</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3724,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124500794</v>
+        <v>124487467</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,41 +3695,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524370</v>
+        <v>524805</v>
       </c>
       <c r="R31" t="n">
-        <v>6845393</v>
+        <v>6845150</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3814,22 +3773,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124504151</v>
+        <v>124489815</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,41 +3797,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524256</v>
+        <v>525208</v>
       </c>
       <c r="R32" t="n">
-        <v>6844925</v>
+        <v>6845169</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3916,22 +3875,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124504916</v>
+        <v>124498070</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,47 +3899,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524219</v>
+        <v>524353</v>
       </c>
       <c r="R33" t="n">
-        <v>6844970</v>
+        <v>6845201</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4039,7 +3989,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124491805</v>
+        <v>124487771</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4079,10 +4029,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524880</v>
+        <v>524761</v>
       </c>
       <c r="R34" t="n">
-        <v>6845212</v>
+        <v>6845213</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4141,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124498794</v>
+        <v>124488326</v>
       </c>
       <c r="B35" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4153,38 +4103,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524383</v>
+        <v>524734</v>
       </c>
       <c r="R35" t="n">
-        <v>6845264</v>
+        <v>6845219</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4243,10 +4193,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124503027</v>
+        <v>124504485</v>
       </c>
       <c r="B36" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4255,38 +4205,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524345</v>
+        <v>524261</v>
       </c>
       <c r="R36" t="n">
-        <v>6845032</v>
+        <v>6844909</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4345,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124499895</v>
+        <v>124491765</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,47 +4316,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524362</v>
+        <v>524904</v>
       </c>
       <c r="R37" t="n">
-        <v>6845391</v>
+        <v>6845207</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4430,11 +4380,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4461,10 +4406,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124504545</v>
+        <v>124488923</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4473,50 +4418,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524237</v>
+        <v>525312</v>
       </c>
       <c r="R38" t="n">
-        <v>6844919</v>
+        <v>6845166</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4560,22 +4496,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124487775</v>
+        <v>124500926</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4588,37 +4524,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525079</v>
+        <v>524345</v>
       </c>
       <c r="R39" t="n">
-        <v>6845164</v>
+        <v>6845461</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4662,22 +4598,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124503002</v>
+        <v>124504662</v>
       </c>
       <c r="B40" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4690,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4714,13 +4650,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524333</v>
+        <v>524244</v>
       </c>
       <c r="R40" t="n">
-        <v>6845022</v>
+        <v>6844920</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4776,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124501662</v>
+        <v>124501563</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4788,50 +4724,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524272</v>
+        <v>524245</v>
       </c>
       <c r="R41" t="n">
-        <v>6845365</v>
+        <v>6845371</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4887,7 +4814,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124504513</v>
+        <v>124502783</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4922,7 +4849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4936,13 +4863,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524245</v>
+        <v>524254</v>
       </c>
       <c r="R42" t="n">
-        <v>6844924</v>
+        <v>6845067</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4986,22 +4913,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124490978</v>
+        <v>124503227</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5014,37 +4941,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525086</v>
+        <v>524472</v>
       </c>
       <c r="R43" t="n">
-        <v>6845224</v>
+        <v>6845023</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5100,10 +5027,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124491300</v>
+        <v>124493108</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5116,21 +5043,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5140,13 +5067,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525015</v>
+        <v>524776</v>
       </c>
       <c r="R44" t="n">
-        <v>6845263</v>
+        <v>6845248</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5176,6 +5103,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5190,22 +5122,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124490527</v>
+        <v>124487293</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5214,31 +5146,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5247,10 +5183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525139</v>
+        <v>524948</v>
       </c>
       <c r="R45" t="n">
-        <v>6845241</v>
+        <v>6845179</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5283,11 +5219,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5314,10 +5245,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124503785</v>
+        <v>124490097</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5330,37 +5261,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524244</v>
+        <v>525147</v>
       </c>
       <c r="R46" t="n">
-        <v>6845004</v>
+        <v>6845208</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5416,7 +5347,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124504662</v>
+        <v>124504321</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5456,13 +5387,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524244</v>
+        <v>524276</v>
       </c>
       <c r="R47" t="n">
-        <v>6844920</v>
+        <v>6844888</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5506,22 +5437,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124500926</v>
+        <v>124503276</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5534,21 +5465,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5558,10 +5489,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524345</v>
+        <v>524472</v>
       </c>
       <c r="R48" t="n">
-        <v>6845461</v>
+        <v>6845023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5620,10 +5551,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124491246</v>
+        <v>124503388</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5632,38 +5563,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525065</v>
+        <v>524214</v>
       </c>
       <c r="R49" t="n">
-        <v>6845243</v>
+        <v>6844996</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5710,19 +5650,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124491548</v>
+        <v>124486832</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5762,10 +5702,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524916</v>
+        <v>524856</v>
       </c>
       <c r="R50" t="n">
-        <v>6845244</v>
+        <v>6845111</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5824,10 +5764,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124489002</v>
+        <v>124487039</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5836,38 +5776,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525277</v>
+        <v>524908</v>
       </c>
       <c r="R51" t="n">
-        <v>6845196</v>
+        <v>6845155</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5900,11 +5849,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,10 +5875,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124502910</v>
+        <v>124491917</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5943,50 +5887,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524247</v>
+        <v>524852</v>
       </c>
       <c r="R52" t="n">
-        <v>6845069</v>
+        <v>6845214</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6030,22 +5965,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124503504</v>
+        <v>124486895</v>
       </c>
       <c r="B53" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6058,34 +5993,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524511</v>
+        <v>524856</v>
       </c>
       <c r="R53" t="n">
-        <v>6845029</v>
+        <v>6845128</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6144,7 +6079,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124491428</v>
+        <v>124504973</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6179,7 +6114,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6189,14 +6124,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524954</v>
+        <v>524210</v>
       </c>
       <c r="R54" t="n">
-        <v>6845241</v>
+        <v>6844954</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6255,10 +6190,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124498165</v>
+        <v>124504354</v>
       </c>
       <c r="B55" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6267,41 +6202,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524349</v>
+        <v>524274</v>
       </c>
       <c r="R55" t="n">
-        <v>6845225</v>
+        <v>6844889</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6345,22 +6289,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124490692</v>
+        <v>124500069</v>
       </c>
       <c r="B56" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6369,38 +6313,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525103</v>
+        <v>524370</v>
       </c>
       <c r="R56" t="n">
-        <v>6845194</v>
+        <v>6845396</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6433,6 +6386,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6459,10 +6417,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124491320</v>
+        <v>124487775</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6471,25 +6429,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6499,13 +6457,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525017</v>
+        <v>525079</v>
       </c>
       <c r="R57" t="n">
-        <v>6845257</v>
+        <v>6845164</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6561,10 +6519,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124486839</v>
+        <v>124498165</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6577,37 +6535,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524872</v>
+        <v>524349</v>
       </c>
       <c r="R58" t="n">
-        <v>6845107</v>
+        <v>6845225</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6651,19 +6609,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124490720</v>
+        <v>124492194</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6703,13 +6661,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525133</v>
+        <v>524798</v>
       </c>
       <c r="R59" t="n">
-        <v>6845307</v>
+        <v>6845206</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6753,19 +6711,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124500867</v>
+        <v>124490965</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -6801,17 +6759,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524343</v>
+        <v>525081</v>
       </c>
       <c r="R60" t="n">
-        <v>6845433</v>
+        <v>6845283</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6855,22 +6813,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124504089</v>
+        <v>124488657</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6879,50 +6837,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524238</v>
+        <v>525312</v>
       </c>
       <c r="R61" t="n">
-        <v>6844930</v>
+        <v>6845117</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6978,10 +6927,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124504054</v>
+        <v>124491619</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6990,47 +6939,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524683</v>
+        <v>524906</v>
       </c>
       <c r="R62" t="n">
-        <v>6844956</v>
+        <v>6845220</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7089,10 +7029,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124504565</v>
+        <v>124491300</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7101,50 +7041,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524227</v>
+        <v>525015</v>
       </c>
       <c r="R63" t="n">
-        <v>6844932</v>
+        <v>6845263</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7188,22 +7119,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124504704</v>
+        <v>124490555</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7212,50 +7143,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524238</v>
+        <v>525142</v>
       </c>
       <c r="R64" t="n">
-        <v>6844943</v>
+        <v>6845241</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7285,6 +7207,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7299,19 +7226,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124489748</v>
+        <v>124505389</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7346,7 +7273,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7356,14 +7283,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525230</v>
+        <v>524115</v>
       </c>
       <c r="R65" t="n">
-        <v>6845187</v>
+        <v>6845050</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7422,10 +7349,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124504945</v>
+        <v>124504089</v>
       </c>
       <c r="B66" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7434,38 +7361,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524203</v>
+        <v>524238</v>
       </c>
       <c r="R66" t="n">
-        <v>6844991</v>
+        <v>6844930</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7512,22 +7448,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124490428</v>
+        <v>124504651</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7536,41 +7472,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525133</v>
+        <v>524234</v>
       </c>
       <c r="R67" t="n">
-        <v>6845201</v>
+        <v>6844921</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7626,10 +7571,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124491387</v>
+        <v>124499480</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7638,38 +7583,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524949</v>
+        <v>524365</v>
       </c>
       <c r="R68" t="n">
-        <v>6845252</v>
+        <v>6845400</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7702,6 +7656,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7728,10 +7687,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124487121</v>
+        <v>124492072</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7740,38 +7699,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524844</v>
+        <v>524828</v>
       </c>
       <c r="R69" t="n">
-        <v>6845169</v>
+        <v>6845147</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7830,7 +7798,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124489815</v>
+        <v>124500865</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7866,17 +7834,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525208</v>
+        <v>524350</v>
       </c>
       <c r="R70" t="n">
-        <v>6845169</v>
+        <v>6845399</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7920,19 +7888,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124487283</v>
+        <v>124502605</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7968,17 +7936,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524836</v>
+        <v>524259</v>
       </c>
       <c r="R71" t="n">
-        <v>6845119</v>
+        <v>6845061</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8022,22 +7990,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124492635</v>
+        <v>124500867</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8050,37 +8018,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524790</v>
+        <v>524343</v>
       </c>
       <c r="R72" t="n">
-        <v>6845219</v>
+        <v>6845433</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8110,11 +8078,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8141,10 +8104,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124502475</v>
+        <v>124504151</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8153,25 +8116,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8181,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524197</v>
+        <v>524256</v>
       </c>
       <c r="R73" t="n">
-        <v>6845056</v>
+        <v>6844925</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8243,10 +8206,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124492717</v>
+        <v>124499713</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8259,34 +8222,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524757</v>
+        <v>524311</v>
       </c>
       <c r="R74" t="n">
-        <v>6845190</v>
+        <v>6845368</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8345,7 +8308,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124488326</v>
+        <v>124492513</v>
       </c>
       <c r="B75" t="n">
         <v>78810</v>
@@ -8385,13 +8348,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524734</v>
+        <v>524774</v>
       </c>
       <c r="R75" t="n">
-        <v>6845219</v>
+        <v>6845100</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8435,22 +8398,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124492072</v>
+        <v>124498466</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8459,47 +8422,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524828</v>
+        <v>524369</v>
       </c>
       <c r="R76" t="n">
-        <v>6845147</v>
+        <v>6845293</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8558,7 +8512,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124486962</v>
+        <v>124500201</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8593,7 +8547,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8603,14 +8557,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524859</v>
+        <v>524390</v>
       </c>
       <c r="R77" t="n">
-        <v>6845148</v>
+        <v>6845406</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8643,6 +8597,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8669,10 +8628,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124500201</v>
+        <v>124500909</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8681,50 +8640,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524390</v>
+        <v>524346</v>
       </c>
       <c r="R78" t="n">
-        <v>6845406</v>
+        <v>6845458</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8754,11 +8704,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8785,7 +8730,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124498070</v>
+        <v>124490428</v>
       </c>
       <c r="B79" t="n">
         <v>78810</v>
@@ -8821,11 +8766,11 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524353</v>
+        <v>525133</v>
       </c>
       <c r="R79" t="n">
         <v>6845201</v>
@@ -8887,7 +8832,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124486895</v>
+        <v>124490978</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8927,10 +8872,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524856</v>
+        <v>525086</v>
       </c>
       <c r="R80" t="n">
-        <v>6845128</v>
+        <v>6845224</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8989,7 +8934,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124487689</v>
+        <v>124491294</v>
       </c>
       <c r="B81" t="n">
         <v>78810</v>
@@ -9029,10 +8974,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524780</v>
+        <v>525063</v>
       </c>
       <c r="R81" t="n">
-        <v>6845188</v>
+        <v>6845234</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9091,10 +9036,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124490555</v>
+        <v>124489792</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9103,41 +9048,50 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525142</v>
+        <v>525215</v>
       </c>
       <c r="R82" t="n">
-        <v>6845241</v>
+        <v>6845178</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9167,11 +9121,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9186,22 +9135,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124500069</v>
+        <v>124491246</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9210,47 +9159,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524370</v>
+        <v>525065</v>
       </c>
       <c r="R83" t="n">
-        <v>6845396</v>
+        <v>6845243</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9283,11 +9223,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9314,10 +9249,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124492807</v>
+        <v>124501516</v>
       </c>
       <c r="B84" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9330,34 +9265,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524696</v>
+        <v>524237</v>
       </c>
       <c r="R84" t="n">
-        <v>6845140</v>
+        <v>6845433</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9416,10 +9351,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124501719</v>
+        <v>124497941</v>
       </c>
       <c r="B85" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9432,21 +9367,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9456,13 +9391,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524232</v>
+        <v>524344</v>
       </c>
       <c r="R85" t="n">
-        <v>6845349</v>
+        <v>6845182</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9506,22 +9441,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124499713</v>
+        <v>124490527</v>
       </c>
       <c r="B86" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9534,37 +9469,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524311</v>
+        <v>525139</v>
       </c>
       <c r="R86" t="n">
-        <v>6845368</v>
+        <v>6845241</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9594,6 +9534,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9608,22 +9553,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124487514</v>
+        <v>124503504</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9636,37 +9581,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525016</v>
+        <v>524511</v>
       </c>
       <c r="R87" t="n">
-        <v>6845190</v>
+        <v>6845029</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9710,22 +9655,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124487317</v>
+        <v>124506146</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9734,38 +9679,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524829</v>
+        <v>524148</v>
       </c>
       <c r="R88" t="n">
-        <v>6845141</v>
+        <v>6845027</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9824,10 +9778,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124493358</v>
+        <v>124489670</v>
       </c>
       <c r="B89" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9836,41 +9790,50 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524793</v>
+        <v>525247</v>
       </c>
       <c r="R89" t="n">
-        <v>6845243</v>
+        <v>6845194</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9914,12 +9877,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10037,10 +10000,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124489792</v>
+        <v>124504250</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10049,47 +10012,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525215</v>
+        <v>524436</v>
       </c>
       <c r="R91" t="n">
-        <v>6845178</v>
+        <v>6844930</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -10122,6 +10076,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10148,10 +10107,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124504769</v>
+        <v>124503785</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10160,47 +10119,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524231</v>
+        <v>524244</v>
       </c>
       <c r="R92" t="n">
-        <v>6844957</v>
+        <v>6845004</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10247,22 +10197,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124506146</v>
+        <v>124491531</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10271,50 +10221,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524148</v>
+        <v>524919</v>
       </c>
       <c r="R93" t="n">
-        <v>6845027</v>
+        <v>6845253</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10472,10 +10413,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124488103</v>
+        <v>124493358</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10488,21 +10429,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10512,13 +10453,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525146</v>
+        <v>524793</v>
       </c>
       <c r="R95" t="n">
-        <v>6845150</v>
+        <v>6845243</v>
       </c>
       <c r="S95" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10562,19 +10503,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124491619</v>
+        <v>124502522</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10610,14 +10551,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524906</v>
+        <v>524234</v>
       </c>
       <c r="R96" t="n">
-        <v>6845220</v>
+        <v>6845053</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10676,10 +10617,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124501831</v>
+        <v>124504545</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10688,41 +10629,50 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524268</v>
+        <v>524237</v>
       </c>
       <c r="R97" t="n">
-        <v>6845351</v>
+        <v>6844919</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10766,19 +10716,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124489670</v>
+        <v>124501577</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10813,7 +10763,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10823,17 +10773,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>525247</v>
+        <v>524252</v>
       </c>
       <c r="R98" t="n">
-        <v>6845194</v>
+        <v>6845387</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10877,22 +10827,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124491765</v>
+        <v>124492032</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10901,41 +10851,50 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524904</v>
+        <v>524881</v>
       </c>
       <c r="R99" t="n">
-        <v>6845207</v>
+        <v>6845143</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10979,19 +10938,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124487771</v>
+        <v>124491548</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -11031,10 +10990,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524761</v>
+        <v>524916</v>
       </c>
       <c r="R100" t="n">
-        <v>6845213</v>
+        <v>6845244</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -11093,10 +11052,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124490965</v>
+        <v>124500112</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11109,34 +11068,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>525081</v>
+        <v>524447</v>
       </c>
       <c r="R101" t="n">
-        <v>6845283</v>
+        <v>6845417</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11195,10 +11154,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124488535</v>
+        <v>124502910</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11207,38 +11166,47 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>525311</v>
+        <v>524247</v>
       </c>
       <c r="R102" t="n">
-        <v>6845039</v>
+        <v>6845069</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11297,10 +11265,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124500909</v>
+        <v>124501662</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11309,41 +11277,50 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524346</v>
+        <v>524272</v>
       </c>
       <c r="R103" t="n">
-        <v>6845458</v>
+        <v>6845365</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11387,22 +11364,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124501516</v>
+        <v>124504704</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11411,41 +11388,50 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524237</v>
+        <v>524238</v>
       </c>
       <c r="R104" t="n">
-        <v>6845433</v>
+        <v>6844943</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11489,19 +11475,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124502522</v>
+        <v>124498760</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11541,10 +11527,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524234</v>
+        <v>524388</v>
       </c>
       <c r="R105" t="n">
-        <v>6845053</v>
+        <v>6845283</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11603,10 +11589,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124503276</v>
+        <v>124489983</v>
       </c>
       <c r="B106" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11619,37 +11605,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524472</v>
+        <v>525195</v>
       </c>
       <c r="R106" t="n">
-        <v>6845023</v>
+        <v>6845198</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11705,10 +11691,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124505582</v>
+        <v>124503002</v>
       </c>
       <c r="B107" t="n">
-        <v>91032</v>
+        <v>78546</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11721,21 +11707,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11745,13 +11731,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524121</v>
+        <v>524333</v>
       </c>
       <c r="R107" t="n">
-        <v>6845117</v>
+        <v>6845022</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11807,10 +11793,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124500112</v>
+        <v>124503680</v>
       </c>
       <c r="B108" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11823,21 +11809,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11847,13 +11833,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524447</v>
+        <v>524648</v>
       </c>
       <c r="R108" t="n">
-        <v>6845417</v>
+        <v>6845029</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11897,22 +11883,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124499838</v>
+        <v>124489866</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11921,50 +11907,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524478</v>
+        <v>525217</v>
       </c>
       <c r="R109" t="n">
-        <v>6845426</v>
+        <v>6845195</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12020,10 +11997,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124501577</v>
+        <v>124487121</v>
       </c>
       <c r="B110" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12032,47 +12009,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524252</v>
+        <v>524844</v>
       </c>
       <c r="R110" t="n">
-        <v>6845387</v>
+        <v>6845169</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -12131,10 +12099,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124504651</v>
+        <v>124487374</v>
       </c>
       <c r="B111" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12143,50 +12111,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524234</v>
+        <v>524974</v>
       </c>
       <c r="R111" t="n">
-        <v>6844921</v>
+        <v>6845191</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12230,19 +12189,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124487604</v>
+        <v>124492000</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -12282,10 +12241,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524781</v>
+        <v>524901</v>
       </c>
       <c r="R112" t="n">
-        <v>6845167</v>
+        <v>6845216</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12344,10 +12303,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124502605</v>
+        <v>124499895</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12356,41 +12315,50 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524259</v>
+        <v>524362</v>
       </c>
       <c r="R113" t="n">
-        <v>6845061</v>
+        <v>6845391</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12420,6 +12388,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12434,19 +12407,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124487039</v>
+        <v>124486962</v>
       </c>
       <c r="B114" t="n">
         <v>98101</v>
@@ -12481,7 +12454,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -12495,13 +12468,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524908</v>
+        <v>524859</v>
       </c>
       <c r="R114" t="n">
-        <v>6845155</v>
+        <v>6845148</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12545,22 +12518,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124504250</v>
+        <v>124487567</v>
       </c>
       <c r="B115" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12569,41 +12542,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524436</v>
+        <v>525000</v>
       </c>
       <c r="R115" t="n">
-        <v>6844930</v>
+        <v>6845201</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12633,11 +12606,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12652,22 +12620,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124500865</v>
+        <v>124504916</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12676,41 +12644,50 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524350</v>
+        <v>524219</v>
       </c>
       <c r="R116" t="n">
-        <v>6845399</v>
+        <v>6844970</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12754,19 +12731,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124503680</v>
+        <v>124491477</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -12802,14 +12779,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524648</v>
+        <v>524920</v>
       </c>
       <c r="R117" t="n">
-        <v>6845029</v>
+        <v>6845260</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12868,10 +12845,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124504321</v>
+        <v>124504513</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12880,41 +12857,50 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524276</v>
+        <v>524245</v>
       </c>
       <c r="R118" t="n">
-        <v>6844888</v>
+        <v>6844924</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12958,19 +12944,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124491294</v>
+        <v>124487283</v>
       </c>
       <c r="B119" t="n">
         <v>78810</v>
@@ -13010,10 +12996,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>525063</v>
+        <v>524836</v>
       </c>
       <c r="R119" t="n">
-        <v>6845234</v>
+        <v>6845119</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13072,10 +13058,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124498936</v>
+        <v>124487604</v>
       </c>
       <c r="B120" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13088,34 +13074,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524415</v>
+        <v>524781</v>
       </c>
       <c r="R120" t="n">
-        <v>6845335</v>
+        <v>6845167</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -13174,7 +13160,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124498466</v>
+        <v>124491427</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13210,17 +13196,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524369</v>
+        <v>524946</v>
       </c>
       <c r="R121" t="n">
-        <v>6845293</v>
+        <v>6845286</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13264,22 +13250,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124503227</v>
+        <v>124498544</v>
       </c>
       <c r="B122" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13292,21 +13278,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13316,13 +13302,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524472</v>
+        <v>524364</v>
       </c>
       <c r="R122" t="n">
-        <v>6845023</v>
+        <v>6845312</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13378,7 +13364,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124491427</v>
+        <v>124488535</v>
       </c>
       <c r="B123" t="n">
         <v>78810</v>
@@ -13418,10 +13404,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524946</v>
+        <v>525311</v>
       </c>
       <c r="R123" t="n">
-        <v>6845286</v>
+        <v>6845039</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13480,7 +13466,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124491531</v>
+        <v>124487689</v>
       </c>
       <c r="B124" t="n">
         <v>78810</v>
@@ -13520,13 +13506,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524919</v>
+        <v>524780</v>
       </c>
       <c r="R124" t="n">
-        <v>6845253</v>
+        <v>6845188</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13582,7 +13568,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124486832</v>
+        <v>124499873</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -13618,17 +13604,17 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524856</v>
+        <v>524451</v>
       </c>
       <c r="R125" t="n">
-        <v>6845111</v>
+        <v>6845435</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13672,22 +13658,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124497941</v>
+        <v>124504054</v>
       </c>
       <c r="B126" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13696,41 +13682,50 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524344</v>
+        <v>524683</v>
       </c>
       <c r="R126" t="n">
-        <v>6845182</v>
+        <v>6844956</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13786,10 +13781,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124490091</v>
+        <v>124493648</v>
       </c>
       <c r="B127" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13798,41 +13793,50 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>525149</v>
+        <v>524762</v>
       </c>
       <c r="R127" t="n">
-        <v>6845210</v>
+        <v>6845231</v>
       </c>
       <c r="S127" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13876,22 +13880,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124491477</v>
+        <v>124490692</v>
       </c>
       <c r="B128" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13900,25 +13904,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13928,10 +13932,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524920</v>
+        <v>525103</v>
       </c>
       <c r="R128" t="n">
-        <v>6845260</v>
+        <v>6845194</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13990,7 +13994,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124491822</v>
+        <v>124487564</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14030,10 +14034,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524857</v>
+        <v>524773</v>
       </c>
       <c r="R129" t="n">
-        <v>6845201</v>
+        <v>6845141</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14080,19 +14084,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124489983</v>
+        <v>124490165</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14132,10 +14136,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>525195</v>
+        <v>525151</v>
       </c>
       <c r="R130" t="n">
-        <v>6845198</v>
+        <v>6845190</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14194,10 +14198,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124504860</v>
+        <v>124489748</v>
       </c>
       <c r="B131" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14206,38 +14210,47 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524224</v>
+        <v>525230</v>
       </c>
       <c r="R131" t="n">
-        <v>6844971</v>
+        <v>6845187</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14296,10 +14309,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124503388</v>
+        <v>124492635</v>
       </c>
       <c r="B132" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14308,47 +14321,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524214</v>
+        <v>524790</v>
       </c>
       <c r="R132" t="n">
-        <v>6844996</v>
+        <v>6845219</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>
@@ -14383,6 +14387,11 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14395,22 +14404,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124505389</v>
+        <v>124504945</v>
       </c>
       <c r="B133" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14419,47 +14428,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524115</v>
+        <v>524203</v>
       </c>
       <c r="R133" t="n">
-        <v>6845050</v>
+        <v>6844991</v>
       </c>
       <c r="S133" t="n">
         <v>20</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124487564</v>
+        <v>124504565</v>
       </c>
       <c r="B134" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14530,38 +14530,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524773</v>
+        <v>524227</v>
       </c>
       <c r="R134" t="n">
-        <v>6845141</v>
+        <v>6844932</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14620,10 +14629,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124493648</v>
+        <v>124491822</v>
       </c>
       <c r="B135" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14632,50 +14641,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524762</v>
+        <v>524857</v>
       </c>
       <c r="R135" t="n">
-        <v>6845231</v>
+        <v>6845201</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14731,10 +14731,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124490165</v>
+        <v>124503027</v>
       </c>
       <c r="B136" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14747,34 +14747,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>525151</v>
+        <v>524345</v>
       </c>
       <c r="R136" t="n">
-        <v>6845190</v>
+        <v>6845032</v>
       </c>
       <c r="S136" t="n">
         <v>20</v>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124491428</v>
+        <v>124500865</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524954</v>
+        <v>524350</v>
       </c>
       <c r="R2" t="n">
-        <v>6845241</v>
+        <v>6845399</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124500794</v>
+        <v>124493108</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524370</v>
+        <v>524776</v>
       </c>
       <c r="R3" t="n">
-        <v>6845393</v>
+        <v>6845248</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124490091</v>
+        <v>124497941</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525149</v>
+        <v>524344</v>
       </c>
       <c r="R4" t="n">
-        <v>6845210</v>
+        <v>6845182</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124492717</v>
+        <v>124498165</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,34 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524757</v>
+        <v>524349</v>
       </c>
       <c r="R5" t="n">
-        <v>6845190</v>
+        <v>6845225</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124490720</v>
+        <v>124491246</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1132,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525133</v>
+        <v>525065</v>
       </c>
       <c r="R6" t="n">
-        <v>6845307</v>
+        <v>6845243</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124487317</v>
+        <v>124502910</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,41 +1202,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524829</v>
+        <v>524247</v>
       </c>
       <c r="R7" t="n">
-        <v>6845141</v>
+        <v>6845069</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1289,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124504860</v>
+        <v>124503504</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524224</v>
+        <v>524511</v>
       </c>
       <c r="R8" t="n">
-        <v>6844971</v>
+        <v>6845029</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1398,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124502991</v>
+        <v>124489866</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,17 +1439,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524280</v>
+        <v>525217</v>
       </c>
       <c r="R9" t="n">
-        <v>6845054</v>
+        <v>6845195</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124501831</v>
+        <v>124493648</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,38 +1517,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524268</v>
+        <v>524762</v>
       </c>
       <c r="R10" t="n">
-        <v>6845351</v>
+        <v>6845231</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,7 +1616,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124500965</v>
+        <v>124492000</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1638,14 +1652,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524308</v>
+        <v>524901</v>
       </c>
       <c r="R11" t="n">
-        <v>6845471</v>
+        <v>6845216</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1704,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124491320</v>
+        <v>124491548</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1730,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525017</v>
+        <v>524916</v>
       </c>
       <c r="R12" t="n">
-        <v>6845257</v>
+        <v>6845244</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1794,22 +1808,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124498936</v>
+        <v>124490555</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,37 +1836,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524415</v>
+        <v>525142</v>
       </c>
       <c r="R13" t="n">
-        <v>6845335</v>
+        <v>6845241</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,6 +1896,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,22 +1915,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124492807</v>
+        <v>124487564</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,13 +1967,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524696</v>
+        <v>524773</v>
       </c>
       <c r="R14" t="n">
-        <v>6845140</v>
+        <v>6845141</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1998,22 +2017,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124501039</v>
+        <v>124488157</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,50 +2041,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524281</v>
+        <v>524731</v>
       </c>
       <c r="R15" t="n">
-        <v>6845383</v>
+        <v>6845235</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2109,19 +2119,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124498529</v>
+        <v>124491531</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2157,17 +2167,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524365</v>
+        <v>524919</v>
       </c>
       <c r="R16" t="n">
-        <v>6845310</v>
+        <v>6845253</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124491387</v>
+        <v>124503785</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,34 +2249,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524949</v>
+        <v>524244</v>
       </c>
       <c r="R17" t="n">
-        <v>6845252</v>
+        <v>6845004</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2313,22 +2323,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124498794</v>
+        <v>124504354</v>
       </c>
       <c r="B18" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,41 +2347,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524383</v>
+        <v>524274</v>
       </c>
       <c r="R18" t="n">
-        <v>6845264</v>
+        <v>6844889</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2415,22 +2434,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124486839</v>
+        <v>124502783</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,38 +2458,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524872</v>
+        <v>524254</v>
       </c>
       <c r="R19" t="n">
-        <v>6845107</v>
+        <v>6845067</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124487514</v>
+        <v>124489670</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,38 +2569,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525016</v>
+        <v>525247</v>
       </c>
       <c r="R20" t="n">
-        <v>6845190</v>
+        <v>6845194</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2631,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124499127</v>
+        <v>124501039</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,38 +2680,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524559</v>
+        <v>524281</v>
       </c>
       <c r="R21" t="n">
-        <v>6845427</v>
+        <v>6845383</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2733,7 +2779,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124489002</v>
+        <v>124490428</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2773,13 +2819,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525277</v>
+        <v>525133</v>
       </c>
       <c r="R22" t="n">
-        <v>6845196</v>
+        <v>6845201</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2809,11 +2855,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2828,22 +2869,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124499832</v>
+        <v>124499873</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2852,50 +2893,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524327</v>
+        <v>524451</v>
       </c>
       <c r="R23" t="n">
-        <v>6845386</v>
+        <v>6845435</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2939,12 +2971,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3053,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124505582</v>
+        <v>124500794</v>
       </c>
       <c r="B25" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,25 +3097,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3093,13 +3125,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524121</v>
+        <v>524370</v>
       </c>
       <c r="R25" t="n">
-        <v>6845117</v>
+        <v>6845393</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,22 +3175,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124502475</v>
+        <v>124504704</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,41 +3199,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524197</v>
+        <v>524238</v>
       </c>
       <c r="R26" t="n">
-        <v>6845056</v>
+        <v>6844943</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3245,22 +3286,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124504769</v>
+        <v>124487567</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3269,50 +3310,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524231</v>
+        <v>525000</v>
       </c>
       <c r="R27" t="n">
-        <v>6844957</v>
+        <v>6845201</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,19 +3388,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124491805</v>
+        <v>124487467</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3408,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524880</v>
+        <v>524805</v>
       </c>
       <c r="R28" t="n">
-        <v>6845212</v>
+        <v>6845150</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3470,7 +3502,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124488103</v>
+        <v>124486895</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3510,13 +3542,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525146</v>
+        <v>524856</v>
       </c>
       <c r="R29" t="n">
-        <v>6845150</v>
+        <v>6845128</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3560,22 +3592,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124499838</v>
+        <v>124487374</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3584,50 +3616,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524478</v>
+        <v>524974</v>
       </c>
       <c r="R30" t="n">
-        <v>6845426</v>
+        <v>6845191</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3683,7 +3706,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124487467</v>
+        <v>124490097</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3723,13 +3746,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524805</v>
+        <v>525147</v>
       </c>
       <c r="R31" t="n">
-        <v>6845150</v>
+        <v>6845208</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,22 +3796,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124489815</v>
+        <v>124501662</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,38 +3820,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525208</v>
+        <v>524272</v>
       </c>
       <c r="R32" t="n">
-        <v>6845169</v>
+        <v>6845365</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3875,22 +3907,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124498070</v>
+        <v>124492032</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3899,41 +3931,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524353</v>
+        <v>524881</v>
       </c>
       <c r="R33" t="n">
-        <v>6845201</v>
+        <v>6845143</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3977,22 +4018,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124487771</v>
+        <v>124499832</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4001,38 +4042,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524761</v>
+        <v>524327</v>
       </c>
       <c r="R34" t="n">
-        <v>6845213</v>
+        <v>6845386</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4091,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124488326</v>
+        <v>124499475</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4103,41 +4153,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524734</v>
+        <v>524510</v>
       </c>
       <c r="R35" t="n">
-        <v>6845219</v>
+        <v>6845430</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4181,22 +4240,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124504485</v>
+        <v>124490978</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,47 +4264,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524261</v>
+        <v>525086</v>
       </c>
       <c r="R36" t="n">
-        <v>6844909</v>
+        <v>6845224</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4304,7 +4354,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124491765</v>
+        <v>124491917</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4344,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524904</v>
+        <v>524852</v>
       </c>
       <c r="R37" t="n">
-        <v>6845207</v>
+        <v>6845214</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4406,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124488923</v>
+        <v>124499713</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4422,37 +4472,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525312</v>
+        <v>524311</v>
       </c>
       <c r="R38" t="n">
-        <v>6845166</v>
+        <v>6845368</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4496,22 +4546,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124500926</v>
+        <v>124498936</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4524,21 +4574,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4548,13 +4598,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524345</v>
+        <v>524415</v>
       </c>
       <c r="R39" t="n">
-        <v>6845461</v>
+        <v>6845335</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4610,7 +4660,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124504662</v>
+        <v>124491822</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4646,17 +4696,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524244</v>
+        <v>524857</v>
       </c>
       <c r="R40" t="n">
-        <v>6844920</v>
+        <v>6845201</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4700,22 +4750,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124501563</v>
+        <v>124492717</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4728,37 +4778,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524245</v>
+        <v>524757</v>
       </c>
       <c r="R41" t="n">
-        <v>6845371</v>
+        <v>6845190</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4802,22 +4852,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124502783</v>
+        <v>124491294</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,50 +4876,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524254</v>
+        <v>525063</v>
       </c>
       <c r="R42" t="n">
-        <v>6845067</v>
+        <v>6845234</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4913,22 +4954,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124503227</v>
+        <v>124498544</v>
       </c>
       <c r="B43" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,21 +4982,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4965,13 +5006,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524472</v>
+        <v>524364</v>
       </c>
       <c r="R43" t="n">
-        <v>6845023</v>
+        <v>6845312</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5027,10 +5068,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124493108</v>
+        <v>124491619</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,21 +5084,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5067,10 +5108,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524776</v>
+        <v>524906</v>
       </c>
       <c r="R44" t="n">
-        <v>6845248</v>
+        <v>6845220</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5103,11 +5144,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5134,7 +5170,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124487293</v>
+        <v>124505389</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5169,7 +5205,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5179,17 +5215,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524948</v>
+        <v>524115</v>
       </c>
       <c r="R45" t="n">
-        <v>6845179</v>
+        <v>6845050</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5233,22 +5269,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124490097</v>
+        <v>124504485</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5257,41 +5293,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525147</v>
+        <v>524261</v>
       </c>
       <c r="R46" t="n">
-        <v>6845208</v>
+        <v>6844909</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5335,22 +5380,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124504321</v>
+        <v>124492807</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5363,34 +5408,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524276</v>
+        <v>524696</v>
       </c>
       <c r="R47" t="n">
-        <v>6844888</v>
+        <v>6845140</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5449,10 +5494,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124503276</v>
+        <v>124500965</v>
       </c>
       <c r="B48" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5465,21 +5510,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5489,13 +5534,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524472</v>
+        <v>524308</v>
       </c>
       <c r="R48" t="n">
-        <v>6845023</v>
+        <v>6845471</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5551,10 +5596,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124503388</v>
+        <v>124501516</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5563,50 +5608,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524214</v>
+        <v>524237</v>
       </c>
       <c r="R49" t="n">
-        <v>6844996</v>
+        <v>6845433</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5662,10 +5698,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124486832</v>
+        <v>124503027</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5678,34 +5714,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524856</v>
+        <v>524345</v>
       </c>
       <c r="R50" t="n">
-        <v>6845111</v>
+        <v>6845032</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5764,10 +5800,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124487039</v>
+        <v>124503227</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5776,50 +5812,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524908</v>
+        <v>524472</v>
       </c>
       <c r="R51" t="n">
-        <v>6845155</v>
+        <v>6845023</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5863,19 +5890,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124491917</v>
+        <v>124491427</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5915,13 +5942,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524852</v>
+        <v>524946</v>
       </c>
       <c r="R52" t="n">
-        <v>6845214</v>
+        <v>6845286</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5965,19 +5992,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124486895</v>
+        <v>124488923</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6017,13 +6044,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524856</v>
+        <v>525312</v>
       </c>
       <c r="R53" t="n">
-        <v>6845128</v>
+        <v>6845166</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6067,22 +6094,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124504973</v>
+        <v>124488103</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6091,50 +6118,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524210</v>
+        <v>525146</v>
       </c>
       <c r="R54" t="n">
-        <v>6844954</v>
+        <v>6845150</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6178,22 +6196,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124504354</v>
+        <v>124487121</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6202,50 +6220,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524274</v>
+        <v>524844</v>
       </c>
       <c r="R55" t="n">
-        <v>6844889</v>
+        <v>6845169</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6289,22 +6298,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124500069</v>
+        <v>124498794</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6313,47 +6322,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524370</v>
+        <v>524383</v>
       </c>
       <c r="R56" t="n">
-        <v>6845396</v>
+        <v>6845264</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6386,11 +6386,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6417,10 +6412,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124487775</v>
+        <v>124504054</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6429,41 +6424,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525079</v>
+        <v>524683</v>
       </c>
       <c r="R57" t="n">
-        <v>6845164</v>
+        <v>6844956</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6507,22 +6511,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124498165</v>
+        <v>124486832</v>
       </c>
       <c r="B58" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6535,34 +6539,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524349</v>
+        <v>524856</v>
       </c>
       <c r="R58" t="n">
-        <v>6845225</v>
+        <v>6845111</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6621,7 +6625,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124492194</v>
+        <v>124487317</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6661,10 +6665,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524798</v>
+        <v>524829</v>
       </c>
       <c r="R59" t="n">
-        <v>6845206</v>
+        <v>6845141</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6723,7 +6727,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124490965</v>
+        <v>124498466</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -6759,17 +6763,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525081</v>
+        <v>524369</v>
       </c>
       <c r="R60" t="n">
-        <v>6845283</v>
+        <v>6845293</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6813,19 +6817,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124488657</v>
+        <v>124489002</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -6865,10 +6869,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525312</v>
+        <v>525277</v>
       </c>
       <c r="R61" t="n">
-        <v>6845117</v>
+        <v>6845196</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6901,6 +6905,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6927,10 +6936,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124491619</v>
+        <v>124490527</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6943,37 +6952,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524906</v>
+        <v>525139</v>
       </c>
       <c r="R62" t="n">
-        <v>6845220</v>
+        <v>6845241</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7003,6 +7017,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7017,22 +7036,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124491300</v>
+        <v>124503276</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7045,34 +7064,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525015</v>
+        <v>524472</v>
       </c>
       <c r="R63" t="n">
-        <v>6845263</v>
+        <v>6845023</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,22 +7138,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124490555</v>
+        <v>124505582</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7147,37 +7166,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525142</v>
+        <v>524121</v>
       </c>
       <c r="R64" t="n">
-        <v>6845241</v>
+        <v>6845117</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7207,11 +7226,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7226,22 +7240,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124505389</v>
+        <v>124504250</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7250,47 +7264,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524115</v>
+        <v>524436</v>
       </c>
       <c r="R65" t="n">
-        <v>6845050</v>
+        <v>6844930</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7323,6 +7328,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7349,10 +7359,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124504089</v>
+        <v>124489983</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7361,47 +7371,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524238</v>
+        <v>525195</v>
       </c>
       <c r="R66" t="n">
-        <v>6844930</v>
+        <v>6845198</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7448,22 +7449,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124504651</v>
+        <v>124490692</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7472,50 +7473,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524234</v>
+        <v>525103</v>
       </c>
       <c r="R67" t="n">
-        <v>6844921</v>
+        <v>6845194</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7571,10 +7563,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124499480</v>
+        <v>124499127</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7583,50 +7575,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524365</v>
+        <v>524559</v>
       </c>
       <c r="R68" t="n">
-        <v>6845400</v>
+        <v>6845427</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7656,11 +7639,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7675,22 +7653,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124492072</v>
+        <v>124500926</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7699,50 +7677,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524828</v>
+        <v>524345</v>
       </c>
       <c r="R69" t="n">
-        <v>6845147</v>
+        <v>6845461</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7798,7 +7767,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124500865</v>
+        <v>124502605</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7838,10 +7807,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524350</v>
+        <v>524259</v>
       </c>
       <c r="R70" t="n">
-        <v>6845399</v>
+        <v>6845061</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7900,10 +7869,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124502605</v>
+        <v>124500069</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7912,41 +7881,50 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524259</v>
+        <v>524370</v>
       </c>
       <c r="R71" t="n">
-        <v>6845061</v>
+        <v>6845396</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7976,6 +7954,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7990,22 +7973,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124500867</v>
+        <v>124491428</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8014,41 +7997,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524343</v>
+        <v>524954</v>
       </c>
       <c r="R72" t="n">
-        <v>6845433</v>
+        <v>6845241</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8104,7 +8096,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124504151</v>
+        <v>124506146</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8137,20 +8129,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524256</v>
+        <v>524148</v>
       </c>
       <c r="R73" t="n">
-        <v>6844925</v>
+        <v>6845027</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8194,22 +8195,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124499713</v>
+        <v>124487604</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8222,34 +8223,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524311</v>
+        <v>524781</v>
       </c>
       <c r="R74" t="n">
-        <v>6845368</v>
+        <v>6845167</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8308,7 +8309,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124492513</v>
+        <v>124487283</v>
       </c>
       <c r="B75" t="n">
         <v>78810</v>
@@ -8348,13 +8349,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524774</v>
+        <v>524836</v>
       </c>
       <c r="R75" t="n">
-        <v>6845100</v>
+        <v>6845119</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8398,19 +8399,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124498466</v>
+        <v>124488326</v>
       </c>
       <c r="B76" t="n">
         <v>78810</v>
@@ -8446,14 +8447,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524369</v>
+        <v>524734</v>
       </c>
       <c r="R76" t="n">
-        <v>6845293</v>
+        <v>6845219</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8512,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124500201</v>
+        <v>124503680</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8524,47 +8525,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524390</v>
+        <v>524648</v>
       </c>
       <c r="R77" t="n">
-        <v>6845406</v>
+        <v>6845029</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8597,11 +8589,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8628,7 +8615,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124500909</v>
+        <v>124504860</v>
       </c>
       <c r="B78" t="n">
         <v>78810</v>
@@ -8668,13 +8655,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524346</v>
+        <v>524224</v>
       </c>
       <c r="R78" t="n">
-        <v>6845458</v>
+        <v>6844971</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8730,7 +8717,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124490428</v>
+        <v>124502475</v>
       </c>
       <c r="B79" t="n">
         <v>78810</v>
@@ -8766,17 +8753,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525133</v>
+        <v>524197</v>
       </c>
       <c r="R79" t="n">
-        <v>6845201</v>
+        <v>6845056</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8820,19 +8807,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124490978</v>
+        <v>124490965</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8872,13 +8859,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525086</v>
+        <v>525081</v>
       </c>
       <c r="R80" t="n">
-        <v>6845224</v>
+        <v>6845283</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8922,22 +8909,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124491294</v>
+        <v>124503002</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8950,34 +8937,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525063</v>
+        <v>524333</v>
       </c>
       <c r="R81" t="n">
-        <v>6845234</v>
+        <v>6845022</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9036,10 +9023,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124489792</v>
+        <v>124504321</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9048,50 +9035,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525215</v>
+        <v>524276</v>
       </c>
       <c r="R82" t="n">
-        <v>6845178</v>
+        <v>6844888</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9135,19 +9113,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124491246</v>
+        <v>124502522</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9183,14 +9161,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525065</v>
+        <v>524234</v>
       </c>
       <c r="R83" t="n">
-        <v>6845243</v>
+        <v>6845053</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9249,7 +9227,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124501516</v>
+        <v>124498529</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9289,13 +9267,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524237</v>
+        <v>524365</v>
       </c>
       <c r="R84" t="n">
-        <v>6845433</v>
+        <v>6845310</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9339,22 +9317,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124497941</v>
+        <v>124492635</v>
       </c>
       <c r="B85" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9367,37 +9345,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524344</v>
+        <v>524790</v>
       </c>
       <c r="R85" t="n">
-        <v>6845182</v>
+        <v>6845219</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9427,6 +9405,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9453,10 +9436,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124490527</v>
+        <v>124499895</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9465,46 +9448,50 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525139</v>
+        <v>524362</v>
       </c>
       <c r="R86" t="n">
-        <v>6845241</v>
+        <v>6845391</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9538,7 +9525,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9553,22 +9540,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124503504</v>
+        <v>124487039</v>
       </c>
       <c r="B87" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9577,41 +9564,50 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524511</v>
+        <v>524908</v>
       </c>
       <c r="R87" t="n">
-        <v>6845029</v>
+        <v>6845155</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9655,19 +9651,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124506146</v>
+        <v>124503388</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9702,7 +9698,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9716,10 +9712,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524148</v>
+        <v>524214</v>
       </c>
       <c r="R88" t="n">
-        <v>6845027</v>
+        <v>6844996</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9766,22 +9762,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124489670</v>
+        <v>124490091</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9790,50 +9786,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525247</v>
+        <v>525149</v>
       </c>
       <c r="R89" t="n">
-        <v>6845194</v>
+        <v>6845210</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9877,22 +9864,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124499475</v>
+        <v>124500112</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9901,47 +9888,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524510</v>
+        <v>524447</v>
       </c>
       <c r="R90" t="n">
-        <v>6845430</v>
+        <v>6845417</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -10000,10 +9978,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124504250</v>
+        <v>124498070</v>
       </c>
       <c r="B91" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10012,25 +9990,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10040,10 +10018,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524436</v>
+        <v>524353</v>
       </c>
       <c r="R91" t="n">
-        <v>6844930</v>
+        <v>6845201</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -10076,11 +10054,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10107,10 +10080,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124503785</v>
+        <v>124491300</v>
       </c>
       <c r="B92" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10123,37 +10096,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524244</v>
+        <v>525015</v>
       </c>
       <c r="R92" t="n">
-        <v>6845004</v>
+        <v>6845263</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10209,10 +10182,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124491531</v>
+        <v>124493358</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10225,21 +10198,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10249,13 +10222,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524919</v>
+        <v>524793</v>
       </c>
       <c r="R93" t="n">
-        <v>6845253</v>
+        <v>6845243</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10311,10 +10284,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124488157</v>
+        <v>124504945</v>
       </c>
       <c r="B94" t="n">
-        <v>78546</v>
+        <v>57666</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10327,34 +10300,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524731</v>
+        <v>524203</v>
       </c>
       <c r="R94" t="n">
-        <v>6845235</v>
+        <v>6844991</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10413,10 +10386,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124493358</v>
+        <v>124504565</v>
       </c>
       <c r="B95" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10425,38 +10398,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524793</v>
+        <v>524227</v>
       </c>
       <c r="R95" t="n">
-        <v>6845243</v>
+        <v>6844932</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10515,10 +10497,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124502522</v>
+        <v>124504651</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10527,28 +10509,37 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
@@ -10558,10 +10549,10 @@
         <v>524234</v>
       </c>
       <c r="R96" t="n">
-        <v>6845053</v>
+        <v>6844921</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10617,7 +10608,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124504545</v>
+        <v>124486962</v>
       </c>
       <c r="B97" t="n">
         <v>98101</v>
@@ -10652,7 +10643,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10662,14 +10653,14 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524237</v>
+        <v>524859</v>
       </c>
       <c r="R97" t="n">
-        <v>6844919</v>
+        <v>6845148</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10728,10 +10719,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124501577</v>
+        <v>124490720</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10740,50 +10731,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524252</v>
+        <v>525133</v>
       </c>
       <c r="R98" t="n">
-        <v>6845387</v>
+        <v>6845307</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10827,22 +10809,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124492032</v>
+        <v>124502991</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10851,50 +10833,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524881</v>
+        <v>524280</v>
       </c>
       <c r="R99" t="n">
-        <v>6845143</v>
+        <v>6845054</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10950,7 +10923,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124491548</v>
+        <v>124500909</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -10986,17 +10959,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524916</v>
+        <v>524346</v>
       </c>
       <c r="R100" t="n">
-        <v>6845244</v>
+        <v>6845458</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11052,10 +11025,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124500112</v>
+        <v>124504973</v>
       </c>
       <c r="B101" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11064,41 +11037,50 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524447</v>
+        <v>524210</v>
       </c>
       <c r="R101" t="n">
-        <v>6845417</v>
+        <v>6844954</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11142,22 +11124,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124502910</v>
+        <v>124491477</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11166,50 +11148,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524247</v>
+        <v>524920</v>
       </c>
       <c r="R102" t="n">
-        <v>6845069</v>
+        <v>6845260</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11253,22 +11226,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124501662</v>
+        <v>124498760</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11277,47 +11250,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524272</v>
+        <v>524388</v>
       </c>
       <c r="R103" t="n">
-        <v>6845365</v>
+        <v>6845283</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11364,19 +11328,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124504704</v>
+        <v>124504769</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11411,7 +11375,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11425,10 +11389,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524238</v>
+        <v>524231</v>
       </c>
       <c r="R104" t="n">
-        <v>6844943</v>
+        <v>6844957</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11487,10 +11451,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124498760</v>
+        <v>124504916</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11499,38 +11463,47 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524388</v>
+        <v>524219</v>
       </c>
       <c r="R105" t="n">
-        <v>6845283</v>
+        <v>6844970</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11589,7 +11562,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124489983</v>
+        <v>124500867</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11625,17 +11598,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>525195</v>
+        <v>524343</v>
       </c>
       <c r="R106" t="n">
-        <v>6845198</v>
+        <v>6845433</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11691,10 +11664,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124503002</v>
+        <v>124491765</v>
       </c>
       <c r="B107" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11707,34 +11680,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524333</v>
+        <v>524904</v>
       </c>
       <c r="R107" t="n">
-        <v>6845022</v>
+        <v>6845207</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11793,7 +11766,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124503680</v>
+        <v>124487775</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11829,17 +11802,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524648</v>
+        <v>525079</v>
       </c>
       <c r="R108" t="n">
-        <v>6845029</v>
+        <v>6845164</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11883,19 +11856,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124489866</v>
+        <v>124492194</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -11935,13 +11908,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>525217</v>
+        <v>524798</v>
       </c>
       <c r="R109" t="n">
-        <v>6845195</v>
+        <v>6845206</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11985,19 +11958,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124487121</v>
+        <v>124489815</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -12037,7 +12010,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524844</v>
+        <v>525208</v>
       </c>
       <c r="R110" t="n">
         <v>6845169</v>
@@ -12099,7 +12072,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124487374</v>
+        <v>124487689</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -12139,13 +12112,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524974</v>
+        <v>524780</v>
       </c>
       <c r="R111" t="n">
-        <v>6845191</v>
+        <v>6845188</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12189,22 +12162,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124492000</v>
+        <v>124499838</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12213,41 +12186,50 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524901</v>
+        <v>524478</v>
       </c>
       <c r="R112" t="n">
-        <v>6845216</v>
+        <v>6845426</v>
       </c>
       <c r="S112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12291,22 +12273,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124499895</v>
+        <v>124490165</v>
       </c>
       <c r="B113" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12315,47 +12297,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524362</v>
+        <v>525151</v>
       </c>
       <c r="R113" t="n">
-        <v>6845391</v>
+        <v>6845190</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12388,11 +12361,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12419,10 +12387,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124486962</v>
+        <v>124488535</v>
       </c>
       <c r="B114" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12431,50 +12399,41 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524859</v>
+        <v>525311</v>
       </c>
       <c r="R114" t="n">
-        <v>6845148</v>
+        <v>6845039</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12518,22 +12477,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124487567</v>
+        <v>124504662</v>
       </c>
       <c r="B115" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12546,37 +12505,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>525000</v>
+        <v>524244</v>
       </c>
       <c r="R115" t="n">
-        <v>6845201</v>
+        <v>6844920</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12620,22 +12579,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124504916</v>
+        <v>124488657</v>
       </c>
       <c r="B116" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12644,50 +12603,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524219</v>
+        <v>525312</v>
       </c>
       <c r="R116" t="n">
-        <v>6844970</v>
+        <v>6845117</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12731,19 +12681,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124491477</v>
+        <v>124486839</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -12783,13 +12733,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524920</v>
+        <v>524872</v>
       </c>
       <c r="R117" t="n">
-        <v>6845260</v>
+        <v>6845107</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12833,19 +12783,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124504513</v>
+        <v>124504545</v>
       </c>
       <c r="B118" t="n">
         <v>98101</v>
@@ -12894,10 +12844,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524245</v>
+        <v>524237</v>
       </c>
       <c r="R118" t="n">
-        <v>6844924</v>
+        <v>6844919</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12956,10 +12906,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124487283</v>
+        <v>124501577</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12968,38 +12918,47 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524836</v>
+        <v>524252</v>
       </c>
       <c r="R119" t="n">
-        <v>6845119</v>
+        <v>6845387</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13058,10 +13017,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124487604</v>
+        <v>124487293</v>
       </c>
       <c r="B120" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13070,41 +13029,50 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524781</v>
+        <v>524948</v>
       </c>
       <c r="R120" t="n">
-        <v>6845167</v>
+        <v>6845179</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13148,19 +13116,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124491427</v>
+        <v>124487771</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13200,13 +13168,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524946</v>
+        <v>524761</v>
       </c>
       <c r="R121" t="n">
-        <v>6845286</v>
+        <v>6845213</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13250,22 +13218,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124498544</v>
+        <v>124504513</v>
       </c>
       <c r="B122" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13274,38 +13242,47 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524364</v>
+        <v>524245</v>
       </c>
       <c r="R122" t="n">
-        <v>6845312</v>
+        <v>6844924</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13364,10 +13341,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124488535</v>
+        <v>124492072</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13376,41 +13353,50 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>525311</v>
+        <v>524828</v>
       </c>
       <c r="R123" t="n">
-        <v>6845039</v>
+        <v>6845147</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13454,19 +13440,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124487689</v>
+        <v>124491387</v>
       </c>
       <c r="B124" t="n">
         <v>78810</v>
@@ -13506,10 +13492,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524780</v>
+        <v>524949</v>
       </c>
       <c r="R124" t="n">
-        <v>6845188</v>
+        <v>6845252</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13568,7 +13554,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124499873</v>
+        <v>124492513</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -13604,14 +13590,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524451</v>
+        <v>524774</v>
       </c>
       <c r="R125" t="n">
-        <v>6845435</v>
+        <v>6845100</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13670,10 +13656,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124504054</v>
+        <v>124491320</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13682,47 +13668,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524683</v>
+        <v>525017</v>
       </c>
       <c r="R126" t="n">
-        <v>6844956</v>
+        <v>6845257</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13769,22 +13746,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124493648</v>
+        <v>124489748</v>
       </c>
       <c r="B127" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13793,35 +13770,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13830,13 +13807,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524762</v>
+        <v>525230</v>
       </c>
       <c r="R127" t="n">
-        <v>6845231</v>
+        <v>6845187</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13880,22 +13857,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124490692</v>
+        <v>124499480</v>
       </c>
       <c r="B128" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13904,38 +13881,47 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>525103</v>
+        <v>524365</v>
       </c>
       <c r="R128" t="n">
-        <v>6845194</v>
+        <v>6845400</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13968,6 +13954,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13994,7 +13985,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124487564</v>
+        <v>124487514</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14034,13 +14025,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524773</v>
+        <v>525016</v>
       </c>
       <c r="R129" t="n">
-        <v>6845141</v>
+        <v>6845190</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14084,22 +14075,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124490165</v>
+        <v>124501563</v>
       </c>
       <c r="B130" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14112,37 +14103,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>525151</v>
+        <v>524245</v>
       </c>
       <c r="R130" t="n">
-        <v>6845190</v>
+        <v>6845371</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14186,22 +14177,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124489748</v>
+        <v>124491805</v>
       </c>
       <c r="B131" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14210,47 +14201,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>525230</v>
+        <v>524880</v>
       </c>
       <c r="R131" t="n">
-        <v>6845187</v>
+        <v>6845212</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14309,10 +14291,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124492635</v>
+        <v>124501831</v>
       </c>
       <c r="B132" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14325,37 +14307,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524790</v>
+        <v>524268</v>
       </c>
       <c r="R132" t="n">
-        <v>6845219</v>
+        <v>6845351</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14385,11 +14367,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14404,22 +14381,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124504945</v>
+        <v>124489792</v>
       </c>
       <c r="B133" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14428,38 +14405,47 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524203</v>
+        <v>525215</v>
       </c>
       <c r="R133" t="n">
-        <v>6844991</v>
+        <v>6845178</v>
       </c>
       <c r="S133" t="n">
         <v>20</v>
@@ -14518,7 +14504,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124504565</v>
+        <v>124504151</v>
       </c>
       <c r="B134" t="n">
         <v>98101</v>
@@ -14551,29 +14537,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524227</v>
+        <v>524256</v>
       </c>
       <c r="R134" t="n">
-        <v>6844932</v>
+        <v>6844925</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14617,22 +14594,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124491822</v>
+        <v>124504089</v>
       </c>
       <c r="B135" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14641,38 +14618,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524857</v>
+        <v>524238</v>
       </c>
       <c r="R135" t="n">
-        <v>6845201</v>
+        <v>6844930</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -14731,10 +14717,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124503027</v>
+        <v>124500201</v>
       </c>
       <c r="B136" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14743,38 +14729,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524345</v>
+        <v>524390</v>
       </c>
       <c r="R136" t="n">
-        <v>6845032</v>
+        <v>6845406</v>
       </c>
       <c r="S136" t="n">
         <v>20</v>
@@ -14807,6 +14802,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124500865</v>
+        <v>124498165</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524350</v>
+        <v>524349</v>
       </c>
       <c r="R2" t="n">
-        <v>6845399</v>
+        <v>6845225</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124493108</v>
+        <v>124491246</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524776</v>
+        <v>525065</v>
       </c>
       <c r="R3" t="n">
-        <v>6845248</v>
+        <v>6845243</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124498165</v>
+        <v>124500865</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524349</v>
+        <v>524350</v>
       </c>
       <c r="R5" t="n">
-        <v>6845225</v>
+        <v>6845399</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124491246</v>
+        <v>124493108</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525065</v>
+        <v>524776</v>
       </c>
       <c r="R6" t="n">
-        <v>6845243</v>
+        <v>6845248</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124487467</v>
+        <v>124501662</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3412,38 +3412,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524805</v>
+        <v>524272</v>
       </c>
       <c r="R28" t="n">
-        <v>6845150</v>
+        <v>6845365</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3490,19 +3499,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124486895</v>
+        <v>124487467</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3542,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524856</v>
+        <v>524805</v>
       </c>
       <c r="R29" t="n">
-        <v>6845128</v>
+        <v>6845150</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3604,7 +3613,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124487374</v>
+        <v>124486895</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3644,13 +3653,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524974</v>
+        <v>524856</v>
       </c>
       <c r="R30" t="n">
-        <v>6845191</v>
+        <v>6845128</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3694,19 +3703,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124490097</v>
+        <v>124487374</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3746,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525147</v>
+        <v>524974</v>
       </c>
       <c r="R31" t="n">
-        <v>6845208</v>
+        <v>6845191</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3808,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124501662</v>
+        <v>124490097</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3820,50 +3829,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524272</v>
+        <v>525147</v>
       </c>
       <c r="R32" t="n">
-        <v>6845365</v>
+        <v>6845208</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124489983</v>
+        <v>124500069</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7371,38 +7371,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525195</v>
+        <v>524370</v>
       </c>
       <c r="R66" t="n">
-        <v>6845198</v>
+        <v>6845396</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7435,6 +7444,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7461,10 +7475,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124490692</v>
+        <v>124489983</v>
       </c>
       <c r="B67" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7473,25 +7487,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7501,10 +7515,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525103</v>
+        <v>525195</v>
       </c>
       <c r="R67" t="n">
-        <v>6845194</v>
+        <v>6845198</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7563,10 +7577,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124499127</v>
+        <v>124490692</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7575,41 +7589,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524559</v>
+        <v>525103</v>
       </c>
       <c r="R68" t="n">
-        <v>6845427</v>
+        <v>6845194</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7653,22 +7667,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124500926</v>
+        <v>124499127</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7681,21 +7695,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7705,13 +7719,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524345</v>
+        <v>524559</v>
       </c>
       <c r="R69" t="n">
-        <v>6845461</v>
+        <v>6845427</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7755,22 +7769,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124502605</v>
+        <v>124500926</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7783,21 +7797,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7807,13 +7821,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524259</v>
+        <v>524345</v>
       </c>
       <c r="R70" t="n">
-        <v>6845061</v>
+        <v>6845461</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7857,22 +7871,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124500069</v>
+        <v>124502605</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7881,50 +7895,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524370</v>
+        <v>524259</v>
       </c>
       <c r="R71" t="n">
-        <v>6845396</v>
+        <v>6845061</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7954,11 +7959,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7973,22 +7973,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124491428</v>
+        <v>124487604</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7997,47 +7997,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524954</v>
+        <v>524781</v>
       </c>
       <c r="R72" t="n">
-        <v>6845241</v>
+        <v>6845167</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8096,10 +8087,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124506146</v>
+        <v>124488326</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8108,47 +8099,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524148</v>
+        <v>524734</v>
       </c>
       <c r="R73" t="n">
-        <v>6845027</v>
+        <v>6845219</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8207,7 +8189,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124487604</v>
+        <v>124487283</v>
       </c>
       <c r="B74" t="n">
         <v>78810</v>
@@ -8247,10 +8229,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524781</v>
+        <v>524836</v>
       </c>
       <c r="R74" t="n">
-        <v>6845167</v>
+        <v>6845119</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8309,7 +8291,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124487283</v>
+        <v>124503680</v>
       </c>
       <c r="B75" t="n">
         <v>78810</v>
@@ -8345,14 +8327,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524836</v>
+        <v>524648</v>
       </c>
       <c r="R75" t="n">
-        <v>6845119</v>
+        <v>6845029</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8411,7 +8393,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124488326</v>
+        <v>124504860</v>
       </c>
       <c r="B76" t="n">
         <v>78810</v>
@@ -8447,14 +8429,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524734</v>
+        <v>524224</v>
       </c>
       <c r="R76" t="n">
-        <v>6845219</v>
+        <v>6844971</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8513,7 +8495,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124503680</v>
+        <v>124502475</v>
       </c>
       <c r="B77" t="n">
         <v>78810</v>
@@ -8553,13 +8535,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524648</v>
+        <v>524197</v>
       </c>
       <c r="R77" t="n">
-        <v>6845029</v>
+        <v>6845056</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8603,22 +8585,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124504860</v>
+        <v>124506146</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8627,38 +8609,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524224</v>
+        <v>524148</v>
       </c>
       <c r="R78" t="n">
-        <v>6844971</v>
+        <v>6845027</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8717,10 +8708,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124502475</v>
+        <v>124491428</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8729,41 +8720,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524197</v>
+        <v>524954</v>
       </c>
       <c r="R79" t="n">
-        <v>6845056</v>
+        <v>6845241</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8807,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124490965</v>
+        <v>124503388</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8831,41 +8831,50 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525081</v>
+        <v>524214</v>
       </c>
       <c r="R80" t="n">
-        <v>6845283</v>
+        <v>6844996</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8921,10 +8930,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124503002</v>
+        <v>124499895</v>
       </c>
       <c r="B81" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8933,38 +8942,47 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524333</v>
+        <v>524362</v>
       </c>
       <c r="R81" t="n">
-        <v>6845022</v>
+        <v>6845391</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8997,6 +9015,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9023,10 +9046,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124504321</v>
+        <v>124487039</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9035,38 +9058,47 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524276</v>
+        <v>524908</v>
       </c>
       <c r="R82" t="n">
-        <v>6844888</v>
+        <v>6845155</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9125,7 +9157,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124502522</v>
+        <v>124498529</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9165,10 +9197,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524234</v>
+        <v>524365</v>
       </c>
       <c r="R83" t="n">
-        <v>6845053</v>
+        <v>6845310</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9227,7 +9259,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124498529</v>
+        <v>124490965</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9263,17 +9295,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524365</v>
+        <v>525081</v>
       </c>
       <c r="R84" t="n">
-        <v>6845310</v>
+        <v>6845283</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9317,22 +9349,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124492635</v>
+        <v>124503002</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>78546</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9345,34 +9377,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524790</v>
+        <v>524333</v>
       </c>
       <c r="R85" t="n">
-        <v>6845219</v>
+        <v>6845022</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9405,11 +9437,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9436,10 +9463,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124499895</v>
+        <v>124504321</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9448,50 +9475,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524362</v>
+        <v>524276</v>
       </c>
       <c r="R86" t="n">
-        <v>6845391</v>
+        <v>6844888</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9521,11 +9539,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9540,22 +9553,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124487039</v>
+        <v>124502522</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9564,50 +9577,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524908</v>
+        <v>524234</v>
       </c>
       <c r="R87" t="n">
-        <v>6845155</v>
+        <v>6845053</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9651,22 +9655,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124503388</v>
+        <v>124492635</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9675,47 +9679,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524214</v>
+        <v>524790</v>
       </c>
       <c r="R88" t="n">
-        <v>6844996</v>
+        <v>6845219</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9750,6 +9745,11 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9762,12 +9762,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -12591,7 +12591,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124488657</v>
+        <v>124487771</v>
       </c>
       <c r="B116" t="n">
         <v>78810</v>
@@ -12631,13 +12631,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>525312</v>
+        <v>524761</v>
       </c>
       <c r="R116" t="n">
-        <v>6845117</v>
+        <v>6845213</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12681,22 +12681,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124486839</v>
+        <v>124504545</v>
       </c>
       <c r="B117" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12705,41 +12705,50 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524872</v>
+        <v>524237</v>
       </c>
       <c r="R117" t="n">
-        <v>6845107</v>
+        <v>6844919</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12783,19 +12792,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124504545</v>
+        <v>124501577</v>
       </c>
       <c r="B118" t="n">
         <v>98101</v>
@@ -12830,7 +12839,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -12844,10 +12853,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524237</v>
+        <v>524252</v>
       </c>
       <c r="R118" t="n">
-        <v>6844919</v>
+        <v>6845387</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12906,7 +12915,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124501577</v>
+        <v>124487293</v>
       </c>
       <c r="B119" t="n">
         <v>98101</v>
@@ -12941,7 +12950,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12951,17 +12960,17 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524252</v>
+        <v>524948</v>
       </c>
       <c r="R119" t="n">
-        <v>6845387</v>
+        <v>6845179</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13005,22 +13014,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124487293</v>
+        <v>124488657</v>
       </c>
       <c r="B120" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13029,47 +13038,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524948</v>
+        <v>525312</v>
       </c>
       <c r="R120" t="n">
-        <v>6845179</v>
+        <v>6845117</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124487771</v>
+        <v>124486839</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13168,13 +13168,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524761</v>
+        <v>524872</v>
       </c>
       <c r="R121" t="n">
-        <v>6845213</v>
+        <v>6845107</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13218,22 +13218,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124504513</v>
+        <v>124491387</v>
       </c>
       <c r="B122" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13242,47 +13242,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524245</v>
+        <v>524949</v>
       </c>
       <c r="R122" t="n">
-        <v>6844924</v>
+        <v>6845252</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13341,10 +13332,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124492072</v>
+        <v>124492513</v>
       </c>
       <c r="B123" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13353,50 +13344,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524828</v>
+        <v>524774</v>
       </c>
       <c r="R123" t="n">
-        <v>6845147</v>
+        <v>6845100</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13440,22 +13422,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124491387</v>
+        <v>124504513</v>
       </c>
       <c r="B124" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13464,38 +13446,47 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524949</v>
+        <v>524245</v>
       </c>
       <c r="R124" t="n">
-        <v>6845252</v>
+        <v>6844924</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13554,10 +13545,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124492513</v>
+        <v>124492072</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13566,41 +13557,50 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524774</v>
+        <v>524828</v>
       </c>
       <c r="R125" t="n">
-        <v>6845100</v>
+        <v>6845147</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13644,12 +13644,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13985,7 +13985,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124487514</v>
+        <v>124491805</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14025,13 +14025,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>525016</v>
+        <v>524880</v>
       </c>
       <c r="R129" t="n">
-        <v>6845190</v>
+        <v>6845212</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14075,22 +14075,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124501563</v>
+        <v>124501831</v>
       </c>
       <c r="B130" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14103,21 +14103,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524245</v>
+        <v>524268</v>
       </c>
       <c r="R130" t="n">
-        <v>6845371</v>
+        <v>6845351</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14189,10 +14189,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124491805</v>
+        <v>124504151</v>
       </c>
       <c r="B131" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14201,41 +14201,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524880</v>
+        <v>524256</v>
       </c>
       <c r="R131" t="n">
-        <v>6845212</v>
+        <v>6844925</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14279,22 +14279,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124501831</v>
+        <v>124504089</v>
       </c>
       <c r="B132" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14303,41 +14303,50 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524268</v>
+        <v>524238</v>
       </c>
       <c r="R132" t="n">
-        <v>6845351</v>
+        <v>6844930</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14393,7 +14402,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124489792</v>
+        <v>124500201</v>
       </c>
       <c r="B133" t="n">
         <v>98101</v>
@@ -14428,7 +14437,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14438,14 +14447,14 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>525215</v>
+        <v>524390</v>
       </c>
       <c r="R133" t="n">
-        <v>6845178</v>
+        <v>6845406</v>
       </c>
       <c r="S133" t="n">
         <v>20</v>
@@ -14478,6 +14487,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14504,10 +14518,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124504151</v>
+        <v>124487514</v>
       </c>
       <c r="B134" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14516,38 +14530,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524256</v>
+        <v>525016</v>
       </c>
       <c r="R134" t="n">
-        <v>6844925</v>
+        <v>6845190</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14606,10 +14620,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124504089</v>
+        <v>124501563</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14618,50 +14632,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524238</v>
+        <v>524245</v>
       </c>
       <c r="R135" t="n">
-        <v>6844930</v>
+        <v>6845371</v>
       </c>
       <c r="S135" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14717,7 +14722,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124500201</v>
+        <v>124489792</v>
       </c>
       <c r="B136" t="n">
         <v>98101</v>
@@ -14752,7 +14757,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -14762,14 +14767,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524390</v>
+        <v>525215</v>
       </c>
       <c r="R136" t="n">
-        <v>6845406</v>
+        <v>6845178</v>
       </c>
       <c r="S136" t="n">
         <v>20</v>
@@ -14802,11 +14807,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124498165</v>
+        <v>124491320</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524349</v>
+        <v>525017</v>
       </c>
       <c r="R2" t="n">
-        <v>6845225</v>
+        <v>6845257</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124491246</v>
+        <v>124505389</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525065</v>
+        <v>524115</v>
       </c>
       <c r="R3" t="n">
-        <v>6845243</v>
+        <v>6845050</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124497941</v>
+        <v>124491427</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524344</v>
+        <v>524946</v>
       </c>
       <c r="R4" t="n">
-        <v>6845182</v>
+        <v>6845286</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124500865</v>
+        <v>124488103</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1017,17 +1026,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524350</v>
+        <v>525146</v>
       </c>
       <c r="R5" t="n">
-        <v>6845399</v>
+        <v>6845150</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124493108</v>
+        <v>124490555</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524776</v>
+        <v>525142</v>
       </c>
       <c r="R6" t="n">
-        <v>6845248</v>
+        <v>6845241</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1172,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124502910</v>
+        <v>124491387</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,50 +1211,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524247</v>
+        <v>524949</v>
       </c>
       <c r="R7" t="n">
-        <v>6845069</v>
+        <v>6845252</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,22 +1289,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124503504</v>
+        <v>124491619</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,34 +1317,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524511</v>
+        <v>524906</v>
       </c>
       <c r="R8" t="n">
-        <v>6845029</v>
+        <v>6845220</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124489866</v>
+        <v>124492807</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525217</v>
+        <v>524696</v>
       </c>
       <c r="R9" t="n">
-        <v>6845195</v>
+        <v>6845140</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124493648</v>
+        <v>124504151</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,47 +1517,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524762</v>
+        <v>524256</v>
       </c>
       <c r="R10" t="n">
-        <v>6845231</v>
+        <v>6844925</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1616,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124492000</v>
+        <v>124504565</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,38 +1619,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524901</v>
+        <v>524227</v>
       </c>
       <c r="R11" t="n">
-        <v>6845216</v>
+        <v>6844932</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124491548</v>
+        <v>124506146</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,38 +1730,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524916</v>
+        <v>524148</v>
       </c>
       <c r="R12" t="n">
-        <v>6845244</v>
+        <v>6845027</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1820,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124490555</v>
+        <v>124503027</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,37 +1845,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525142</v>
+        <v>524345</v>
       </c>
       <c r="R13" t="n">
-        <v>6845241</v>
+        <v>6845032</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1896,11 +1905,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,22 +1919,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124487564</v>
+        <v>124503276</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,37 +1947,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524773</v>
+        <v>524472</v>
       </c>
       <c r="R14" t="n">
-        <v>6845141</v>
+        <v>6845023</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124488157</v>
+        <v>124487514</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,21 +2049,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,13 +2073,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524731</v>
+        <v>525016</v>
       </c>
       <c r="R15" t="n">
-        <v>6845235</v>
+        <v>6845190</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,19 +2123,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124491531</v>
+        <v>124499873</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2167,17 +2171,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524919</v>
+        <v>524451</v>
       </c>
       <c r="R16" t="n">
-        <v>6845253</v>
+        <v>6845435</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2221,22 +2225,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124503785</v>
+        <v>124501516</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,13 +2277,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524244</v>
+        <v>524237</v>
       </c>
       <c r="R17" t="n">
-        <v>6845004</v>
+        <v>6845433</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2335,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124504354</v>
+        <v>124488923</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,50 +2351,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524274</v>
+        <v>525312</v>
       </c>
       <c r="R18" t="n">
-        <v>6844889</v>
+        <v>6845166</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124502783</v>
+        <v>124487283</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,50 +2453,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524254</v>
+        <v>524836</v>
       </c>
       <c r="R19" t="n">
-        <v>6845067</v>
+        <v>6845119</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2545,22 +2531,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124489670</v>
+        <v>124490091</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,50 +2555,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525247</v>
+        <v>525149</v>
       </c>
       <c r="R20" t="n">
-        <v>6845194</v>
+        <v>6845210</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2656,22 +2633,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124501039</v>
+        <v>124498529</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,50 +2657,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524281</v>
+        <v>524365</v>
       </c>
       <c r="R21" t="n">
-        <v>6845383</v>
+        <v>6845310</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2767,22 +2735,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124490428</v>
+        <v>124504945</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2795,34 +2763,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525133</v>
+        <v>524203</v>
       </c>
       <c r="R22" t="n">
-        <v>6845201</v>
+        <v>6844991</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2881,7 +2849,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124499873</v>
+        <v>124487467</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2917,17 +2885,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524451</v>
+        <v>524805</v>
       </c>
       <c r="R23" t="n">
-        <v>6845435</v>
+        <v>6845150</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,22 +2939,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124501719</v>
+        <v>124488326</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,37 +2967,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524232</v>
+        <v>524734</v>
       </c>
       <c r="R24" t="n">
-        <v>6845349</v>
+        <v>6845219</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,22 +3041,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124500794</v>
+        <v>124499127</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,25 +3065,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3125,10 +3093,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524370</v>
+        <v>524559</v>
       </c>
       <c r="R25" t="n">
-        <v>6845393</v>
+        <v>6845427</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3187,7 +3155,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124504704</v>
+        <v>124487039</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3222,7 +3190,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3232,17 +3200,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524238</v>
+        <v>524908</v>
       </c>
       <c r="R26" t="n">
-        <v>6844943</v>
+        <v>6845155</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3286,22 +3254,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124487567</v>
+        <v>124503388</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3310,41 +3278,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525000</v>
+        <v>524214</v>
       </c>
       <c r="R27" t="n">
-        <v>6845201</v>
+        <v>6844996</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3400,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124501662</v>
+        <v>124490720</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3412,50 +3389,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524272</v>
+        <v>525133</v>
       </c>
       <c r="R28" t="n">
-        <v>6845365</v>
+        <v>6845307</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3511,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124487467</v>
+        <v>124488157</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,21 +3495,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3551,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524805</v>
+        <v>524731</v>
       </c>
       <c r="R29" t="n">
-        <v>6845150</v>
+        <v>6845235</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3613,7 +3581,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124486895</v>
+        <v>124491917</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3653,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524856</v>
+        <v>524852</v>
       </c>
       <c r="R30" t="n">
-        <v>6845128</v>
+        <v>6845214</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3715,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124487374</v>
+        <v>124500112</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3731,34 +3699,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524974</v>
+        <v>524447</v>
       </c>
       <c r="R31" t="n">
-        <v>6845191</v>
+        <v>6845417</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,7 +3785,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124490097</v>
+        <v>124502991</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3853,17 +3821,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525147</v>
+        <v>524280</v>
       </c>
       <c r="R32" t="n">
-        <v>6845208</v>
+        <v>6845054</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3919,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124492032</v>
+        <v>124492635</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3931,50 +3899,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524881</v>
+        <v>524790</v>
       </c>
       <c r="R33" t="n">
-        <v>6845143</v>
+        <v>6845219</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4004,6 +3963,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4018,19 +3982,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124499832</v>
+        <v>124486962</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4065,7 +4029,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4075,14 +4039,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524327</v>
+        <v>524859</v>
       </c>
       <c r="R34" t="n">
-        <v>6845386</v>
+        <v>6845148</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4141,7 +4105,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124499475</v>
+        <v>124489792</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4176,7 +4140,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4186,17 +4150,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524510</v>
+        <v>525215</v>
       </c>
       <c r="R35" t="n">
-        <v>6845430</v>
+        <v>6845178</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4240,22 +4204,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124490978</v>
+        <v>124504545</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,38 +4228,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525086</v>
+        <v>524237</v>
       </c>
       <c r="R36" t="n">
-        <v>6845224</v>
+        <v>6844919</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4354,10 +4327,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124491917</v>
+        <v>124500201</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,38 +4339,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524852</v>
+        <v>524390</v>
       </c>
       <c r="R37" t="n">
-        <v>6845214</v>
+        <v>6845406</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4430,6 +4412,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4456,10 +4443,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124499713</v>
+        <v>124490428</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,34 +4459,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524311</v>
+        <v>525133</v>
       </c>
       <c r="R38" t="n">
-        <v>6845368</v>
+        <v>6845201</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4558,10 +4545,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124498936</v>
+        <v>124499475</v>
       </c>
       <c r="B39" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,41 +4557,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524415</v>
+        <v>524510</v>
       </c>
       <c r="R39" t="n">
-        <v>6845335</v>
+        <v>6845430</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4648,22 +4644,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124491822</v>
+        <v>124492072</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4672,38 +4668,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524857</v>
+        <v>524828</v>
       </c>
       <c r="R40" t="n">
-        <v>6845201</v>
+        <v>6845147</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4750,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124492717</v>
+        <v>124493108</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4778,21 +4783,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4802,10 +4807,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524757</v>
+        <v>524776</v>
       </c>
       <c r="R41" t="n">
-        <v>6845190</v>
+        <v>6845248</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4838,6 +4843,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4864,10 +4874,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124491294</v>
+        <v>124501039</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4876,41 +4886,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525063</v>
+        <v>524281</v>
       </c>
       <c r="R42" t="n">
-        <v>6845234</v>
+        <v>6845383</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,22 +4973,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124498544</v>
+        <v>124492194</v>
       </c>
       <c r="B43" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4982,34 +5001,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524364</v>
+        <v>524798</v>
       </c>
       <c r="R43" t="n">
-        <v>6845312</v>
+        <v>6845206</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5068,10 +5087,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124491619</v>
+        <v>124497941</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5084,37 +5103,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524906</v>
+        <v>524344</v>
       </c>
       <c r="R44" t="n">
-        <v>6845220</v>
+        <v>6845182</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5170,10 +5189,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124505389</v>
+        <v>124501831</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5182,50 +5201,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524115</v>
+        <v>524268</v>
       </c>
       <c r="R45" t="n">
-        <v>6845050</v>
+        <v>6845351</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5269,22 +5279,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124504485</v>
+        <v>124487689</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,47 +5303,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524261</v>
+        <v>524780</v>
       </c>
       <c r="R46" t="n">
-        <v>6844909</v>
+        <v>6845188</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5392,10 +5393,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124492807</v>
+        <v>124498466</v>
       </c>
       <c r="B47" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5408,37 +5409,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524696</v>
+        <v>524369</v>
       </c>
       <c r="R47" t="n">
-        <v>6845140</v>
+        <v>6845293</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5482,22 +5483,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124500965</v>
+        <v>124501563</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5510,21 +5511,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5534,13 +5535,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524308</v>
+        <v>524245</v>
       </c>
       <c r="R48" t="n">
-        <v>6845471</v>
+        <v>6845371</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5584,19 +5585,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124501516</v>
+        <v>124502605</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5636,10 +5637,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524237</v>
+        <v>524259</v>
       </c>
       <c r="R49" t="n">
-        <v>6845433</v>
+        <v>6845061</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5698,10 +5699,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124503027</v>
+        <v>124502910</v>
       </c>
       <c r="B50" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,41 +5711,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524345</v>
+        <v>524247</v>
       </c>
       <c r="R50" t="n">
-        <v>6845032</v>
+        <v>6845069</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5788,22 +5798,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124503227</v>
+        <v>124504704</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5812,41 +5822,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524472</v>
+        <v>524238</v>
       </c>
       <c r="R51" t="n">
-        <v>6845023</v>
+        <v>6844943</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5902,7 +5921,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124491427</v>
+        <v>124500909</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5938,17 +5957,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524946</v>
+        <v>524346</v>
       </c>
       <c r="R52" t="n">
-        <v>6845286</v>
+        <v>6845458</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5992,19 +6011,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124488923</v>
+        <v>124489866</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6044,13 +6063,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525312</v>
+        <v>525217</v>
       </c>
       <c r="R53" t="n">
-        <v>6845166</v>
+        <v>6845195</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6106,7 +6125,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124488103</v>
+        <v>124498070</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6142,17 +6161,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525146</v>
+        <v>524353</v>
       </c>
       <c r="R54" t="n">
-        <v>6845150</v>
+        <v>6845201</v>
       </c>
       <c r="S54" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6196,19 +6215,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124487121</v>
+        <v>124487775</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6248,13 +6267,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524844</v>
+        <v>525079</v>
       </c>
       <c r="R55" t="n">
-        <v>6845169</v>
+        <v>6845164</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6298,19 +6317,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124498794</v>
+        <v>124493648</v>
       </c>
       <c r="B56" t="n">
         <v>92293</v>
@@ -6343,20 +6362,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524383</v>
+        <v>524762</v>
       </c>
       <c r="R56" t="n">
-        <v>6845264</v>
+        <v>6845231</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6400,22 +6428,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124504054</v>
+        <v>124489983</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6424,47 +6452,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524683</v>
+        <v>525195</v>
       </c>
       <c r="R57" t="n">
-        <v>6844956</v>
+        <v>6845198</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6523,10 +6542,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124486832</v>
+        <v>124505582</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6539,37 +6558,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524856</v>
+        <v>524121</v>
       </c>
       <c r="R58" t="n">
-        <v>6845111</v>
+        <v>6845117</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6625,10 +6644,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124487317</v>
+        <v>124487293</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6637,41 +6656,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524829</v>
+        <v>524948</v>
       </c>
       <c r="R59" t="n">
-        <v>6845141</v>
+        <v>6845179</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6715,22 +6743,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124498466</v>
+        <v>124502783</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6739,41 +6767,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524369</v>
+        <v>524254</v>
       </c>
       <c r="R60" t="n">
-        <v>6845293</v>
+        <v>6845067</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6817,22 +6854,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124489002</v>
+        <v>124493358</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6845,21 +6882,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6869,13 +6906,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525277</v>
+        <v>524793</v>
       </c>
       <c r="R61" t="n">
-        <v>6845196</v>
+        <v>6845243</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6905,11 +6942,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6924,22 +6956,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124490527</v>
+        <v>124491805</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6952,42 +6984,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525139</v>
+        <v>524880</v>
       </c>
       <c r="R62" t="n">
-        <v>6845241</v>
+        <v>6845212</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7017,11 +7044,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7036,22 +7058,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124503276</v>
+        <v>124500926</v>
       </c>
       <c r="B63" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7064,21 +7086,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7088,10 +7110,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524472</v>
+        <v>524345</v>
       </c>
       <c r="R63" t="n">
-        <v>6845023</v>
+        <v>6845461</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7150,10 +7172,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124505582</v>
+        <v>124489815</v>
       </c>
       <c r="B64" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7166,37 +7188,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524121</v>
+        <v>525208</v>
       </c>
       <c r="R64" t="n">
-        <v>6845117</v>
+        <v>6845169</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7252,10 +7274,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124504250</v>
+        <v>124491822</v>
       </c>
       <c r="B65" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7264,38 +7286,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524436</v>
+        <v>524857</v>
       </c>
       <c r="R65" t="n">
-        <v>6844930</v>
+        <v>6845201</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7330,11 +7352,6 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7347,22 +7364,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124500069</v>
+        <v>124500965</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7371,47 +7388,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524370</v>
+        <v>524308</v>
       </c>
       <c r="R66" t="n">
-        <v>6845396</v>
+        <v>6845471</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7444,11 +7452,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7475,10 +7478,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124489983</v>
+        <v>124492032</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7487,41 +7490,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525195</v>
+        <v>524881</v>
       </c>
       <c r="R67" t="n">
-        <v>6845198</v>
+        <v>6845143</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7565,22 +7577,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124490692</v>
+        <v>124499838</v>
       </c>
       <c r="B68" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7589,41 +7601,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525103</v>
+        <v>524478</v>
       </c>
       <c r="R68" t="n">
-        <v>6845194</v>
+        <v>6845426</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7667,19 +7688,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124499127</v>
+        <v>124492513</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7715,14 +7736,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524559</v>
+        <v>524774</v>
       </c>
       <c r="R69" t="n">
-        <v>6845427</v>
+        <v>6845100</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7781,10 +7802,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124500926</v>
+        <v>124490965</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7797,37 +7818,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524345</v>
+        <v>525081</v>
       </c>
       <c r="R70" t="n">
-        <v>6845461</v>
+        <v>6845283</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7871,19 +7892,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124502605</v>
+        <v>124489002</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7919,14 +7940,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524259</v>
+        <v>525277</v>
       </c>
       <c r="R71" t="n">
-        <v>6845061</v>
+        <v>6845196</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7959,6 +7980,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7985,7 +8011,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124487604</v>
+        <v>124492717</v>
       </c>
       <c r="B72" t="n">
         <v>78810</v>
@@ -8025,10 +8051,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524781</v>
+        <v>524757</v>
       </c>
       <c r="R72" t="n">
-        <v>6845167</v>
+        <v>6845190</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8087,7 +8113,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124488326</v>
+        <v>124490165</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -8127,10 +8153,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524734</v>
+        <v>525151</v>
       </c>
       <c r="R73" t="n">
-        <v>6845219</v>
+        <v>6845190</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8189,10 +8215,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124487283</v>
+        <v>124498165</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8205,34 +8231,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524836</v>
+        <v>524349</v>
       </c>
       <c r="R74" t="n">
-        <v>6845119</v>
+        <v>6845225</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8291,10 +8317,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124503680</v>
+        <v>124503227</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8307,21 +8333,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8331,13 +8357,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524648</v>
+        <v>524472</v>
       </c>
       <c r="R75" t="n">
-        <v>6845029</v>
+        <v>6845023</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8393,10 +8419,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124504860</v>
+        <v>124503504</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8409,21 +8435,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8433,10 +8459,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524224</v>
+        <v>524511</v>
       </c>
       <c r="R76" t="n">
-        <v>6844971</v>
+        <v>6845029</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8495,10 +8521,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124502475</v>
+        <v>124501577</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8507,41 +8533,50 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524197</v>
+        <v>524252</v>
       </c>
       <c r="R77" t="n">
-        <v>6845056</v>
+        <v>6845387</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8585,19 +8620,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124506146</v>
+        <v>124504651</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8632,7 +8667,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8646,13 +8681,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524148</v>
+        <v>524234</v>
       </c>
       <c r="R78" t="n">
-        <v>6845027</v>
+        <v>6844921</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8708,7 +8743,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124491428</v>
+        <v>124504485</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8743,7 +8778,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8753,14 +8788,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524954</v>
+        <v>524261</v>
       </c>
       <c r="R79" t="n">
-        <v>6845241</v>
+        <v>6844909</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8819,7 +8854,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124503388</v>
+        <v>124500069</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8854,7 +8889,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8868,10 +8903,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524214</v>
+        <v>524370</v>
       </c>
       <c r="R80" t="n">
-        <v>6844996</v>
+        <v>6845396</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8906,6 +8941,11 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8918,22 +8958,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124499895</v>
+        <v>124501719</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8942,50 +8982,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524362</v>
+        <v>524232</v>
       </c>
       <c r="R81" t="n">
-        <v>6845391</v>
+        <v>6845349</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9015,11 +9046,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9034,22 +9060,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124487039</v>
+        <v>124502522</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9058,50 +9084,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524908</v>
+        <v>524234</v>
       </c>
       <c r="R82" t="n">
-        <v>6845155</v>
+        <v>6845053</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9145,19 +9162,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124498529</v>
+        <v>124491548</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9193,14 +9210,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524365</v>
+        <v>524916</v>
       </c>
       <c r="R83" t="n">
-        <v>6845310</v>
+        <v>6845244</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9259,10 +9276,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124490965</v>
+        <v>124499713</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9275,37 +9292,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525081</v>
+        <v>524311</v>
       </c>
       <c r="R84" t="n">
-        <v>6845283</v>
+        <v>6845368</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9349,22 +9366,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124503002</v>
+        <v>124490978</v>
       </c>
       <c r="B85" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9377,34 +9394,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524333</v>
+        <v>525086</v>
       </c>
       <c r="R85" t="n">
-        <v>6845022</v>
+        <v>6845224</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9463,7 +9480,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124504321</v>
+        <v>124486895</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9499,17 +9516,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524276</v>
+        <v>524856</v>
       </c>
       <c r="R86" t="n">
-        <v>6844888</v>
+        <v>6845128</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9553,22 +9570,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124502522</v>
+        <v>124504973</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9577,38 +9594,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524234</v>
+        <v>524210</v>
       </c>
       <c r="R87" t="n">
-        <v>6845053</v>
+        <v>6844954</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9667,10 +9693,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124492635</v>
+        <v>124487564</v>
       </c>
       <c r="B88" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9683,21 +9709,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9707,10 +9733,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524790</v>
+        <v>524773</v>
       </c>
       <c r="R88" t="n">
-        <v>6845219</v>
+        <v>6845141</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9743,11 +9769,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9774,10 +9795,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124490091</v>
+        <v>124499895</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9786,38 +9807,47 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525149</v>
+        <v>524362</v>
       </c>
       <c r="R89" t="n">
-        <v>6845210</v>
+        <v>6845391</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9850,6 +9880,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9876,10 +9911,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124500112</v>
+        <v>124504513</v>
       </c>
       <c r="B90" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9888,41 +9923,50 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524447</v>
+        <v>524245</v>
       </c>
       <c r="R90" t="n">
-        <v>6845417</v>
+        <v>6844924</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9966,19 +10010,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124498070</v>
+        <v>124502475</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -10018,13 +10062,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524353</v>
+        <v>524197</v>
       </c>
       <c r="R91" t="n">
-        <v>6845201</v>
+        <v>6845056</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10068,22 +10112,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124491300</v>
+        <v>124504354</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10092,41 +10136,50 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525015</v>
+        <v>524274</v>
       </c>
       <c r="R92" t="n">
-        <v>6845263</v>
+        <v>6844889</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10182,10 +10235,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124493358</v>
+        <v>124498794</v>
       </c>
       <c r="B93" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10194,38 +10247,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524793</v>
+        <v>524383</v>
       </c>
       <c r="R93" t="n">
-        <v>6845243</v>
+        <v>6845264</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10284,10 +10337,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124504945</v>
+        <v>124488535</v>
       </c>
       <c r="B94" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10300,37 +10353,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524203</v>
+        <v>525311</v>
       </c>
       <c r="R94" t="n">
-        <v>6844991</v>
+        <v>6845039</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10374,22 +10427,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124504565</v>
+        <v>124487771</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10398,47 +10451,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524227</v>
+        <v>524761</v>
       </c>
       <c r="R95" t="n">
-        <v>6844932</v>
+        <v>6845213</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10497,10 +10541,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124504651</v>
+        <v>124498760</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10509,50 +10553,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524234</v>
+        <v>524388</v>
       </c>
       <c r="R96" t="n">
-        <v>6844921</v>
+        <v>6845283</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10608,10 +10643,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124486962</v>
+        <v>124486832</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10620,47 +10655,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524859</v>
+        <v>524856</v>
       </c>
       <c r="R97" t="n">
-        <v>6845148</v>
+        <v>6845111</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10719,10 +10745,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124490720</v>
+        <v>124498936</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10735,37 +10761,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>525133</v>
+        <v>524415</v>
       </c>
       <c r="R98" t="n">
-        <v>6845307</v>
+        <v>6845335</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10809,22 +10835,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124502991</v>
+        <v>124503785</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10837,21 +10863,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,10 +10887,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524280</v>
+        <v>524244</v>
       </c>
       <c r="R99" t="n">
-        <v>6845054</v>
+        <v>6845004</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10923,7 +10949,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124500909</v>
+        <v>124487374</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -10959,17 +10985,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524346</v>
+        <v>524974</v>
       </c>
       <c r="R100" t="n">
-        <v>6845458</v>
+        <v>6845191</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11013,22 +11039,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124504973</v>
+        <v>124504860</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11037,47 +11063,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524210</v>
+        <v>524224</v>
       </c>
       <c r="R101" t="n">
-        <v>6844954</v>
+        <v>6844971</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11238,7 +11255,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124498760</v>
+        <v>124491531</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11274,17 +11291,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524388</v>
+        <v>524919</v>
       </c>
       <c r="R103" t="n">
-        <v>6845283</v>
+        <v>6845253</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11340,10 +11357,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124504769</v>
+        <v>124492000</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11352,47 +11369,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524231</v>
+        <v>524901</v>
       </c>
       <c r="R104" t="n">
-        <v>6844957</v>
+        <v>6845216</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11451,10 +11459,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124504916</v>
+        <v>124503680</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11463,47 +11471,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524219</v>
+        <v>524648</v>
       </c>
       <c r="R105" t="n">
-        <v>6844970</v>
+        <v>6845029</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11562,7 +11561,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124500867</v>
+        <v>124491246</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11598,17 +11597,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524343</v>
+        <v>525065</v>
       </c>
       <c r="R106" t="n">
-        <v>6845433</v>
+        <v>6845243</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11664,7 +11663,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124491765</v>
+        <v>124486839</v>
       </c>
       <c r="B107" t="n">
         <v>78810</v>
@@ -11704,13 +11703,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524904</v>
+        <v>524872</v>
       </c>
       <c r="R107" t="n">
-        <v>6845207</v>
+        <v>6845107</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11754,19 +11753,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124487775</v>
+        <v>124490097</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11806,10 +11805,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>525079</v>
+        <v>525147</v>
       </c>
       <c r="R108" t="n">
-        <v>6845164</v>
+        <v>6845208</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11868,10 +11867,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124492194</v>
+        <v>124490692</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11880,25 +11879,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11908,10 +11907,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524798</v>
+        <v>525103</v>
       </c>
       <c r="R109" t="n">
-        <v>6845206</v>
+        <v>6845194</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11970,10 +11969,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124489815</v>
+        <v>124487567</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11986,21 +11985,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12010,13 +12009,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>525208</v>
+        <v>525000</v>
       </c>
       <c r="R110" t="n">
-        <v>6845169</v>
+        <v>6845201</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12060,19 +12059,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124487689</v>
+        <v>124500865</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -12108,17 +12107,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524780</v>
+        <v>524350</v>
       </c>
       <c r="R111" t="n">
-        <v>6845188</v>
+        <v>6845399</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12162,22 +12161,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124499838</v>
+        <v>124498544</v>
       </c>
       <c r="B112" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12186,50 +12185,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524478</v>
+        <v>524364</v>
       </c>
       <c r="R112" t="n">
-        <v>6845426</v>
+        <v>6845312</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12273,19 +12263,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124490165</v>
+        <v>124487121</v>
       </c>
       <c r="B113" t="n">
         <v>78810</v>
@@ -12325,10 +12315,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>525151</v>
+        <v>524844</v>
       </c>
       <c r="R113" t="n">
-        <v>6845190</v>
+        <v>6845169</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12387,7 +12377,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124488535</v>
+        <v>124491294</v>
       </c>
       <c r="B114" t="n">
         <v>78810</v>
@@ -12427,13 +12417,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>525311</v>
+        <v>525063</v>
       </c>
       <c r="R114" t="n">
-        <v>6845039</v>
+        <v>6845234</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12477,22 +12467,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124504662</v>
+        <v>124491428</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12501,41 +12491,50 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524244</v>
+        <v>524954</v>
       </c>
       <c r="R115" t="n">
-        <v>6844920</v>
+        <v>6845241</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12591,10 +12590,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124487771</v>
+        <v>124504054</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12603,38 +12602,47 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524761</v>
+        <v>524683</v>
       </c>
       <c r="R116" t="n">
-        <v>6845213</v>
+        <v>6844956</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12693,10 +12701,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124504545</v>
+        <v>124490527</v>
       </c>
       <c r="B117" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12705,50 +12713,46 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524237</v>
+        <v>525139</v>
       </c>
       <c r="R117" t="n">
-        <v>6844919</v>
+        <v>6845241</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12778,6 +12782,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12792,19 +12801,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124501577</v>
+        <v>124500794</v>
       </c>
       <c r="B118" t="n">
         <v>98101</v>
@@ -12837,29 +12846,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524252</v>
+        <v>524370</v>
       </c>
       <c r="R118" t="n">
-        <v>6845387</v>
+        <v>6845393</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12903,19 +12903,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124487293</v>
+        <v>124504916</v>
       </c>
       <c r="B119" t="n">
         <v>98101</v>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12960,17 +12960,17 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524948</v>
+        <v>524219</v>
       </c>
       <c r="R119" t="n">
-        <v>6845179</v>
+        <v>6844970</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13014,19 +13014,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124488657</v>
+        <v>124491765</v>
       </c>
       <c r="B120" t="n">
         <v>78810</v>
@@ -13066,13 +13066,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>525312</v>
+        <v>524904</v>
       </c>
       <c r="R120" t="n">
-        <v>6845117</v>
+        <v>6845207</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13116,19 +13116,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124486839</v>
+        <v>124491300</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13168,13 +13168,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524872</v>
+        <v>525015</v>
       </c>
       <c r="R121" t="n">
-        <v>6845107</v>
+        <v>6845263</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124491387</v>
+        <v>124504662</v>
       </c>
       <c r="B122" t="n">
         <v>78810</v>
@@ -13266,17 +13266,17 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524949</v>
+        <v>524244</v>
       </c>
       <c r="R122" t="n">
-        <v>6845252</v>
+        <v>6844920</v>
       </c>
       <c r="S122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124492513</v>
+        <v>124500867</v>
       </c>
       <c r="B123" t="n">
         <v>78810</v>
@@ -13368,17 +13368,17 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524774</v>
+        <v>524343</v>
       </c>
       <c r="R123" t="n">
-        <v>6845100</v>
+        <v>6845433</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13422,19 +13422,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124504513</v>
+        <v>124504769</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524245</v>
+        <v>524231</v>
       </c>
       <c r="R124" t="n">
-        <v>6844924</v>
+        <v>6844957</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13545,7 +13545,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124492072</v>
+        <v>124499832</v>
       </c>
       <c r="B125" t="n">
         <v>98101</v>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13590,14 +13590,14 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524828</v>
+        <v>524327</v>
       </c>
       <c r="R125" t="n">
-        <v>6845147</v>
+        <v>6845386</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13656,10 +13656,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124491320</v>
+        <v>124489748</v>
       </c>
       <c r="B126" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13668,38 +13668,47 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>525017</v>
+        <v>525230</v>
       </c>
       <c r="R126" t="n">
-        <v>6845257</v>
+        <v>6845187</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13746,22 +13755,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124489748</v>
+        <v>124487604</v>
       </c>
       <c r="B127" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13770,47 +13779,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>525230</v>
+        <v>524781</v>
       </c>
       <c r="R127" t="n">
-        <v>6845187</v>
+        <v>6845167</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124499480</v>
+        <v>124487317</v>
       </c>
       <c r="B128" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13881,47 +13881,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524365</v>
+        <v>524829</v>
       </c>
       <c r="R128" t="n">
-        <v>6845400</v>
+        <v>6845141</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13954,11 +13945,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13985,7 +13971,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124491805</v>
+        <v>124488657</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14025,13 +14011,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524880</v>
+        <v>525312</v>
       </c>
       <c r="R129" t="n">
-        <v>6845212</v>
+        <v>6845117</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14075,22 +14061,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124501831</v>
+        <v>124501662</v>
       </c>
       <c r="B130" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14099,41 +14085,50 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524268</v>
+        <v>524272</v>
       </c>
       <c r="R130" t="n">
-        <v>6845351</v>
+        <v>6845365</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14189,7 +14184,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124504151</v>
+        <v>124504089</v>
       </c>
       <c r="B131" t="n">
         <v>98101</v>
@@ -14222,20 +14217,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524256</v>
+        <v>524238</v>
       </c>
       <c r="R131" t="n">
-        <v>6844925</v>
+        <v>6844930</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14291,10 +14295,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124504089</v>
+        <v>124503002</v>
       </c>
       <c r="B132" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14303,47 +14307,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524238</v>
+        <v>524333</v>
       </c>
       <c r="R132" t="n">
-        <v>6844930</v>
+        <v>6845022</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>
@@ -14390,22 +14385,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124500201</v>
+        <v>124504321</v>
       </c>
       <c r="B133" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14414,50 +14409,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524390</v>
+        <v>524276</v>
       </c>
       <c r="R133" t="n">
-        <v>6845406</v>
+        <v>6844888</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14487,11 +14473,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14506,22 +14487,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124487514</v>
+        <v>124504250</v>
       </c>
       <c r="B134" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14530,41 +14511,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>525016</v>
+        <v>524436</v>
       </c>
       <c r="R134" t="n">
-        <v>6845190</v>
+        <v>6844930</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14594,6 +14575,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14608,22 +14594,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124501563</v>
+        <v>124489670</v>
       </c>
       <c r="B135" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14632,38 +14618,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524245</v>
+        <v>525247</v>
       </c>
       <c r="R135" t="n">
-        <v>6845371</v>
+        <v>6845194</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14722,7 +14717,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124489792</v>
+        <v>124499480</v>
       </c>
       <c r="B136" t="n">
         <v>98101</v>
@@ -14757,7 +14752,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -14767,14 +14762,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>525215</v>
+        <v>524365</v>
       </c>
       <c r="R136" t="n">
-        <v>6845178</v>
+        <v>6845400</v>
       </c>
       <c r="S136" t="n">
         <v>20</v>
@@ -14807,6 +14802,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124491320</v>
+        <v>124491427</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525017</v>
+        <v>524946</v>
       </c>
       <c r="R2" t="n">
-        <v>6845257</v>
+        <v>6845286</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124505389</v>
+        <v>124488103</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524115</v>
+        <v>525146</v>
       </c>
       <c r="R3" t="n">
-        <v>6845050</v>
+        <v>6845150</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124491427</v>
+        <v>124490555</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524946</v>
+        <v>525142</v>
       </c>
       <c r="R4" t="n">
-        <v>6845286</v>
+        <v>6845241</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124488103</v>
+        <v>124491320</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525146</v>
+        <v>525017</v>
       </c>
       <c r="R5" t="n">
-        <v>6845150</v>
+        <v>6845257</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124490555</v>
+        <v>124505389</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1100,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525142</v>
+        <v>524115</v>
       </c>
       <c r="R6" t="n">
-        <v>6845241</v>
+        <v>6845050</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,11 +1173,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,12 +1187,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124487467</v>
+        <v>124487039</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,41 +2861,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524805</v>
+        <v>524908</v>
       </c>
       <c r="R23" t="n">
-        <v>6845150</v>
+        <v>6845155</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2939,19 +2948,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124488326</v>
+        <v>124487467</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2991,10 +3000,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524734</v>
+        <v>524805</v>
       </c>
       <c r="R24" t="n">
-        <v>6845219</v>
+        <v>6845150</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3053,7 +3062,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124499127</v>
+        <v>124488326</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3089,17 +3098,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524559</v>
+        <v>524734</v>
       </c>
       <c r="R25" t="n">
-        <v>6845427</v>
+        <v>6845219</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,22 +3152,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124487039</v>
+        <v>124499127</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,47 +3176,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524908</v>
+        <v>524559</v>
       </c>
       <c r="R26" t="n">
-        <v>6845155</v>
+        <v>6845427</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3377,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124490720</v>
+        <v>124492635</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525133</v>
+        <v>524790</v>
       </c>
       <c r="R28" t="n">
-        <v>6845307</v>
+        <v>6845219</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3453,6 +3453,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3467,22 +3472,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124488157</v>
+        <v>124490720</v>
       </c>
       <c r="B29" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,13 +3524,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524731</v>
+        <v>525133</v>
       </c>
       <c r="R29" t="n">
-        <v>6845235</v>
+        <v>6845307</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,22 +3574,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124491917</v>
+        <v>124488157</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,21 +3602,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524852</v>
+        <v>524731</v>
       </c>
       <c r="R30" t="n">
-        <v>6845214</v>
+        <v>6845235</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3683,10 +3688,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124500112</v>
+        <v>124491917</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,37 +3704,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524447</v>
+        <v>524852</v>
       </c>
       <c r="R31" t="n">
-        <v>6845417</v>
+        <v>6845214</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,12 +3778,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3887,10 +3892,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124492635</v>
+        <v>124500112</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3903,37 +3908,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524790</v>
+        <v>524447</v>
       </c>
       <c r="R33" t="n">
-        <v>6845219</v>
+        <v>6845417</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3963,11 +3968,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3982,19 +3982,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124486962</v>
+        <v>124504545</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4039,14 +4039,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524859</v>
+        <v>524237</v>
       </c>
       <c r="R34" t="n">
-        <v>6845148</v>
+        <v>6844919</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124489792</v>
+        <v>124500201</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4150,14 +4150,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525215</v>
+        <v>524390</v>
       </c>
       <c r="R35" t="n">
-        <v>6845178</v>
+        <v>6845406</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4190,6 +4190,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,7 +4221,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124504545</v>
+        <v>124486962</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4251,7 +4256,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4261,14 +4266,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524237</v>
+        <v>524859</v>
       </c>
       <c r="R36" t="n">
-        <v>6844919</v>
+        <v>6845148</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4327,7 +4332,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124500201</v>
+        <v>124489792</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4362,7 +4367,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4372,14 +4377,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524390</v>
+        <v>525215</v>
       </c>
       <c r="R37" t="n">
-        <v>6845406</v>
+        <v>6845178</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4412,11 +4417,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4443,7 +4443,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124490428</v>
+        <v>124501831</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4479,17 +4479,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525133</v>
+        <v>524268</v>
       </c>
       <c r="R38" t="n">
-        <v>6845201</v>
+        <v>6845351</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4533,12 +4533,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124493108</v>
+        <v>124501039</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,41 +4779,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524776</v>
+        <v>524281</v>
       </c>
       <c r="R41" t="n">
-        <v>6845248</v>
+        <v>6845383</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4843,11 +4852,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4862,22 +4866,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124501039</v>
+        <v>124492194</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,50 +4890,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524281</v>
+        <v>524798</v>
       </c>
       <c r="R42" t="n">
-        <v>6845383</v>
+        <v>6845206</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4973,22 +4968,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124492194</v>
+        <v>124497941</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5001,37 +4996,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524798</v>
+        <v>524344</v>
       </c>
       <c r="R43" t="n">
-        <v>6845206</v>
+        <v>6845182</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5087,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124497941</v>
+        <v>124490428</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5103,37 +5098,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524344</v>
+        <v>525133</v>
       </c>
       <c r="R44" t="n">
-        <v>6845182</v>
+        <v>6845201</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5189,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124501831</v>
+        <v>124493108</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5205,37 +5200,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524268</v>
+        <v>524776</v>
       </c>
       <c r="R45" t="n">
-        <v>6845351</v>
+        <v>6845248</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5265,6 +5260,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5279,12 +5279,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -7172,7 +7172,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124489815</v>
+        <v>124491822</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525208</v>
+        <v>524857</v>
       </c>
       <c r="R64" t="n">
-        <v>6845169</v>
+        <v>6845201</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7262,19 +7262,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124491822</v>
+        <v>124500965</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7310,14 +7310,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524857</v>
+        <v>524308</v>
       </c>
       <c r="R65" t="n">
-        <v>6845201</v>
+        <v>6845471</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7364,22 +7364,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124500965</v>
+        <v>124492032</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7388,41 +7388,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524308</v>
+        <v>524881</v>
       </c>
       <c r="R66" t="n">
-        <v>6845471</v>
+        <v>6845143</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7466,19 +7475,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124492032</v>
+        <v>124499838</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7513,7 +7522,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7523,17 +7532,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524881</v>
+        <v>524478</v>
       </c>
       <c r="R67" t="n">
-        <v>6845143</v>
+        <v>6845426</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7589,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124499838</v>
+        <v>124489815</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7601,50 +7610,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524478</v>
+        <v>525208</v>
       </c>
       <c r="R68" t="n">
-        <v>6845426</v>
+        <v>6845169</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7688,22 +7688,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124492513</v>
+        <v>124501577</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7712,41 +7712,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524774</v>
+        <v>524252</v>
       </c>
       <c r="R69" t="n">
-        <v>6845100</v>
+        <v>6845387</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7790,22 +7799,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124490965</v>
+        <v>124504651</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7814,41 +7823,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525081</v>
+        <v>524234</v>
       </c>
       <c r="R70" t="n">
-        <v>6845283</v>
+        <v>6844921</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7892,22 +7910,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124489002</v>
+        <v>124504485</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7916,41 +7934,50 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525277</v>
+        <v>524261</v>
       </c>
       <c r="R71" t="n">
-        <v>6845196</v>
+        <v>6844909</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7980,11 +8007,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7999,22 +8021,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124492717</v>
+        <v>124500069</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8023,38 +8045,47 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524757</v>
+        <v>524370</v>
       </c>
       <c r="R72" t="n">
-        <v>6845190</v>
+        <v>6845396</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8087,6 +8118,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8113,10 +8149,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124490165</v>
+        <v>124503227</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8129,37 +8165,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525151</v>
+        <v>524472</v>
       </c>
       <c r="R73" t="n">
-        <v>6845190</v>
+        <v>6845023</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8215,7 +8251,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124498165</v>
+        <v>124503504</v>
       </c>
       <c r="B74" t="n">
         <v>78546</v>
@@ -8255,10 +8291,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524349</v>
+        <v>524511</v>
       </c>
       <c r="R74" t="n">
-        <v>6845225</v>
+        <v>6845029</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8317,10 +8353,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124503227</v>
+        <v>124492717</v>
       </c>
       <c r="B75" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8333,37 +8369,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524472</v>
+        <v>524757</v>
       </c>
       <c r="R75" t="n">
-        <v>6845023</v>
+        <v>6845190</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8419,10 +8455,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124503504</v>
+        <v>124490165</v>
       </c>
       <c r="B76" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8435,34 +8471,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524511</v>
+        <v>525151</v>
       </c>
       <c r="R76" t="n">
-        <v>6845029</v>
+        <v>6845190</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8521,10 +8557,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124501577</v>
+        <v>124498165</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8533,47 +8569,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524252</v>
+        <v>524349</v>
       </c>
       <c r="R77" t="n">
-        <v>6845387</v>
+        <v>6845225</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8632,10 +8659,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124504651</v>
+        <v>124492513</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8644,50 +8671,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524234</v>
+        <v>524774</v>
       </c>
       <c r="R78" t="n">
-        <v>6844921</v>
+        <v>6845100</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,22 +8749,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124504485</v>
+        <v>124490965</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8755,50 +8773,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524261</v>
+        <v>525081</v>
       </c>
       <c r="R79" t="n">
-        <v>6844909</v>
+        <v>6845283</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8842,22 +8851,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124500069</v>
+        <v>124489002</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8866,50 +8875,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524370</v>
+        <v>525277</v>
       </c>
       <c r="R80" t="n">
-        <v>6845396</v>
+        <v>6845196</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8958,22 +8958,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124501719</v>
+        <v>124491548</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8986,37 +8986,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524232</v>
+        <v>524916</v>
       </c>
       <c r="R81" t="n">
-        <v>6845349</v>
+        <v>6845244</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9060,22 +9060,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124502522</v>
+        <v>124499713</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524234</v>
+        <v>524311</v>
       </c>
       <c r="R82" t="n">
-        <v>6845053</v>
+        <v>6845368</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9174,7 +9174,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124491548</v>
+        <v>124490978</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524916</v>
+        <v>525086</v>
       </c>
       <c r="R83" t="n">
-        <v>6845244</v>
+        <v>6845224</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9276,10 +9276,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124499713</v>
+        <v>124486895</v>
       </c>
       <c r="B84" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9292,34 +9292,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524311</v>
+        <v>524856</v>
       </c>
       <c r="R84" t="n">
-        <v>6845368</v>
+        <v>6845128</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9378,10 +9378,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124490978</v>
+        <v>124501719</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9394,37 +9394,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525086</v>
+        <v>524232</v>
       </c>
       <c r="R85" t="n">
-        <v>6845224</v>
+        <v>6845349</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9468,19 +9468,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124486895</v>
+        <v>124502522</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9516,14 +9516,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524856</v>
+        <v>524234</v>
       </c>
       <c r="R86" t="n">
-        <v>6845128</v>
+        <v>6845053</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9693,10 +9693,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124487564</v>
+        <v>124499895</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9705,38 +9705,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524773</v>
+        <v>524362</v>
       </c>
       <c r="R88" t="n">
-        <v>6845141</v>
+        <v>6845391</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9769,6 +9778,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9795,7 +9809,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124499895</v>
+        <v>124504513</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9830,7 +9844,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9844,10 +9858,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524362</v>
+        <v>524245</v>
       </c>
       <c r="R89" t="n">
-        <v>6845391</v>
+        <v>6844924</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9880,11 +9894,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9911,10 +9920,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124504513</v>
+        <v>124487564</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9923,47 +9932,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524245</v>
+        <v>524773</v>
       </c>
       <c r="R90" t="n">
-        <v>6844924</v>
+        <v>6845141</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -10124,10 +10124,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124504354</v>
+        <v>124498794</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10136,50 +10136,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524274</v>
+        <v>524383</v>
       </c>
       <c r="R92" t="n">
-        <v>6844889</v>
+        <v>6845264</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10223,22 +10214,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124498794</v>
+        <v>124488535</v>
       </c>
       <c r="B93" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10247,41 +10238,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524383</v>
+        <v>525311</v>
       </c>
       <c r="R93" t="n">
-        <v>6845264</v>
+        <v>6845039</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10325,19 +10316,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124488535</v>
+        <v>124487771</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10377,13 +10368,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525311</v>
+        <v>524761</v>
       </c>
       <c r="R94" t="n">
-        <v>6845039</v>
+        <v>6845213</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10427,19 +10418,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124487771</v>
+        <v>124498760</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10475,14 +10466,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524761</v>
+        <v>524388</v>
       </c>
       <c r="R95" t="n">
-        <v>6845213</v>
+        <v>6845283</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10541,7 +10532,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124498760</v>
+        <v>124486832</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10577,14 +10568,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524388</v>
+        <v>524856</v>
       </c>
       <c r="R96" t="n">
-        <v>6845283</v>
+        <v>6845111</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10643,10 +10634,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124486832</v>
+        <v>124498936</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10659,34 +10650,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524856</v>
+        <v>524415</v>
       </c>
       <c r="R97" t="n">
-        <v>6845111</v>
+        <v>6845335</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10745,10 +10736,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124498936</v>
+        <v>124504354</v>
       </c>
       <c r="B98" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10757,41 +10748,50 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524415</v>
+        <v>524274</v>
       </c>
       <c r="R98" t="n">
-        <v>6845335</v>
+        <v>6844889</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10835,12 +10835,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11255,7 +11255,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124491531</v>
+        <v>124503680</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11291,17 +11291,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524919</v>
+        <v>524648</v>
       </c>
       <c r="R103" t="n">
-        <v>6845253</v>
+        <v>6845029</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124492000</v>
+        <v>124491246</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524901</v>
+        <v>525065</v>
       </c>
       <c r="R104" t="n">
-        <v>6845216</v>
+        <v>6845243</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124503680</v>
+        <v>124486839</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11495,17 +11495,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524648</v>
+        <v>524872</v>
       </c>
       <c r="R105" t="n">
-        <v>6845029</v>
+        <v>6845107</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11549,19 +11549,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124491246</v>
+        <v>124490097</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11601,13 +11601,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>525065</v>
+        <v>525147</v>
       </c>
       <c r="R106" t="n">
-        <v>6845243</v>
+        <v>6845208</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11651,22 +11651,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124486839</v>
+        <v>124490692</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11675,25 +11675,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11703,13 +11703,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524872</v>
+        <v>525103</v>
       </c>
       <c r="R107" t="n">
-        <v>6845107</v>
+        <v>6845194</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11753,19 +11753,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124490097</v>
+        <v>124491531</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11805,13 +11805,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>525147</v>
+        <v>524919</v>
       </c>
       <c r="R108" t="n">
-        <v>6845208</v>
+        <v>6845253</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11855,22 +11855,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124490692</v>
+        <v>124492000</v>
       </c>
       <c r="B109" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11879,25 +11879,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>525103</v>
+        <v>524901</v>
       </c>
       <c r="R109" t="n">
-        <v>6845194</v>
+        <v>6845216</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -12071,10 +12071,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124500865</v>
+        <v>124490527</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12087,34 +12087,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524350</v>
+        <v>525139</v>
       </c>
       <c r="R111" t="n">
-        <v>6845399</v>
+        <v>6845241</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12147,6 +12152,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12479,10 +12489,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124491428</v>
+        <v>124500865</v>
       </c>
       <c r="B115" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12491,50 +12501,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524954</v>
+        <v>524350</v>
       </c>
       <c r="R115" t="n">
-        <v>6845241</v>
+        <v>6845399</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12578,19 +12579,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124504054</v>
+        <v>124491428</v>
       </c>
       <c r="B116" t="n">
         <v>98101</v>
@@ -12625,7 +12626,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -12635,14 +12636,14 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524683</v>
+        <v>524954</v>
       </c>
       <c r="R116" t="n">
-        <v>6844956</v>
+        <v>6845241</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12701,10 +12702,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124490527</v>
+        <v>124504054</v>
       </c>
       <c r="B117" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12713,46 +12714,50 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>525139</v>
+        <v>524683</v>
       </c>
       <c r="R117" t="n">
-        <v>6845241</v>
+        <v>6844956</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12782,11 +12787,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12801,12 +12801,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13971,10 +13971,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124488657</v>
+        <v>124504250</v>
       </c>
       <c r="B129" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13983,41 +13983,41 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>525312</v>
+        <v>524436</v>
       </c>
       <c r="R129" t="n">
-        <v>6845117</v>
+        <v>6844930</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14047,6 +14047,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14061,22 +14066,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124501662</v>
+        <v>124504321</v>
       </c>
       <c r="B130" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14085,50 +14090,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524272</v>
+        <v>524276</v>
       </c>
       <c r="R130" t="n">
-        <v>6845365</v>
+        <v>6844888</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14184,7 +14180,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124504089</v>
+        <v>124501662</v>
       </c>
       <c r="B131" t="n">
         <v>98101</v>
@@ -14219,7 +14215,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14233,10 +14229,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524238</v>
+        <v>524272</v>
       </c>
       <c r="R131" t="n">
-        <v>6844930</v>
+        <v>6845365</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14295,10 +14291,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124503002</v>
+        <v>124504089</v>
       </c>
       <c r="B132" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14307,38 +14303,47 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524333</v>
+        <v>524238</v>
       </c>
       <c r="R132" t="n">
-        <v>6845022</v>
+        <v>6844930</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>
@@ -14385,22 +14390,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124504321</v>
+        <v>124503002</v>
       </c>
       <c r="B133" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14413,21 +14418,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14437,13 +14442,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524276</v>
+        <v>524333</v>
       </c>
       <c r="R133" t="n">
-        <v>6844888</v>
+        <v>6845022</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14487,22 +14492,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124504250</v>
+        <v>124488657</v>
       </c>
       <c r="B134" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14511,41 +14516,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524436</v>
+        <v>525312</v>
       </c>
       <c r="R134" t="n">
-        <v>6844930</v>
+        <v>6845117</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14575,11 +14580,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14594,12 +14594,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -2849,10 +2849,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124487039</v>
+        <v>124487467</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,50 +2861,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524908</v>
+        <v>524805</v>
       </c>
       <c r="R23" t="n">
-        <v>6845155</v>
+        <v>6845150</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2948,19 +2939,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124487467</v>
+        <v>124488326</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3000,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524805</v>
+        <v>524734</v>
       </c>
       <c r="R24" t="n">
-        <v>6845150</v>
+        <v>6845219</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3062,7 +3053,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124488326</v>
+        <v>124499127</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3098,17 +3089,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524734</v>
+        <v>524559</v>
       </c>
       <c r="R25" t="n">
-        <v>6845219</v>
+        <v>6845427</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3152,22 +3143,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124499127</v>
+        <v>124487039</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,38 +3167,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524559</v>
+        <v>524908</v>
       </c>
       <c r="R26" t="n">
-        <v>6845427</v>
+        <v>6845155</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3377,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124492635</v>
+        <v>124490720</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524790</v>
+        <v>525133</v>
       </c>
       <c r="R28" t="n">
-        <v>6845219</v>
+        <v>6845307</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3453,11 +3453,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3472,22 +3467,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124490720</v>
+        <v>124488157</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3500,21 +3495,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,13 +3519,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525133</v>
+        <v>524731</v>
       </c>
       <c r="R29" t="n">
-        <v>6845307</v>
+        <v>6845235</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,22 +3569,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124488157</v>
+        <v>124491917</v>
       </c>
       <c r="B30" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3602,21 +3597,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3626,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524731</v>
+        <v>524852</v>
       </c>
       <c r="R30" t="n">
-        <v>6845235</v>
+        <v>6845214</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3688,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124491917</v>
+        <v>124500112</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3704,37 +3699,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524852</v>
+        <v>524447</v>
       </c>
       <c r="R31" t="n">
-        <v>6845214</v>
+        <v>6845417</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3778,12 +3773,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3892,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124500112</v>
+        <v>124492635</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3908,37 +3903,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524447</v>
+        <v>524790</v>
       </c>
       <c r="R33" t="n">
-        <v>6845417</v>
+        <v>6845219</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3968,6 +3963,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3982,19 +3982,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124504545</v>
+        <v>124486962</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4039,14 +4039,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524237</v>
+        <v>524859</v>
       </c>
       <c r="R34" t="n">
-        <v>6844919</v>
+        <v>6845148</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124500201</v>
+        <v>124489792</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4150,14 +4150,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524390</v>
+        <v>525215</v>
       </c>
       <c r="R35" t="n">
-        <v>6845406</v>
+        <v>6845178</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4190,11 +4190,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4221,7 +4216,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124486962</v>
+        <v>124504545</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4256,7 +4251,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4266,14 +4261,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524859</v>
+        <v>524237</v>
       </c>
       <c r="R36" t="n">
-        <v>6845148</v>
+        <v>6844919</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4332,7 +4327,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124489792</v>
+        <v>124500201</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4367,7 +4362,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4377,14 +4372,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525215</v>
+        <v>524390</v>
       </c>
       <c r="R37" t="n">
-        <v>6845178</v>
+        <v>6845406</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4417,6 +4412,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4443,7 +4443,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124501831</v>
+        <v>124490428</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4479,17 +4479,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524268</v>
+        <v>525133</v>
       </c>
       <c r="R38" t="n">
-        <v>6845351</v>
+        <v>6845201</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4533,12 +4533,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124501039</v>
+        <v>124493108</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,50 +4779,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524281</v>
+        <v>524776</v>
       </c>
       <c r="R41" t="n">
-        <v>6845383</v>
+        <v>6845248</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4852,6 +4843,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4866,22 +4862,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124492194</v>
+        <v>124501039</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4890,41 +4886,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524798</v>
+        <v>524281</v>
       </c>
       <c r="R42" t="n">
-        <v>6845206</v>
+        <v>6845383</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4968,22 +4973,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124497941</v>
+        <v>124492194</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4996,37 +5001,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524344</v>
+        <v>524798</v>
       </c>
       <c r="R43" t="n">
-        <v>6845182</v>
+        <v>6845206</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5082,10 +5087,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124490428</v>
+        <v>124497941</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5098,37 +5103,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525133</v>
+        <v>524344</v>
       </c>
       <c r="R44" t="n">
-        <v>6845201</v>
+        <v>6845182</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5184,10 +5189,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124493108</v>
+        <v>124501831</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,37 +5205,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524776</v>
+        <v>524268</v>
       </c>
       <c r="R45" t="n">
-        <v>6845248</v>
+        <v>6845351</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5260,11 +5265,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5279,22 +5279,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124487689</v>
+        <v>124502910</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5303,41 +5303,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524780</v>
+        <v>524247</v>
       </c>
       <c r="R46" t="n">
-        <v>6845188</v>
+        <v>6845069</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5381,22 +5390,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124498466</v>
+        <v>124504704</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5405,38 +5414,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524369</v>
+        <v>524238</v>
       </c>
       <c r="R47" t="n">
-        <v>6845293</v>
+        <v>6844943</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5495,10 +5513,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124501563</v>
+        <v>124487689</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5511,37 +5529,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524245</v>
+        <v>524780</v>
       </c>
       <c r="R48" t="n">
-        <v>6845371</v>
+        <v>6845188</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5585,19 +5603,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124502605</v>
+        <v>124498466</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5637,13 +5655,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524259</v>
+        <v>524369</v>
       </c>
       <c r="R49" t="n">
-        <v>6845061</v>
+        <v>6845293</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5687,22 +5705,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124502910</v>
+        <v>124501563</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5711,47 +5729,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524247</v>
+        <v>524245</v>
       </c>
       <c r="R50" t="n">
-        <v>6845069</v>
+        <v>6845371</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5810,10 +5819,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124504704</v>
+        <v>124502605</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5822,50 +5831,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524238</v>
+        <v>524259</v>
       </c>
       <c r="R51" t="n">
-        <v>6844943</v>
+        <v>6845061</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5909,12 +5909,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124487293</v>
+        <v>124500926</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6656,50 +6656,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524948</v>
+        <v>524345</v>
       </c>
       <c r="R59" t="n">
-        <v>6845179</v>
+        <v>6845461</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6743,22 +6734,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124502783</v>
+        <v>124491805</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6767,50 +6758,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524254</v>
+        <v>524880</v>
       </c>
       <c r="R60" t="n">
-        <v>6845067</v>
+        <v>6845212</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6854,12 +6836,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6968,10 +6950,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124491805</v>
+        <v>124487293</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6980,41 +6962,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524880</v>
+        <v>524948</v>
       </c>
       <c r="R62" t="n">
-        <v>6845212</v>
+        <v>6845179</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7058,22 +7049,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124500926</v>
+        <v>124502783</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7082,41 +7073,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524345</v>
+        <v>524254</v>
       </c>
       <c r="R63" t="n">
-        <v>6845461</v>
+        <v>6845067</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7160,12 +7160,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124501577</v>
+        <v>124492513</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7712,50 +7712,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524252</v>
+        <v>524774</v>
       </c>
       <c r="R69" t="n">
-        <v>6845387</v>
+        <v>6845100</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7799,22 +7790,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124504651</v>
+        <v>124490965</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7823,50 +7814,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524234</v>
+        <v>525081</v>
       </c>
       <c r="R70" t="n">
-        <v>6844921</v>
+        <v>6845283</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7910,22 +7892,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124504485</v>
+        <v>124489002</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7934,50 +7916,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524261</v>
+        <v>525277</v>
       </c>
       <c r="R71" t="n">
-        <v>6844909</v>
+        <v>6845196</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8007,6 +7980,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8021,22 +7999,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124500069</v>
+        <v>124492717</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8045,47 +8023,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524370</v>
+        <v>524757</v>
       </c>
       <c r="R72" t="n">
-        <v>6845396</v>
+        <v>6845190</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8118,11 +8087,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8149,10 +8113,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124503227</v>
+        <v>124490165</v>
       </c>
       <c r="B73" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8165,37 +8129,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524472</v>
+        <v>525151</v>
       </c>
       <c r="R73" t="n">
-        <v>6845023</v>
+        <v>6845190</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8251,7 +8215,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124503504</v>
+        <v>124498165</v>
       </c>
       <c r="B74" t="n">
         <v>78546</v>
@@ -8291,10 +8255,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524511</v>
+        <v>524349</v>
       </c>
       <c r="R74" t="n">
-        <v>6845029</v>
+        <v>6845225</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8353,10 +8317,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124492717</v>
+        <v>124503227</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8369,37 +8333,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524757</v>
+        <v>524472</v>
       </c>
       <c r="R75" t="n">
-        <v>6845190</v>
+        <v>6845023</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8455,10 +8419,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124490165</v>
+        <v>124503504</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8471,34 +8435,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525151</v>
+        <v>524511</v>
       </c>
       <c r="R76" t="n">
-        <v>6845190</v>
+        <v>6845029</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8557,10 +8521,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124498165</v>
+        <v>124501577</v>
       </c>
       <c r="B77" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8569,38 +8533,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524349</v>
+        <v>524252</v>
       </c>
       <c r="R77" t="n">
-        <v>6845225</v>
+        <v>6845387</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8659,10 +8632,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124492513</v>
+        <v>124504651</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8671,41 +8644,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524774</v>
+        <v>524234</v>
       </c>
       <c r="R78" t="n">
-        <v>6845100</v>
+        <v>6844921</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8749,22 +8731,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124490965</v>
+        <v>124504485</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8773,41 +8755,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525081</v>
+        <v>524261</v>
       </c>
       <c r="R79" t="n">
-        <v>6845283</v>
+        <v>6844909</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8851,22 +8842,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124489002</v>
+        <v>124500069</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8875,41 +8866,50 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525277</v>
+        <v>524370</v>
       </c>
       <c r="R80" t="n">
-        <v>6845196</v>
+        <v>6845396</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8958,12 +8958,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -11051,7 +11051,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124504860</v>
+        <v>124491477</v>
       </c>
       <c r="B101" t="n">
         <v>78810</v>
@@ -11087,14 +11087,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524224</v>
+        <v>524920</v>
       </c>
       <c r="R101" t="n">
-        <v>6844971</v>
+        <v>6845260</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11153,7 +11153,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124491477</v>
+        <v>124504860</v>
       </c>
       <c r="B102" t="n">
         <v>78810</v>
@@ -11189,14 +11189,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524920</v>
+        <v>524224</v>
       </c>
       <c r="R102" t="n">
-        <v>6845260</v>
+        <v>6844971</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -12071,10 +12071,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124490527</v>
+        <v>124500865</v>
       </c>
       <c r="B111" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12087,39 +12087,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>525139</v>
+        <v>524350</v>
       </c>
       <c r="R111" t="n">
-        <v>6845241</v>
+        <v>6845399</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12152,11 +12147,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12489,10 +12479,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124500865</v>
+        <v>124490527</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12505,34 +12495,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524350</v>
+        <v>525139</v>
       </c>
       <c r="R115" t="n">
-        <v>6845399</v>
+        <v>6845241</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12565,6 +12560,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12591,7 +12591,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124491428</v>
+        <v>124500794</v>
       </c>
       <c r="B116" t="n">
         <v>98101</v>
@@ -12624,29 +12624,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524954</v>
+        <v>524370</v>
       </c>
       <c r="R116" t="n">
-        <v>6845241</v>
+        <v>6845393</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12690,19 +12681,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124504054</v>
+        <v>124504916</v>
       </c>
       <c r="B117" t="n">
         <v>98101</v>
@@ -12737,7 +12728,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -12751,10 +12742,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524683</v>
+        <v>524219</v>
       </c>
       <c r="R117" t="n">
-        <v>6844956</v>
+        <v>6844970</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12813,7 +12804,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124500794</v>
+        <v>124491428</v>
       </c>
       <c r="B118" t="n">
         <v>98101</v>
@@ -12846,20 +12837,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524370</v>
+        <v>524954</v>
       </c>
       <c r="R118" t="n">
-        <v>6845393</v>
+        <v>6845241</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12903,19 +12903,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124504916</v>
+        <v>124504054</v>
       </c>
       <c r="B119" t="n">
         <v>98101</v>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12964,10 +12964,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524219</v>
+        <v>524683</v>
       </c>
       <c r="R119" t="n">
-        <v>6844970</v>
+        <v>6844956</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13971,10 +13971,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124504250</v>
+        <v>124488657</v>
       </c>
       <c r="B129" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13983,41 +13983,41 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524436</v>
+        <v>525312</v>
       </c>
       <c r="R129" t="n">
-        <v>6844930</v>
+        <v>6845117</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14047,11 +14047,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14066,22 +14061,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124504321</v>
+        <v>124501662</v>
       </c>
       <c r="B130" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14090,41 +14085,50 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524276</v>
+        <v>524272</v>
       </c>
       <c r="R130" t="n">
-        <v>6844888</v>
+        <v>6845365</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14180,7 +14184,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124501662</v>
+        <v>124504089</v>
       </c>
       <c r="B131" t="n">
         <v>98101</v>
@@ -14215,7 +14219,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14229,10 +14233,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524272</v>
+        <v>524238</v>
       </c>
       <c r="R131" t="n">
-        <v>6845365</v>
+        <v>6844930</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14291,10 +14295,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124504089</v>
+        <v>124503002</v>
       </c>
       <c r="B132" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14303,47 +14307,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524238</v>
+        <v>524333</v>
       </c>
       <c r="R132" t="n">
-        <v>6844930</v>
+        <v>6845022</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>
@@ -14390,22 +14385,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124503002</v>
+        <v>124504321</v>
       </c>
       <c r="B133" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14418,21 +14413,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14442,13 +14437,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524333</v>
+        <v>524276</v>
       </c>
       <c r="R133" t="n">
-        <v>6845022</v>
+        <v>6844888</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14492,22 +14487,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124488657</v>
+        <v>124504250</v>
       </c>
       <c r="B134" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14516,41 +14511,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>525312</v>
+        <v>524436</v>
       </c>
       <c r="R134" t="n">
-        <v>6845117</v>
+        <v>6844930</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14580,6 +14575,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14594,12 +14594,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124491427</v>
+        <v>124504704</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524946</v>
+        <v>524238</v>
       </c>
       <c r="R2" t="n">
-        <v>6845286</v>
+        <v>6844943</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124488103</v>
+        <v>124503027</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525146</v>
+        <v>524345</v>
       </c>
       <c r="R3" t="n">
-        <v>6845150</v>
+        <v>6845032</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +876,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124490555</v>
+        <v>124500867</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -915,17 +924,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525142</v>
+        <v>524343</v>
       </c>
       <c r="R4" t="n">
-        <v>6845241</v>
+        <v>6845433</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124491320</v>
+        <v>124491619</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525017</v>
+        <v>524906</v>
       </c>
       <c r="R5" t="n">
-        <v>6845257</v>
+        <v>6845220</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1076,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124505389</v>
+        <v>124493358</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,47 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524115</v>
+        <v>524793</v>
       </c>
       <c r="R6" t="n">
-        <v>6845050</v>
+        <v>6845243</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1199,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124491387</v>
+        <v>124504662</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1235,17 +1230,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524949</v>
+        <v>524244</v>
       </c>
       <c r="R7" t="n">
-        <v>6845252</v>
+        <v>6844920</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124491619</v>
+        <v>124499895</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,38 +1308,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524906</v>
+        <v>524362</v>
       </c>
       <c r="R8" t="n">
-        <v>6845220</v>
+        <v>6845391</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1377,6 +1381,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124504151</v>
+        <v>124500069</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1538,20 +1547,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524256</v>
+        <v>524370</v>
       </c>
       <c r="R10" t="n">
-        <v>6844925</v>
+        <v>6845396</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,6 +1599,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,19 +1618,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124504565</v>
+        <v>124502783</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1642,7 +1665,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1656,13 +1679,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524227</v>
+        <v>524254</v>
       </c>
       <c r="R11" t="n">
-        <v>6844932</v>
+        <v>6845067</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124506146</v>
+        <v>124501719</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,50 +1753,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524148</v>
+        <v>524232</v>
       </c>
       <c r="R12" t="n">
-        <v>6845027</v>
+        <v>6845349</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,22 +1831,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124503027</v>
+        <v>124487564</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,34 +1859,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524345</v>
+        <v>524773</v>
       </c>
       <c r="R13" t="n">
-        <v>6845032</v>
+        <v>6845141</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1931,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124503276</v>
+        <v>124487121</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,37 +1961,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524472</v>
+        <v>524844</v>
       </c>
       <c r="R14" t="n">
-        <v>6845023</v>
+        <v>6845169</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2033,7 +2047,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124487514</v>
+        <v>124486832</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2073,13 +2087,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525016</v>
+        <v>524856</v>
       </c>
       <c r="R15" t="n">
-        <v>6845190</v>
+        <v>6845111</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,19 +2137,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124499873</v>
+        <v>124491805</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2171,17 +2185,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524451</v>
+        <v>524880</v>
       </c>
       <c r="R16" t="n">
-        <v>6845435</v>
+        <v>6845212</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2225,19 +2239,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124501516</v>
+        <v>124489815</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2273,17 +2287,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524237</v>
+        <v>525208</v>
       </c>
       <c r="R17" t="n">
-        <v>6845433</v>
+        <v>6845169</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2327,19 +2341,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124488923</v>
+        <v>124492513</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2379,13 +2393,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525312</v>
+        <v>524774</v>
       </c>
       <c r="R18" t="n">
-        <v>6845166</v>
+        <v>6845100</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,7 +2455,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124487283</v>
+        <v>124491822</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2481,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524836</v>
+        <v>524857</v>
       </c>
       <c r="R19" t="n">
-        <v>6845119</v>
+        <v>6845201</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2531,19 +2545,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124490091</v>
+        <v>124491246</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2583,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525149</v>
+        <v>525065</v>
       </c>
       <c r="R20" t="n">
-        <v>6845210</v>
+        <v>6845243</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2645,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124498529</v>
+        <v>124488157</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2661,34 +2675,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524365</v>
+        <v>524731</v>
       </c>
       <c r="R21" t="n">
-        <v>6845310</v>
+        <v>6845235</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2747,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124504945</v>
+        <v>124491548</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,34 +2777,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524203</v>
+        <v>524916</v>
       </c>
       <c r="R22" t="n">
-        <v>6844991</v>
+        <v>6845244</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2849,7 +2863,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124487467</v>
+        <v>124502991</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2885,14 +2899,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524805</v>
+        <v>524280</v>
       </c>
       <c r="R23" t="n">
-        <v>6845150</v>
+        <v>6845054</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2939,22 +2953,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124488326</v>
+        <v>124506146</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,38 +2977,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524734</v>
+        <v>524148</v>
       </c>
       <c r="R24" t="n">
-        <v>6845219</v>
+        <v>6845027</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3053,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124499127</v>
+        <v>124491531</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3089,17 +3112,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524559</v>
+        <v>524919</v>
       </c>
       <c r="R25" t="n">
-        <v>6845427</v>
+        <v>6845253</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,22 +3166,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124487039</v>
+        <v>124492717</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,50 +3190,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524908</v>
+        <v>524757</v>
       </c>
       <c r="R26" t="n">
-        <v>6845155</v>
+        <v>6845190</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3254,22 +3268,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124503388</v>
+        <v>124497941</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,50 +3292,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524214</v>
+        <v>524344</v>
       </c>
       <c r="R27" t="n">
-        <v>6844996</v>
+        <v>6845182</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3365,19 +3370,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124490720</v>
+        <v>124488923</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3417,13 +3422,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525133</v>
+        <v>525312</v>
       </c>
       <c r="R28" t="n">
-        <v>6845307</v>
+        <v>6845166</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3479,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124488157</v>
+        <v>124490965</v>
       </c>
       <c r="B29" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,21 +3500,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,13 +3524,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524731</v>
+        <v>525081</v>
       </c>
       <c r="R29" t="n">
-        <v>6845235</v>
+        <v>6845283</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3569,19 +3574,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124491917</v>
+        <v>124488535</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3621,13 +3626,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524852</v>
+        <v>525311</v>
       </c>
       <c r="R30" t="n">
-        <v>6845214</v>
+        <v>6845039</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,22 +3676,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124500112</v>
+        <v>124502910</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3695,38 +3700,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524447</v>
+        <v>524247</v>
       </c>
       <c r="R31" t="n">
-        <v>6845417</v>
+        <v>6845069</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3785,10 +3799,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124502991</v>
+        <v>124504565</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,38 +3811,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524280</v>
+        <v>524227</v>
       </c>
       <c r="R32" t="n">
-        <v>6845054</v>
+        <v>6844932</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3875,22 +3898,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124492635</v>
+        <v>124504545</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3899,38 +3922,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524790</v>
+        <v>524237</v>
       </c>
       <c r="R33" t="n">
-        <v>6845219</v>
+        <v>6844919</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3963,11 +3995,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3994,7 +4021,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124486962</v>
+        <v>124492072</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4029,7 +4056,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4043,10 +4070,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524859</v>
+        <v>524828</v>
       </c>
       <c r="R34" t="n">
-        <v>6845148</v>
+        <v>6845147</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4105,10 +4132,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124489792</v>
+        <v>124491477</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4117,47 +4144,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525215</v>
+        <v>524920</v>
       </c>
       <c r="R35" t="n">
-        <v>6845178</v>
+        <v>6845260</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4216,10 +4234,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124504545</v>
+        <v>124498070</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,47 +4246,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524237</v>
+        <v>524353</v>
       </c>
       <c r="R36" t="n">
-        <v>6844919</v>
+        <v>6845201</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4327,10 +4336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124500201</v>
+        <v>124487317</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4339,47 +4348,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524390</v>
+        <v>524829</v>
       </c>
       <c r="R37" t="n">
-        <v>6845406</v>
+        <v>6845141</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4412,11 +4412,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4443,7 +4438,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124490428</v>
+        <v>124488326</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4483,10 +4478,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525133</v>
+        <v>524734</v>
       </c>
       <c r="R38" t="n">
-        <v>6845201</v>
+        <v>6845219</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4545,10 +4540,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124499475</v>
+        <v>124490692</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4557,50 +4552,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524510</v>
+        <v>525103</v>
       </c>
       <c r="R39" t="n">
-        <v>6845430</v>
+        <v>6845194</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4644,22 +4630,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124492072</v>
+        <v>124500965</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,47 +4654,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524828</v>
+        <v>524308</v>
       </c>
       <c r="R40" t="n">
-        <v>6845147</v>
+        <v>6845471</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4767,10 +4744,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124493108</v>
+        <v>124503785</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,34 +4760,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524776</v>
+        <v>524244</v>
       </c>
       <c r="R41" t="n">
-        <v>6845248</v>
+        <v>6845004</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4845,11 +4822,6 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4862,22 +4834,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124501039</v>
+        <v>124486839</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,47 +4858,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524281</v>
+        <v>524872</v>
       </c>
       <c r="R42" t="n">
-        <v>6845383</v>
+        <v>6845107</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4985,7 +4948,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124492194</v>
+        <v>124488103</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5025,13 +4988,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524798</v>
+        <v>525146</v>
       </c>
       <c r="R43" t="n">
-        <v>6845206</v>
+        <v>6845150</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5075,22 +5038,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124497941</v>
+        <v>124491765</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5103,37 +5066,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524344</v>
+        <v>524904</v>
       </c>
       <c r="R44" t="n">
-        <v>6845182</v>
+        <v>6845207</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5189,10 +5152,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124501831</v>
+        <v>124498165</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5205,21 +5168,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5229,13 +5192,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524268</v>
+        <v>524349</v>
       </c>
       <c r="R45" t="n">
-        <v>6845351</v>
+        <v>6845225</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5279,22 +5242,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124502910</v>
+        <v>124504250</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5303,50 +5266,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524247</v>
+        <v>524436</v>
       </c>
       <c r="R46" t="n">
-        <v>6845069</v>
+        <v>6844930</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5376,6 +5330,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5390,22 +5349,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124504704</v>
+        <v>124486895</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5414,47 +5373,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524238</v>
+        <v>524856</v>
       </c>
       <c r="R47" t="n">
-        <v>6844943</v>
+        <v>6845128</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5513,10 +5463,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124487689</v>
+        <v>124487039</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5525,41 +5475,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524780</v>
+        <v>524908</v>
       </c>
       <c r="R48" t="n">
-        <v>6845188</v>
+        <v>6845155</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5603,22 +5562,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124498466</v>
+        <v>124504151</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5627,25 +5586,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5655,13 +5614,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524369</v>
+        <v>524256</v>
       </c>
       <c r="R49" t="n">
-        <v>6845293</v>
+        <v>6844925</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5705,22 +5664,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124501563</v>
+        <v>124504485</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5729,41 +5688,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524245</v>
+        <v>524261</v>
       </c>
       <c r="R50" t="n">
-        <v>6845371</v>
+        <v>6844909</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5807,22 +5775,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124502605</v>
+        <v>124504916</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5831,41 +5799,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524259</v>
+        <v>524219</v>
       </c>
       <c r="R51" t="n">
-        <v>6845061</v>
+        <v>6844970</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5909,22 +5886,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124500909</v>
+        <v>124499475</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5933,41 +5910,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524346</v>
+        <v>524510</v>
       </c>
       <c r="R52" t="n">
-        <v>6845458</v>
+        <v>6845430</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6011,19 +5997,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124489866</v>
+        <v>124498529</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6059,17 +6045,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525217</v>
+        <v>524365</v>
       </c>
       <c r="R53" t="n">
-        <v>6845195</v>
+        <v>6845310</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6113,19 +6099,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124498070</v>
+        <v>124488657</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6161,17 +6147,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524353</v>
+        <v>525312</v>
       </c>
       <c r="R54" t="n">
-        <v>6845201</v>
+        <v>6845117</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6215,19 +6201,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124487775</v>
+        <v>124489983</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6267,13 +6253,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525079</v>
+        <v>525195</v>
       </c>
       <c r="R55" t="n">
-        <v>6845164</v>
+        <v>6845198</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6317,22 +6303,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124493648</v>
+        <v>124490555</v>
       </c>
       <c r="B56" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6341,47 +6327,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524762</v>
+        <v>525142</v>
       </c>
       <c r="R56" t="n">
-        <v>6845231</v>
+        <v>6845241</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6414,6 +6391,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6440,7 +6422,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124489983</v>
+        <v>124499873</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6476,17 +6458,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525195</v>
+        <v>524451</v>
       </c>
       <c r="R57" t="n">
-        <v>6845198</v>
+        <v>6845435</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6530,22 +6512,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124505582</v>
+        <v>124499713</v>
       </c>
       <c r="B58" t="n">
-        <v>91032</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6558,21 +6540,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6582,13 +6564,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524121</v>
+        <v>524311</v>
       </c>
       <c r="R58" t="n">
-        <v>6845117</v>
+        <v>6845368</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6644,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124500926</v>
+        <v>124504089</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6656,41 +6638,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524345</v>
+        <v>524238</v>
       </c>
       <c r="R59" t="n">
-        <v>6845461</v>
+        <v>6844930</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6734,22 +6725,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124491805</v>
+        <v>124501563</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6762,37 +6753,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524880</v>
+        <v>524245</v>
       </c>
       <c r="R60" t="n">
-        <v>6845212</v>
+        <v>6845371</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6836,22 +6827,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124493358</v>
+        <v>124503680</v>
       </c>
       <c r="B61" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6864,34 +6855,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524793</v>
+        <v>524648</v>
       </c>
       <c r="R61" t="n">
-        <v>6845243</v>
+        <v>6845029</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6950,10 +6941,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124487293</v>
+        <v>124502522</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6962,50 +6953,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524948</v>
+        <v>524234</v>
       </c>
       <c r="R62" t="n">
-        <v>6845179</v>
+        <v>6845053</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7049,19 +7031,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124502783</v>
+        <v>124500794</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7094,26 +7076,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524254</v>
+        <v>524370</v>
       </c>
       <c r="R63" t="n">
-        <v>6845067</v>
+        <v>6845393</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7172,7 +7145,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124491822</v>
+        <v>124489002</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7212,13 +7185,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524857</v>
+        <v>525277</v>
       </c>
       <c r="R64" t="n">
-        <v>6845201</v>
+        <v>6845196</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7248,6 +7221,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7274,7 +7252,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124500965</v>
+        <v>124487467</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7310,14 +7288,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524308</v>
+        <v>524805</v>
       </c>
       <c r="R65" t="n">
-        <v>6845471</v>
+        <v>6845150</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7376,10 +7354,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124492032</v>
+        <v>124487771</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7388,50 +7366,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524881</v>
+        <v>524761</v>
       </c>
       <c r="R66" t="n">
-        <v>6845143</v>
+        <v>6845213</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7475,22 +7444,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499838</v>
+        <v>124490978</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7499,50 +7468,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524478</v>
+        <v>525086</v>
       </c>
       <c r="R67" t="n">
-        <v>6845426</v>
+        <v>6845224</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7586,19 +7546,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124489815</v>
+        <v>124487775</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7638,13 +7598,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525208</v>
+        <v>525079</v>
       </c>
       <c r="R68" t="n">
-        <v>6845169</v>
+        <v>6845164</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7688,19 +7648,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124492513</v>
+        <v>124491300</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7740,13 +7700,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524774</v>
+        <v>525015</v>
       </c>
       <c r="R69" t="n">
-        <v>6845100</v>
+        <v>6845263</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7802,10 +7762,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124490965</v>
+        <v>124489748</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7814,41 +7774,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525081</v>
+        <v>525230</v>
       </c>
       <c r="R70" t="n">
-        <v>6845283</v>
+        <v>6845187</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7892,19 +7861,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124489002</v>
+        <v>124491917</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7944,13 +7913,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525277</v>
+        <v>524852</v>
       </c>
       <c r="R71" t="n">
-        <v>6845196</v>
+        <v>6845214</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7980,11 +7949,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7999,22 +7963,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124492717</v>
+        <v>124498936</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8027,34 +7991,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524757</v>
+        <v>524415</v>
       </c>
       <c r="R72" t="n">
-        <v>6845190</v>
+        <v>6845335</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8113,10 +8077,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124490165</v>
+        <v>124504769</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8125,38 +8089,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525151</v>
+        <v>524231</v>
       </c>
       <c r="R73" t="n">
-        <v>6845190</v>
+        <v>6844957</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8215,10 +8188,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124498165</v>
+        <v>124490428</v>
       </c>
       <c r="B74" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8231,34 +8204,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524349</v>
+        <v>525133</v>
       </c>
       <c r="R74" t="n">
-        <v>6845225</v>
+        <v>6845201</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8317,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124503227</v>
+        <v>124487283</v>
       </c>
       <c r="B75" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8333,37 +8306,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524472</v>
+        <v>524836</v>
       </c>
       <c r="R75" t="n">
-        <v>6845023</v>
+        <v>6845119</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8419,10 +8392,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124503504</v>
+        <v>124505389</v>
       </c>
       <c r="B76" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8431,38 +8404,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524511</v>
+        <v>524115</v>
       </c>
       <c r="R76" t="n">
-        <v>6845029</v>
+        <v>6845050</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8521,7 +8503,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124501577</v>
+        <v>124501039</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8556,7 +8538,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8570,13 +8552,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524252</v>
+        <v>524281</v>
       </c>
       <c r="R77" t="n">
-        <v>6845387</v>
+        <v>6845383</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8620,22 +8602,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124504651</v>
+        <v>124503504</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8644,50 +8626,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524234</v>
+        <v>524511</v>
       </c>
       <c r="R78" t="n">
-        <v>6844921</v>
+        <v>6845029</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8743,10 +8716,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124504485</v>
+        <v>124503276</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8755,50 +8728,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524261</v>
+        <v>524472</v>
       </c>
       <c r="R79" t="n">
-        <v>6844909</v>
+        <v>6845023</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8854,10 +8818,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124500069</v>
+        <v>124505582</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8866,50 +8830,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524370</v>
+        <v>524121</v>
       </c>
       <c r="R80" t="n">
-        <v>6845396</v>
+        <v>6845117</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8939,11 +8894,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8970,10 +8920,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124491548</v>
+        <v>124499838</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8982,41 +8932,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524916</v>
+        <v>524478</v>
       </c>
       <c r="R81" t="n">
-        <v>6845244</v>
+        <v>6845426</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9060,22 +9019,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124499713</v>
+        <v>124504945</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9088,21 +9047,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9112,10 +9071,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524311</v>
+        <v>524203</v>
       </c>
       <c r="R82" t="n">
-        <v>6845368</v>
+        <v>6844991</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9174,10 +9133,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124490978</v>
+        <v>124493108</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9190,21 +9149,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9214,10 +9173,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525086</v>
+        <v>524776</v>
       </c>
       <c r="R83" t="n">
-        <v>6845224</v>
+        <v>6845248</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9250,6 +9209,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9276,10 +9240,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124486895</v>
+        <v>124500926</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9292,37 +9256,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524856</v>
+        <v>524345</v>
       </c>
       <c r="R84" t="n">
-        <v>6845128</v>
+        <v>6845461</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9378,10 +9342,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124501719</v>
+        <v>124503002</v>
       </c>
       <c r="B85" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9394,21 +9358,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9418,13 +9382,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524232</v>
+        <v>524333</v>
       </c>
       <c r="R85" t="n">
-        <v>6845349</v>
+        <v>6845022</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9468,19 +9432,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124502522</v>
+        <v>124504321</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9520,13 +9484,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524234</v>
+        <v>524276</v>
       </c>
       <c r="R86" t="n">
-        <v>6845053</v>
+        <v>6844888</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9570,22 +9534,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124504973</v>
+        <v>124491427</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9594,50 +9558,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524210</v>
+        <v>524946</v>
       </c>
       <c r="R87" t="n">
-        <v>6844954</v>
+        <v>6845286</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9681,22 +9636,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124499895</v>
+        <v>124487604</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9705,47 +9660,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524362</v>
+        <v>524781</v>
       </c>
       <c r="R88" t="n">
-        <v>6845391</v>
+        <v>6845167</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9778,11 +9724,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9809,7 +9750,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124504513</v>
+        <v>124504054</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9844,7 +9785,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9858,10 +9799,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524245</v>
+        <v>524683</v>
       </c>
       <c r="R89" t="n">
-        <v>6844924</v>
+        <v>6844956</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9920,10 +9861,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124487564</v>
+        <v>124503227</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9936,37 +9877,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524773</v>
+        <v>524472</v>
       </c>
       <c r="R90" t="n">
-        <v>6845141</v>
+        <v>6845023</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10022,10 +9963,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124502475</v>
+        <v>124487293</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10034,38 +9975,47 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524197</v>
+        <v>524948</v>
       </c>
       <c r="R91" t="n">
-        <v>6845056</v>
+        <v>6845179</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10124,10 +10074,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124498794</v>
+        <v>124499832</v>
       </c>
       <c r="B92" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10136,38 +10086,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524383</v>
+        <v>524327</v>
       </c>
       <c r="R92" t="n">
-        <v>6845264</v>
+        <v>6845386</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10226,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124488535</v>
+        <v>124492635</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10242,21 +10201,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10266,13 +10225,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525311</v>
+        <v>524790</v>
       </c>
       <c r="R93" t="n">
-        <v>6845039</v>
+        <v>6845219</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10302,6 +10261,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10280,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124487771</v>
+        <v>124500112</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10344,37 +10308,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524761</v>
+        <v>524447</v>
       </c>
       <c r="R94" t="n">
-        <v>6845213</v>
+        <v>6845417</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10418,19 +10382,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124498760</v>
+        <v>124500909</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10470,13 +10434,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524388</v>
+        <v>524346</v>
       </c>
       <c r="R95" t="n">
-        <v>6845283</v>
+        <v>6845458</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10532,7 +10496,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124486832</v>
+        <v>124502475</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10568,17 +10532,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524856</v>
+        <v>524197</v>
       </c>
       <c r="R96" t="n">
-        <v>6845111</v>
+        <v>6845056</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10622,22 +10586,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124498936</v>
+        <v>124491428</v>
       </c>
       <c r="B97" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10646,38 +10610,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524415</v>
+        <v>524954</v>
       </c>
       <c r="R97" t="n">
-        <v>6845335</v>
+        <v>6845241</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10736,10 +10709,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124504354</v>
+        <v>124498466</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10748,50 +10721,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524274</v>
+        <v>524369</v>
       </c>
       <c r="R98" t="n">
-        <v>6844889</v>
+        <v>6845293</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10835,22 +10799,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124503785</v>
+        <v>124489866</v>
       </c>
       <c r="B99" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10863,37 +10827,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524244</v>
+        <v>525217</v>
       </c>
       <c r="R99" t="n">
-        <v>6845004</v>
+        <v>6845195</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10949,10 +10913,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124487374</v>
+        <v>124498794</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10961,41 +10925,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524974</v>
+        <v>524383</v>
       </c>
       <c r="R100" t="n">
-        <v>6845191</v>
+        <v>6845264</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11039,22 +11003,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124491477</v>
+        <v>124492032</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11063,41 +11027,50 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524920</v>
+        <v>524881</v>
       </c>
       <c r="R101" t="n">
-        <v>6845260</v>
+        <v>6845143</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11141,22 +11114,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124504860</v>
+        <v>124503388</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11165,38 +11138,47 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524224</v>
+        <v>524214</v>
       </c>
       <c r="R102" t="n">
-        <v>6844971</v>
+        <v>6844996</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11243,22 +11225,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124503680</v>
+        <v>124504354</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11267,41 +11249,50 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524648</v>
+        <v>524274</v>
       </c>
       <c r="R103" t="n">
-        <v>6845029</v>
+        <v>6844889</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11345,19 +11336,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124491246</v>
+        <v>124501831</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11393,17 +11384,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>525065</v>
+        <v>524268</v>
       </c>
       <c r="R104" t="n">
-        <v>6845243</v>
+        <v>6845351</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11447,19 +11438,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124486839</v>
+        <v>124501516</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11495,14 +11486,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524872</v>
+        <v>524237</v>
       </c>
       <c r="R105" t="n">
-        <v>6845107</v>
+        <v>6845433</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11663,10 +11654,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124490692</v>
+        <v>124499480</v>
       </c>
       <c r="B107" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11675,38 +11666,47 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>525103</v>
+        <v>524365</v>
       </c>
       <c r="R107" t="n">
-        <v>6845194</v>
+        <v>6845400</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11739,6 +11739,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11765,10 +11770,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124491531</v>
+        <v>124486962</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11777,41 +11782,50 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524919</v>
+        <v>524859</v>
       </c>
       <c r="R108" t="n">
-        <v>6845253</v>
+        <v>6845148</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11867,10 +11881,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124492000</v>
+        <v>124501662</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11879,38 +11893,47 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524901</v>
+        <v>524272</v>
       </c>
       <c r="R109" t="n">
-        <v>6845216</v>
+        <v>6845365</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11957,22 +11980,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124487567</v>
+        <v>124504973</v>
       </c>
       <c r="B110" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11981,41 +12004,50 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>525000</v>
+        <v>524210</v>
       </c>
       <c r="R110" t="n">
-        <v>6845201</v>
+        <v>6844954</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12059,22 +12091,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124500865</v>
+        <v>124493648</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12083,38 +12115,47 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524350</v>
+        <v>524762</v>
       </c>
       <c r="R111" t="n">
-        <v>6845399</v>
+        <v>6845231</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12173,10 +12214,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124498544</v>
+        <v>124499127</v>
       </c>
       <c r="B112" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12189,21 +12230,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12213,13 +12254,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524364</v>
+        <v>524559</v>
       </c>
       <c r="R112" t="n">
-        <v>6845312</v>
+        <v>6845427</v>
       </c>
       <c r="S112" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12263,19 +12304,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124487121</v>
+        <v>124492000</v>
       </c>
       <c r="B113" t="n">
         <v>78810</v>
@@ -12315,10 +12356,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524844</v>
+        <v>524901</v>
       </c>
       <c r="R113" t="n">
-        <v>6845169</v>
+        <v>6845216</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12377,10 +12418,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124491294</v>
+        <v>124490527</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12393,37 +12434,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>525063</v>
+        <v>525139</v>
       </c>
       <c r="R114" t="n">
-        <v>6845234</v>
+        <v>6845241</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12453,6 +12499,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12467,22 +12518,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124490527</v>
+        <v>124500865</v>
       </c>
       <c r="B115" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12495,39 +12546,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>525139</v>
+        <v>524350</v>
       </c>
       <c r="R115" t="n">
-        <v>6845241</v>
+        <v>6845399</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12560,11 +12606,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12591,10 +12632,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124500794</v>
+        <v>124491320</v>
       </c>
       <c r="B116" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12603,41 +12644,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524370</v>
+        <v>525017</v>
       </c>
       <c r="R116" t="n">
-        <v>6845393</v>
+        <v>6845257</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12693,10 +12734,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124504916</v>
+        <v>124491387</v>
       </c>
       <c r="B117" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12705,47 +12746,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524219</v>
+        <v>524949</v>
       </c>
       <c r="R117" t="n">
-        <v>6844970</v>
+        <v>6845252</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12804,10 +12836,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124491428</v>
+        <v>124490720</v>
       </c>
       <c r="B118" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12816,50 +12848,41 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524954</v>
+        <v>525133</v>
       </c>
       <c r="R118" t="n">
-        <v>6845241</v>
+        <v>6845307</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12903,22 +12926,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124504054</v>
+        <v>124498544</v>
       </c>
       <c r="B119" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12927,47 +12950,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524683</v>
+        <v>524364</v>
       </c>
       <c r="R119" t="n">
-        <v>6844956</v>
+        <v>6845312</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13026,7 +13040,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124491765</v>
+        <v>124502605</v>
       </c>
       <c r="B120" t="n">
         <v>78810</v>
@@ -13062,17 +13076,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524904</v>
+        <v>524259</v>
       </c>
       <c r="R120" t="n">
-        <v>6845207</v>
+        <v>6845061</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13116,22 +13130,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124491300</v>
+        <v>124489670</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13140,41 +13154,50 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>525015</v>
+        <v>525247</v>
       </c>
       <c r="R121" t="n">
-        <v>6845263</v>
+        <v>6845194</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13230,10 +13253,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124504662</v>
+        <v>124501577</v>
       </c>
       <c r="B122" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13242,41 +13265,50 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524244</v>
+        <v>524252</v>
       </c>
       <c r="R122" t="n">
-        <v>6844920</v>
+        <v>6845387</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13332,10 +13364,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124500867</v>
+        <v>124500201</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13344,41 +13376,50 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524343</v>
+        <v>524390</v>
       </c>
       <c r="R123" t="n">
-        <v>6845433</v>
+        <v>6845406</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13408,6 +13449,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13434,7 +13480,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124504769</v>
+        <v>124504651</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -13469,7 +13515,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13483,13 +13529,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524231</v>
+        <v>524234</v>
       </c>
       <c r="R124" t="n">
-        <v>6844957</v>
+        <v>6844921</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13545,10 +13591,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124499832</v>
+        <v>124490091</v>
       </c>
       <c r="B125" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13557,47 +13603,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524327</v>
+        <v>525149</v>
       </c>
       <c r="R125" t="n">
-        <v>6845386</v>
+        <v>6845210</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13656,10 +13693,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124489748</v>
+        <v>124492194</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13668,47 +13705,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>525230</v>
+        <v>524798</v>
       </c>
       <c r="R126" t="n">
-        <v>6845187</v>
+        <v>6845206</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13767,7 +13795,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124487604</v>
+        <v>124490165</v>
       </c>
       <c r="B127" t="n">
         <v>78810</v>
@@ -13807,10 +13835,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524781</v>
+        <v>525151</v>
       </c>
       <c r="R127" t="n">
-        <v>6845167</v>
+        <v>6845190</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13869,10 +13897,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124487317</v>
+        <v>124489792</v>
       </c>
       <c r="B128" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13881,38 +13909,47 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524829</v>
+        <v>525215</v>
       </c>
       <c r="R128" t="n">
-        <v>6845141</v>
+        <v>6845178</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13971,7 +14008,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124488657</v>
+        <v>124487514</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14011,10 +14048,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>525312</v>
+        <v>525016</v>
       </c>
       <c r="R129" t="n">
-        <v>6845117</v>
+        <v>6845190</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14073,10 +14110,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124501662</v>
+        <v>124498760</v>
       </c>
       <c r="B130" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14085,47 +14122,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524272</v>
+        <v>524388</v>
       </c>
       <c r="R130" t="n">
-        <v>6845365</v>
+        <v>6845283</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14172,22 +14200,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124504089</v>
+        <v>124491294</v>
       </c>
       <c r="B131" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14196,47 +14224,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524238</v>
+        <v>525063</v>
       </c>
       <c r="R131" t="n">
-        <v>6844930</v>
+        <v>6845234</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14283,22 +14302,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124503002</v>
+        <v>124487374</v>
       </c>
       <c r="B132" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14311,37 +14330,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524333</v>
+        <v>524974</v>
       </c>
       <c r="R132" t="n">
-        <v>6845022</v>
+        <v>6845191</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14385,19 +14404,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124504321</v>
+        <v>124487689</v>
       </c>
       <c r="B133" t="n">
         <v>78810</v>
@@ -14433,17 +14452,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524276</v>
+        <v>524780</v>
       </c>
       <c r="R133" t="n">
-        <v>6844888</v>
+        <v>6845188</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14487,22 +14506,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124504250</v>
+        <v>124504513</v>
       </c>
       <c r="B134" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14511,38 +14530,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524436</v>
+        <v>524245</v>
       </c>
       <c r="R134" t="n">
-        <v>6844930</v>
+        <v>6844924</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14575,11 +14603,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14606,10 +14629,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124489670</v>
+        <v>124504860</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14618,50 +14641,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>525247</v>
+        <v>524224</v>
       </c>
       <c r="R135" t="n">
-        <v>6845194</v>
+        <v>6844971</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14705,22 +14719,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124499480</v>
+        <v>124487567</v>
       </c>
       <c r="B136" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14729,50 +14743,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524365</v>
+        <v>525000</v>
       </c>
       <c r="R136" t="n">
-        <v>6845400</v>
+        <v>6845201</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14802,11 +14807,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14821,12 +14821,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124504704</v>
+        <v>124490978</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524238</v>
+        <v>525086</v>
       </c>
       <c r="R2" t="n">
-        <v>6844943</v>
+        <v>6845224</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124503027</v>
+        <v>124500794</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524345</v>
+        <v>524370</v>
       </c>
       <c r="R3" t="n">
-        <v>6845032</v>
+        <v>6845393</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124500867</v>
+        <v>124489002</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524343</v>
+        <v>525277</v>
       </c>
       <c r="R4" t="n">
-        <v>6845433</v>
+        <v>6845196</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124491619</v>
+        <v>124490720</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1030,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524906</v>
+        <v>525133</v>
       </c>
       <c r="R5" t="n">
-        <v>6845220</v>
+        <v>6845307</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124493358</v>
+        <v>124487514</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524793</v>
+        <v>525016</v>
       </c>
       <c r="R6" t="n">
-        <v>6845243</v>
+        <v>6845190</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,19 +1178,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124504662</v>
+        <v>124501831</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1234,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524244</v>
+        <v>524268</v>
       </c>
       <c r="R7" t="n">
-        <v>6844920</v>
+        <v>6845351</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,19 +1280,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124499895</v>
+        <v>124492032</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1331,7 +1327,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1341,17 +1337,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524362</v>
+        <v>524881</v>
       </c>
       <c r="R8" t="n">
-        <v>6845391</v>
+        <v>6845143</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,11 +1377,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,22 +1391,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124492807</v>
+        <v>124500909</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,37 +1419,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524696</v>
+        <v>524346</v>
       </c>
       <c r="R9" t="n">
-        <v>6845140</v>
+        <v>6845458</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,22 +1493,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124500069</v>
+        <v>124488923</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,50 +1517,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524370</v>
+        <v>525312</v>
       </c>
       <c r="R10" t="n">
-        <v>6845396</v>
+        <v>6845166</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,11 +1581,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,22 +1595,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124502783</v>
+        <v>124497941</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,50 +1619,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524254</v>
+        <v>524344</v>
       </c>
       <c r="R11" t="n">
-        <v>6845067</v>
+        <v>6845182</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,22 +1697,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124501719</v>
+        <v>124499127</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524232</v>
+        <v>524559</v>
       </c>
       <c r="R12" t="n">
-        <v>6845349</v>
+        <v>6845427</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1843,7 +1811,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124487564</v>
+        <v>124487283</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1883,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524773</v>
+        <v>524836</v>
       </c>
       <c r="R13" t="n">
-        <v>6845141</v>
+        <v>6845119</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1945,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124487121</v>
+        <v>124504651</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,41 +1925,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524844</v>
+        <v>524234</v>
       </c>
       <c r="R14" t="n">
-        <v>6845169</v>
+        <v>6844921</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2047,7 +2024,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124486832</v>
+        <v>124501516</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2083,17 +2060,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524856</v>
+        <v>524237</v>
       </c>
       <c r="R15" t="n">
-        <v>6845111</v>
+        <v>6845433</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2137,22 +2114,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124491805</v>
+        <v>124503276</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,37 +2142,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524880</v>
+        <v>524472</v>
       </c>
       <c r="R16" t="n">
-        <v>6845212</v>
+        <v>6845023</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,7 +2228,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124489815</v>
+        <v>124487121</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2291,7 +2268,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525208</v>
+        <v>524844</v>
       </c>
       <c r="R17" t="n">
         <v>6845169</v>
@@ -2353,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124492513</v>
+        <v>124492635</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,21 +2346,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,13 +2370,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524774</v>
+        <v>524790</v>
       </c>
       <c r="R18" t="n">
-        <v>6845100</v>
+        <v>6845219</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,6 +2406,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2443,19 +2425,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124491822</v>
+        <v>124500965</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2491,14 +2473,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524857</v>
+        <v>524308</v>
       </c>
       <c r="R19" t="n">
-        <v>6845201</v>
+        <v>6845471</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2545,19 +2527,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124491246</v>
+        <v>124500867</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2593,17 +2575,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525065</v>
+        <v>524343</v>
       </c>
       <c r="R20" t="n">
-        <v>6845243</v>
+        <v>6845433</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2659,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124488157</v>
+        <v>124499713</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,34 +2657,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524731</v>
+        <v>524311</v>
       </c>
       <c r="R21" t="n">
-        <v>6845235</v>
+        <v>6845368</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2761,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124491548</v>
+        <v>124504151</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,41 +2755,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524916</v>
+        <v>524256</v>
       </c>
       <c r="R22" t="n">
-        <v>6845244</v>
+        <v>6844925</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2851,19 +2833,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124502991</v>
+        <v>124498760</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2903,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524280</v>
+        <v>524388</v>
       </c>
       <c r="R23" t="n">
-        <v>6845054</v>
+        <v>6845283</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2953,22 +2935,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124506146</v>
+        <v>124491320</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2977,47 +2959,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524148</v>
+        <v>525017</v>
       </c>
       <c r="R24" t="n">
-        <v>6845027</v>
+        <v>6845257</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3064,19 +3037,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124491531</v>
+        <v>124490097</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3116,13 +3089,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524919</v>
+        <v>525147</v>
       </c>
       <c r="R25" t="n">
-        <v>6845253</v>
+        <v>6845208</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3166,19 +3139,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124492717</v>
+        <v>124491477</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3218,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524757</v>
+        <v>524920</v>
       </c>
       <c r="R26" t="n">
-        <v>6845190</v>
+        <v>6845260</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3280,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124497941</v>
+        <v>124490692</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3292,41 +3265,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524344</v>
+        <v>525103</v>
       </c>
       <c r="R27" t="n">
-        <v>6845182</v>
+        <v>6845194</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3382,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124488923</v>
+        <v>124498936</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,37 +3371,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525312</v>
+        <v>524415</v>
       </c>
       <c r="R28" t="n">
-        <v>6845166</v>
+        <v>6845335</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3472,22 +3445,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124490965</v>
+        <v>124493108</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3500,21 +3473,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,13 +3497,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525081</v>
+        <v>524776</v>
       </c>
       <c r="R29" t="n">
-        <v>6845283</v>
+        <v>6845248</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3560,6 +3533,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3574,19 +3552,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124488535</v>
+        <v>124491294</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3626,13 +3604,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525311</v>
+        <v>525063</v>
       </c>
       <c r="R30" t="n">
-        <v>6845039</v>
+        <v>6845234</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3676,19 +3654,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124502910</v>
+        <v>124505389</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3723,7 +3701,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3737,13 +3715,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524247</v>
+        <v>524115</v>
       </c>
       <c r="R31" t="n">
-        <v>6845069</v>
+        <v>6845050</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3787,22 +3765,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124504565</v>
+        <v>124502475</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3811,50 +3789,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524227</v>
+        <v>524197</v>
       </c>
       <c r="R32" t="n">
-        <v>6844932</v>
+        <v>6845056</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3898,19 +3867,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124504545</v>
+        <v>124500069</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -3945,7 +3914,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3959,10 +3928,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524237</v>
+        <v>524370</v>
       </c>
       <c r="R33" t="n">
-        <v>6844919</v>
+        <v>6845396</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3995,6 +3964,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4021,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124492072</v>
+        <v>124492194</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4033,47 +4007,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524828</v>
+        <v>524798</v>
       </c>
       <c r="R34" t="n">
-        <v>6845147</v>
+        <v>6845206</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4132,10 +4097,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124491477</v>
+        <v>124506146</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4144,38 +4109,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524920</v>
+        <v>524148</v>
       </c>
       <c r="R35" t="n">
-        <v>6845260</v>
+        <v>6845027</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4234,10 +4208,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124498070</v>
+        <v>124504089</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4246,38 +4220,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524353</v>
+        <v>524238</v>
       </c>
       <c r="R36" t="n">
-        <v>6845201</v>
+        <v>6844930</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4324,19 +4307,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124487317</v>
+        <v>124487564</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4376,7 +4359,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524829</v>
+        <v>524773</v>
       </c>
       <c r="R37" t="n">
         <v>6845141</v>
@@ -4438,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124488326</v>
+        <v>124498165</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4454,34 +4437,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524734</v>
+        <v>524349</v>
       </c>
       <c r="R38" t="n">
-        <v>6845219</v>
+        <v>6845225</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4540,10 +4523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124490692</v>
+        <v>124486839</v>
       </c>
       <c r="B39" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4552,25 +4535,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4580,13 +4563,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525103</v>
+        <v>524872</v>
       </c>
       <c r="R39" t="n">
-        <v>6845194</v>
+        <v>6845107</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4630,22 +4613,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124500965</v>
+        <v>124504769</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4654,38 +4637,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524308</v>
+        <v>524231</v>
       </c>
       <c r="R40" t="n">
-        <v>6845471</v>
+        <v>6844957</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4744,7 +4736,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124503785</v>
+        <v>124504945</v>
       </c>
       <c r="B41" t="n">
         <v>57666</v>
@@ -4784,10 +4776,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524244</v>
+        <v>524203</v>
       </c>
       <c r="R41" t="n">
-        <v>6845004</v>
+        <v>6844991</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4834,22 +4826,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124486839</v>
+        <v>124486962</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4858,41 +4850,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524872</v>
+        <v>524859</v>
       </c>
       <c r="R42" t="n">
-        <v>6845107</v>
+        <v>6845148</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4936,22 +4937,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124488103</v>
+        <v>124501563</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4964,37 +4965,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525146</v>
+        <v>524245</v>
       </c>
       <c r="R43" t="n">
-        <v>6845150</v>
+        <v>6845371</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5050,10 +5051,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124491765</v>
+        <v>124487567</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5066,21 +5067,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5090,13 +5091,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524904</v>
+        <v>525000</v>
       </c>
       <c r="R44" t="n">
-        <v>6845207</v>
+        <v>6845201</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5140,22 +5141,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124498165</v>
+        <v>124492072</v>
       </c>
       <c r="B45" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5164,38 +5165,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524349</v>
+        <v>524828</v>
       </c>
       <c r="R45" t="n">
-        <v>6845225</v>
+        <v>6845147</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5254,10 +5264,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124504250</v>
+        <v>124487775</v>
       </c>
       <c r="B46" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5266,41 +5276,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524436</v>
+        <v>525079</v>
       </c>
       <c r="R46" t="n">
-        <v>6844930</v>
+        <v>6845164</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5330,11 +5340,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5349,19 +5354,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124486895</v>
+        <v>124489815</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5401,10 +5406,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524856</v>
+        <v>525208</v>
       </c>
       <c r="R47" t="n">
-        <v>6845128</v>
+        <v>6845169</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5463,10 +5468,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124487039</v>
+        <v>124499873</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5475,47 +5480,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524908</v>
+        <v>524451</v>
       </c>
       <c r="R48" t="n">
-        <v>6845155</v>
+        <v>6845435</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5574,10 +5570,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124504151</v>
+        <v>124487771</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5586,41 +5582,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524256</v>
+        <v>524761</v>
       </c>
       <c r="R49" t="n">
-        <v>6844925</v>
+        <v>6845213</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5664,22 +5660,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124504485</v>
+        <v>124487604</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5688,47 +5684,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524261</v>
+        <v>524781</v>
       </c>
       <c r="R50" t="n">
-        <v>6844909</v>
+        <v>6845167</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5787,10 +5774,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124504916</v>
+        <v>124489866</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5799,50 +5786,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524219</v>
+        <v>525217</v>
       </c>
       <c r="R51" t="n">
-        <v>6844970</v>
+        <v>6845195</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5886,22 +5864,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124499475</v>
+        <v>124504860</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5910,50 +5888,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524510</v>
+        <v>524224</v>
       </c>
       <c r="R52" t="n">
-        <v>6845430</v>
+        <v>6844971</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5997,19 +5966,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124498529</v>
+        <v>124504321</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6049,13 +6018,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524365</v>
+        <v>524276</v>
       </c>
       <c r="R53" t="n">
-        <v>6845310</v>
+        <v>6844888</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6099,22 +6068,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124488657</v>
+        <v>124504704</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6123,41 +6092,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525312</v>
+        <v>524238</v>
       </c>
       <c r="R54" t="n">
-        <v>6845117</v>
+        <v>6844943</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6201,19 +6179,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124489983</v>
+        <v>124491548</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6253,10 +6231,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525195</v>
+        <v>524916</v>
       </c>
       <c r="R55" t="n">
-        <v>6845198</v>
+        <v>6845244</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6315,7 +6293,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124490555</v>
+        <v>124491619</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6355,13 +6333,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525142</v>
+        <v>524906</v>
       </c>
       <c r="R56" t="n">
-        <v>6845241</v>
+        <v>6845220</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6391,11 +6369,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6410,22 +6383,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124499873</v>
+        <v>124504916</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6434,41 +6407,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524451</v>
+        <v>524219</v>
       </c>
       <c r="R57" t="n">
-        <v>6845435</v>
+        <v>6844970</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6512,22 +6494,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124499713</v>
+        <v>124491427</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6540,37 +6522,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524311</v>
+        <v>524946</v>
       </c>
       <c r="R58" t="n">
-        <v>6845368</v>
+        <v>6845286</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6614,22 +6596,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124504089</v>
+        <v>124488326</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6638,47 +6620,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524238</v>
+        <v>524734</v>
       </c>
       <c r="R59" t="n">
-        <v>6844930</v>
+        <v>6845219</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6725,22 +6698,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124501563</v>
+        <v>124499895</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6749,41 +6722,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524245</v>
+        <v>524362</v>
       </c>
       <c r="R60" t="n">
-        <v>6845371</v>
+        <v>6845391</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6813,6 +6795,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6827,19 +6814,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124503680</v>
+        <v>124490165</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -6875,14 +6862,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524648</v>
+        <v>525151</v>
       </c>
       <c r="R61" t="n">
-        <v>6845029</v>
+        <v>6845190</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6941,10 +6928,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124502522</v>
+        <v>124493358</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6957,34 +6944,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524234</v>
+        <v>524793</v>
       </c>
       <c r="R62" t="n">
-        <v>6845053</v>
+        <v>6845243</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7043,7 +7030,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124500794</v>
+        <v>124504565</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7076,20 +7063,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524370</v>
+        <v>524227</v>
       </c>
       <c r="R63" t="n">
-        <v>6845393</v>
+        <v>6844932</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7133,22 +7129,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124489002</v>
+        <v>124503227</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7161,37 +7157,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525277</v>
+        <v>524472</v>
       </c>
       <c r="R64" t="n">
-        <v>6845196</v>
+        <v>6845023</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7221,11 +7217,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7240,22 +7231,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124487467</v>
+        <v>124501577</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7264,38 +7255,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524805</v>
+        <v>524252</v>
       </c>
       <c r="R65" t="n">
-        <v>6845150</v>
+        <v>6845387</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7354,10 +7354,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124487771</v>
+        <v>124493648</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7366,41 +7366,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524761</v>
+        <v>524762</v>
       </c>
       <c r="R66" t="n">
-        <v>6845213</v>
+        <v>6845231</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7444,22 +7453,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124490978</v>
+        <v>124503002</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7472,34 +7481,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525086</v>
+        <v>524333</v>
       </c>
       <c r="R67" t="n">
-        <v>6845224</v>
+        <v>6845022</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7558,7 +7567,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124487775</v>
+        <v>124491822</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7598,13 +7607,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525079</v>
+        <v>524857</v>
       </c>
       <c r="R68" t="n">
-        <v>6845164</v>
+        <v>6845201</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7660,10 +7669,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124491300</v>
+        <v>124487039</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7672,41 +7681,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525015</v>
+        <v>524908</v>
       </c>
       <c r="R69" t="n">
-        <v>6845263</v>
+        <v>6845155</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7762,7 +7780,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124489748</v>
+        <v>124499838</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7797,7 +7815,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7807,17 +7825,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525230</v>
+        <v>524478</v>
       </c>
       <c r="R70" t="n">
-        <v>6845187</v>
+        <v>6845426</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7861,22 +7879,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124491917</v>
+        <v>124488157</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7889,21 +7907,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7913,10 +7931,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524852</v>
+        <v>524731</v>
       </c>
       <c r="R71" t="n">
-        <v>6845214</v>
+        <v>6845235</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7975,7 +7993,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124498936</v>
+        <v>124503504</v>
       </c>
       <c r="B72" t="n">
         <v>78546</v>
@@ -8015,10 +8033,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524415</v>
+        <v>524511</v>
       </c>
       <c r="R72" t="n">
-        <v>6845335</v>
+        <v>6845029</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8077,7 +8095,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124504769</v>
+        <v>124500201</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8112,7 +8130,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8126,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524231</v>
+        <v>524390</v>
       </c>
       <c r="R73" t="n">
-        <v>6844957</v>
+        <v>6845406</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8162,6 +8180,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8188,10 +8211,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124490428</v>
+        <v>124499475</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8200,41 +8223,50 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525133</v>
+        <v>524510</v>
       </c>
       <c r="R74" t="n">
-        <v>6845201</v>
+        <v>6845430</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8278,19 +8310,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124487283</v>
+        <v>124489983</v>
       </c>
       <c r="B75" t="n">
         <v>78810</v>
@@ -8330,10 +8362,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524836</v>
+        <v>525195</v>
       </c>
       <c r="R75" t="n">
-        <v>6845119</v>
+        <v>6845198</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8392,10 +8424,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124505389</v>
+        <v>124487467</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8404,47 +8436,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524115</v>
+        <v>524805</v>
       </c>
       <c r="R76" t="n">
-        <v>6845050</v>
+        <v>6845150</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8503,7 +8526,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124501039</v>
+        <v>124489670</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8538,7 +8561,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8548,14 +8571,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524281</v>
+        <v>525247</v>
       </c>
       <c r="R77" t="n">
-        <v>6845383</v>
+        <v>6845194</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8614,10 +8637,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124503504</v>
+        <v>124488103</v>
       </c>
       <c r="B78" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8630,37 +8653,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524511</v>
+        <v>525146</v>
       </c>
       <c r="R78" t="n">
-        <v>6845029</v>
+        <v>6845150</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8704,22 +8727,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124503276</v>
+        <v>124504485</v>
       </c>
       <c r="B79" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8728,41 +8751,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524472</v>
+        <v>524261</v>
       </c>
       <c r="R79" t="n">
-        <v>6845023</v>
+        <v>6844909</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8818,10 +8850,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124505582</v>
+        <v>124502991</v>
       </c>
       <c r="B80" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8834,21 +8866,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8858,13 +8890,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524121</v>
+        <v>524280</v>
       </c>
       <c r="R80" t="n">
-        <v>6845117</v>
+        <v>6845054</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8908,19 +8940,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124499838</v>
+        <v>124504513</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8955,7 +8987,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8969,13 +9001,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524478</v>
+        <v>524245</v>
       </c>
       <c r="R81" t="n">
-        <v>6845426</v>
+        <v>6844924</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9019,22 +9051,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124504945</v>
+        <v>124491805</v>
       </c>
       <c r="B82" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9047,34 +9079,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524203</v>
+        <v>524880</v>
       </c>
       <c r="R82" t="n">
-        <v>6844991</v>
+        <v>6845212</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9133,10 +9165,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124493108</v>
+        <v>124491917</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9149,21 +9181,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9173,10 +9205,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524776</v>
+        <v>524852</v>
       </c>
       <c r="R83" t="n">
-        <v>6845248</v>
+        <v>6845214</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9209,11 +9241,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9240,10 +9267,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124500926</v>
+        <v>124486895</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9256,37 +9283,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524345</v>
+        <v>524856</v>
       </c>
       <c r="R84" t="n">
-        <v>6845461</v>
+        <v>6845128</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9342,10 +9369,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124503002</v>
+        <v>124498466</v>
       </c>
       <c r="B85" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9358,21 +9385,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9382,10 +9409,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524333</v>
+        <v>524369</v>
       </c>
       <c r="R85" t="n">
-        <v>6845022</v>
+        <v>6845293</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9444,7 +9471,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124504321</v>
+        <v>124490965</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9480,14 +9507,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524276</v>
+        <v>525081</v>
       </c>
       <c r="R86" t="n">
-        <v>6844888</v>
+        <v>6845283</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9546,10 +9573,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124491427</v>
+        <v>124490527</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9562,34 +9589,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524946</v>
+        <v>525139</v>
       </c>
       <c r="R87" t="n">
-        <v>6845286</v>
+        <v>6845241</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9622,6 +9654,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9648,7 +9685,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124487604</v>
+        <v>124502522</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9684,14 +9721,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524781</v>
+        <v>524234</v>
       </c>
       <c r="R88" t="n">
-        <v>6845167</v>
+        <v>6845053</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9750,7 +9787,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124504054</v>
+        <v>124501662</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9785,7 +9822,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9799,10 +9836,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524683</v>
+        <v>524272</v>
       </c>
       <c r="R89" t="n">
-        <v>6844956</v>
+        <v>6845365</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9849,22 +9886,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124503227</v>
+        <v>124489748</v>
       </c>
       <c r="B90" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9873,41 +9910,50 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524472</v>
+        <v>525230</v>
       </c>
       <c r="R90" t="n">
-        <v>6845023</v>
+        <v>6845187</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9963,10 +10009,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124487293</v>
+        <v>124498529</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9975,50 +10021,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524948</v>
+        <v>524365</v>
       </c>
       <c r="R91" t="n">
-        <v>6845179</v>
+        <v>6845310</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10062,22 +10099,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124499832</v>
+        <v>124504662</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10086,50 +10123,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524327</v>
+        <v>524244</v>
       </c>
       <c r="R92" t="n">
-        <v>6845386</v>
+        <v>6844920</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10185,10 +10213,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124492635</v>
+        <v>124502605</v>
       </c>
       <c r="B93" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10201,37 +10229,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524790</v>
+        <v>524259</v>
       </c>
       <c r="R93" t="n">
-        <v>6845219</v>
+        <v>6845061</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10261,11 +10289,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10280,22 +10303,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124500112</v>
+        <v>124491387</v>
       </c>
       <c r="B94" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10308,37 +10331,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524447</v>
+        <v>524949</v>
       </c>
       <c r="R94" t="n">
-        <v>6845417</v>
+        <v>6845252</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10382,19 +10405,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124500909</v>
+        <v>124492717</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10430,17 +10453,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524346</v>
+        <v>524757</v>
       </c>
       <c r="R95" t="n">
-        <v>6845458</v>
+        <v>6845190</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10496,10 +10519,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124502475</v>
+        <v>124503027</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10512,21 +10535,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10536,13 +10559,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524197</v>
+        <v>524345</v>
       </c>
       <c r="R96" t="n">
-        <v>6845056</v>
+        <v>6845032</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10586,19 +10609,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124491428</v>
+        <v>124489792</v>
       </c>
       <c r="B97" t="n">
         <v>98101</v>
@@ -10633,7 +10656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10647,10 +10670,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524954</v>
+        <v>525215</v>
       </c>
       <c r="R97" t="n">
-        <v>6845241</v>
+        <v>6845178</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10709,7 +10732,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124498466</v>
+        <v>124491765</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10745,14 +10768,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524369</v>
+        <v>524904</v>
       </c>
       <c r="R98" t="n">
-        <v>6845293</v>
+        <v>6845207</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10811,7 +10834,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124489866</v>
+        <v>124487374</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10851,10 +10874,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>525217</v>
+        <v>524974</v>
       </c>
       <c r="R99" t="n">
-        <v>6845195</v>
+        <v>6845191</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10913,10 +10936,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124498794</v>
+        <v>124490091</v>
       </c>
       <c r="B100" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10925,38 +10948,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524383</v>
+        <v>525149</v>
       </c>
       <c r="R100" t="n">
-        <v>6845264</v>
+        <v>6845210</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -11015,10 +11038,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124492032</v>
+        <v>124500865</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11027,47 +11050,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524881</v>
+        <v>524350</v>
       </c>
       <c r="R101" t="n">
-        <v>6845143</v>
+        <v>6845399</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11126,10 +11140,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124503388</v>
+        <v>124488535</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11138,50 +11152,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524214</v>
+        <v>525311</v>
       </c>
       <c r="R102" t="n">
-        <v>6844996</v>
+        <v>6845039</v>
       </c>
       <c r="S102" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11237,7 +11242,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124504354</v>
+        <v>124501039</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11272,7 +11277,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11286,10 +11291,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524274</v>
+        <v>524281</v>
       </c>
       <c r="R103" t="n">
-        <v>6844889</v>
+        <v>6845383</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11348,10 +11353,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124501831</v>
+        <v>124499480</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11360,41 +11365,50 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524268</v>
+        <v>524365</v>
       </c>
       <c r="R104" t="n">
-        <v>6845351</v>
+        <v>6845400</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11424,6 +11438,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11438,22 +11457,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124501516</v>
+        <v>124504973</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11462,41 +11481,50 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524237</v>
+        <v>524210</v>
       </c>
       <c r="R105" t="n">
-        <v>6845433</v>
+        <v>6844954</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11540,22 +11568,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124490097</v>
+        <v>124487293</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11564,38 +11592,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>525147</v>
+        <v>524948</v>
       </c>
       <c r="R106" t="n">
-        <v>6845208</v>
+        <v>6845179</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11654,10 +11691,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124499480</v>
+        <v>124500112</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11666,50 +11703,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524365</v>
+        <v>524447</v>
       </c>
       <c r="R107" t="n">
-        <v>6845400</v>
+        <v>6845417</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11739,11 +11767,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11758,22 +11781,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124486962</v>
+        <v>124498070</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11782,47 +11805,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524859</v>
+        <v>524353</v>
       </c>
       <c r="R108" t="n">
-        <v>6845148</v>
+        <v>6845201</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11881,10 +11895,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124501662</v>
+        <v>124487689</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11893,47 +11907,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524272</v>
+        <v>524780</v>
       </c>
       <c r="R109" t="n">
-        <v>6845365</v>
+        <v>6845188</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11980,22 +11985,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124504973</v>
+        <v>124492513</v>
       </c>
       <c r="B110" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12004,50 +12009,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524210</v>
+        <v>524774</v>
       </c>
       <c r="R110" t="n">
-        <v>6844954</v>
+        <v>6845100</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12091,22 +12087,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124493648</v>
+        <v>124487317</v>
       </c>
       <c r="B111" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12115,50 +12111,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524762</v>
+        <v>524829</v>
       </c>
       <c r="R111" t="n">
-        <v>6845231</v>
+        <v>6845141</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12202,22 +12189,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124499127</v>
+        <v>124504354</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12226,38 +12213,47 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524559</v>
+        <v>524274</v>
       </c>
       <c r="R112" t="n">
-        <v>6845427</v>
+        <v>6844889</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12316,10 +12312,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124492000</v>
+        <v>124500926</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12332,37 +12328,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524901</v>
+        <v>524345</v>
       </c>
       <c r="R113" t="n">
-        <v>6845216</v>
+        <v>6845461</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12418,10 +12414,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124490527</v>
+        <v>124492807</v>
       </c>
       <c r="B114" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12434,39 +12430,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>525139</v>
+        <v>524696</v>
       </c>
       <c r="R114" t="n">
-        <v>6845241</v>
+        <v>6845140</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12499,11 +12490,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12530,7 +12516,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124500865</v>
+        <v>124490428</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -12566,17 +12552,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524350</v>
+        <v>525133</v>
       </c>
       <c r="R115" t="n">
-        <v>6845399</v>
+        <v>6845201</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12620,22 +12606,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124491320</v>
+        <v>124486832</v>
       </c>
       <c r="B116" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12644,25 +12630,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12672,10 +12658,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>525017</v>
+        <v>524856</v>
       </c>
       <c r="R116" t="n">
-        <v>6845257</v>
+        <v>6845111</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12722,19 +12708,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124491387</v>
+        <v>124490555</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -12774,13 +12760,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524949</v>
+        <v>525142</v>
       </c>
       <c r="R117" t="n">
-        <v>6845252</v>
+        <v>6845241</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12810,6 +12796,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12824,19 +12815,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124490720</v>
+        <v>124491246</v>
       </c>
       <c r="B118" t="n">
         <v>78810</v>
@@ -12876,13 +12867,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>525133</v>
+        <v>525065</v>
       </c>
       <c r="R118" t="n">
-        <v>6845307</v>
+        <v>6845243</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12926,22 +12917,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124498544</v>
+        <v>124491531</v>
       </c>
       <c r="B119" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12954,37 +12945,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524364</v>
+        <v>524919</v>
       </c>
       <c r="R119" t="n">
-        <v>6845312</v>
+        <v>6845253</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13040,10 +13031,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124502605</v>
+        <v>124498544</v>
       </c>
       <c r="B120" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13056,21 +13047,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13080,13 +13071,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524259</v>
+        <v>524364</v>
       </c>
       <c r="R120" t="n">
-        <v>6845061</v>
+        <v>6845312</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13130,22 +13121,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124489670</v>
+        <v>124492000</v>
       </c>
       <c r="B121" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13154,50 +13145,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>525247</v>
+        <v>524901</v>
       </c>
       <c r="R121" t="n">
-        <v>6845194</v>
+        <v>6845216</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13241,22 +13223,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124501577</v>
+        <v>124498794</v>
       </c>
       <c r="B122" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13265,47 +13247,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524252</v>
+        <v>524383</v>
       </c>
       <c r="R122" t="n">
-        <v>6845387</v>
+        <v>6845264</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13364,7 +13337,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124500201</v>
+        <v>124504545</v>
       </c>
       <c r="B123" t="n">
         <v>98101</v>
@@ -13413,10 +13386,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524390</v>
+        <v>524237</v>
       </c>
       <c r="R123" t="n">
-        <v>6845406</v>
+        <v>6844919</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13449,11 +13422,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13480,7 +13448,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124504651</v>
+        <v>124503388</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -13515,7 +13483,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13529,13 +13497,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524234</v>
+        <v>524214</v>
       </c>
       <c r="R124" t="n">
-        <v>6844921</v>
+        <v>6844996</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13579,19 +13547,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124490091</v>
+        <v>124503680</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -13627,14 +13595,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>525149</v>
+        <v>524648</v>
       </c>
       <c r="R125" t="n">
-        <v>6845210</v>
+        <v>6845029</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13693,10 +13661,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124492194</v>
+        <v>124505582</v>
       </c>
       <c r="B126" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13709,37 +13677,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524798</v>
+        <v>524121</v>
       </c>
       <c r="R126" t="n">
-        <v>6845206</v>
+        <v>6845117</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13795,10 +13763,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124490165</v>
+        <v>124503785</v>
       </c>
       <c r="B127" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13811,34 +13779,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>525151</v>
+        <v>524244</v>
       </c>
       <c r="R127" t="n">
-        <v>6845190</v>
+        <v>6845004</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13885,19 +13853,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124489792</v>
+        <v>124502910</v>
       </c>
       <c r="B128" t="n">
         <v>98101</v>
@@ -13932,7 +13900,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -13942,17 +13910,17 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>525215</v>
+        <v>524247</v>
       </c>
       <c r="R128" t="n">
-        <v>6845178</v>
+        <v>6845069</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13996,22 +13964,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124487514</v>
+        <v>124501719</v>
       </c>
       <c r="B129" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14024,34 +13992,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>525016</v>
+        <v>524232</v>
       </c>
       <c r="R129" t="n">
-        <v>6845190</v>
+        <v>6845349</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14110,10 +14078,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124498760</v>
+        <v>124504250</v>
       </c>
       <c r="B130" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14122,25 +14090,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14150,10 +14118,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524388</v>
+        <v>524436</v>
       </c>
       <c r="R130" t="n">
-        <v>6845283</v>
+        <v>6844930</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14186,6 +14154,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14212,7 +14185,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124491294</v>
+        <v>124488657</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14252,13 +14225,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>525063</v>
+        <v>525312</v>
       </c>
       <c r="R131" t="n">
-        <v>6845234</v>
+        <v>6845117</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14302,19 +14275,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124487374</v>
+        <v>124491300</v>
       </c>
       <c r="B132" t="n">
         <v>78810</v>
@@ -14354,13 +14327,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524974</v>
+        <v>525015</v>
       </c>
       <c r="R132" t="n">
-        <v>6845191</v>
+        <v>6845263</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14416,10 +14389,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124487689</v>
+        <v>124499832</v>
       </c>
       <c r="B133" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14428,38 +14401,47 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524780</v>
+        <v>524327</v>
       </c>
       <c r="R133" t="n">
-        <v>6845188</v>
+        <v>6845386</v>
       </c>
       <c r="S133" t="n">
         <v>20</v>
@@ -14518,7 +14500,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124504513</v>
+        <v>124491428</v>
       </c>
       <c r="B134" t="n">
         <v>98101</v>
@@ -14553,7 +14535,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14563,14 +14545,14 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524245</v>
+        <v>524954</v>
       </c>
       <c r="R134" t="n">
-        <v>6844924</v>
+        <v>6845241</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14629,10 +14611,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124504860</v>
+        <v>124504054</v>
       </c>
       <c r="B135" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14641,38 +14623,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524224</v>
+        <v>524683</v>
       </c>
       <c r="R135" t="n">
-        <v>6844971</v>
+        <v>6844956</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -14731,10 +14722,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124487567</v>
+        <v>124502783</v>
       </c>
       <c r="B136" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14743,38 +14734,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>525000</v>
+        <v>524254</v>
       </c>
       <c r="R136" t="n">
-        <v>6845201</v>
+        <v>6845067</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124501831</v>
+        <v>124488923</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1226,17 +1226,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524268</v>
+        <v>525312</v>
       </c>
       <c r="R7" t="n">
-        <v>6845351</v>
+        <v>6845166</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124492032</v>
+        <v>124499127</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,47 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524881</v>
+        <v>524559</v>
       </c>
       <c r="R8" t="n">
-        <v>6845143</v>
+        <v>6845427</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124488923</v>
+        <v>124492032</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,41 +1508,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525312</v>
+        <v>524881</v>
       </c>
       <c r="R10" t="n">
-        <v>6845166</v>
+        <v>6845143</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124499127</v>
+        <v>124501831</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524559</v>
+        <v>524268</v>
       </c>
       <c r="R12" t="n">
-        <v>6845427</v>
+        <v>6845351</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124503276</v>
+        <v>124492635</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,37 +2142,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524472</v>
+        <v>524790</v>
       </c>
       <c r="R16" t="n">
-        <v>6845023</v>
+        <v>6845219</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,6 +2202,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2228,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124487121</v>
+        <v>124500965</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2264,14 +2269,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524844</v>
+        <v>524308</v>
       </c>
       <c r="R17" t="n">
-        <v>6845169</v>
+        <v>6845471</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2330,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124492635</v>
+        <v>124503276</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,37 +2351,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524790</v>
+        <v>524472</v>
       </c>
       <c r="R18" t="n">
-        <v>6845219</v>
+        <v>6845023</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2406,11 +2411,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,7 +2437,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124500965</v>
+        <v>124487121</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2473,14 +2473,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524308</v>
+        <v>524844</v>
       </c>
       <c r="R19" t="n">
-        <v>6845471</v>
+        <v>6845169</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124500867</v>
+        <v>124498760</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524343</v>
+        <v>524388</v>
       </c>
       <c r="R20" t="n">
-        <v>6845433</v>
+        <v>6845283</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124498760</v>
+        <v>124490097</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2881,17 +2881,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524388</v>
+        <v>525147</v>
       </c>
       <c r="R23" t="n">
-        <v>6845283</v>
+        <v>6845208</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,12 +2935,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124490097</v>
+        <v>124500867</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3085,17 +3085,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525147</v>
+        <v>524343</v>
       </c>
       <c r="R25" t="n">
-        <v>6845208</v>
+        <v>6845433</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3139,22 +3139,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124491477</v>
+        <v>124490692</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524920</v>
+        <v>525103</v>
       </c>
       <c r="R26" t="n">
-        <v>6845260</v>
+        <v>6845194</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124490692</v>
+        <v>124493108</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,25 +3265,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525103</v>
+        <v>524776</v>
       </c>
       <c r="R27" t="n">
-        <v>6845194</v>
+        <v>6845248</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3329,6 +3329,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3355,10 +3360,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124498936</v>
+        <v>124491294</v>
       </c>
       <c r="B28" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,34 +3376,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524415</v>
+        <v>525063</v>
       </c>
       <c r="R28" t="n">
-        <v>6845335</v>
+        <v>6845234</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3457,10 +3462,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124493108</v>
+        <v>124505389</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,38 +3474,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524776</v>
+        <v>524115</v>
       </c>
       <c r="R29" t="n">
-        <v>6845248</v>
+        <v>6845050</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3533,11 +3547,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,7 +3573,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124491294</v>
+        <v>124502475</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3600,17 +3609,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525063</v>
+        <v>524197</v>
       </c>
       <c r="R30" t="n">
-        <v>6845234</v>
+        <v>6845056</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3654,19 +3663,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124505389</v>
+        <v>124500069</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3701,7 +3710,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3715,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524115</v>
+        <v>524370</v>
       </c>
       <c r="R31" t="n">
-        <v>6845050</v>
+        <v>6845396</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,6 +3760,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,7 +3791,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124502475</v>
+        <v>124491477</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3813,17 +3827,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524197</v>
+        <v>524920</v>
       </c>
       <c r="R32" t="n">
-        <v>6845056</v>
+        <v>6845260</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3867,22 +3881,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124500069</v>
+        <v>124498936</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3891,47 +3905,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524370</v>
+        <v>524415</v>
       </c>
       <c r="R33" t="n">
-        <v>6845396</v>
+        <v>6845335</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3964,11 +3969,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3995,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124492194</v>
+        <v>124504769</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4007,38 +4007,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524798</v>
+        <v>524231</v>
       </c>
       <c r="R34" t="n">
-        <v>6845206</v>
+        <v>6844957</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4097,10 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124506146</v>
+        <v>124487564</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4109,47 +4118,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524148</v>
+        <v>524773</v>
       </c>
       <c r="R35" t="n">
-        <v>6845027</v>
+        <v>6845141</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124504089</v>
+        <v>124498165</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4220,47 +4220,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524238</v>
+        <v>524349</v>
       </c>
       <c r="R36" t="n">
-        <v>6844930</v>
+        <v>6845225</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4307,19 +4298,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124487564</v>
+        <v>124486839</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4359,13 +4350,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524773</v>
+        <v>524872</v>
       </c>
       <c r="R37" t="n">
-        <v>6845141</v>
+        <v>6845107</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4409,22 +4400,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124498165</v>
+        <v>124492194</v>
       </c>
       <c r="B38" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4437,34 +4428,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524349</v>
+        <v>524798</v>
       </c>
       <c r="R38" t="n">
-        <v>6845225</v>
+        <v>6845206</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4523,10 +4514,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124486839</v>
+        <v>124504945</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4539,37 +4530,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524872</v>
+        <v>524203</v>
       </c>
       <c r="R39" t="n">
-        <v>6845107</v>
+        <v>6844991</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4613,19 +4604,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124504769</v>
+        <v>124506146</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4660,7 +4651,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4674,10 +4665,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524231</v>
+        <v>524148</v>
       </c>
       <c r="R40" t="n">
-        <v>6844957</v>
+        <v>6845027</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4736,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124504945</v>
+        <v>124504089</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4748,38 +4739,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524203</v>
+        <v>524238</v>
       </c>
       <c r="R41" t="n">
-        <v>6844991</v>
+        <v>6844930</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4826,22 +4826,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124486962</v>
+        <v>124501563</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4850,50 +4850,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524859</v>
+        <v>524245</v>
       </c>
       <c r="R42" t="n">
-        <v>6845148</v>
+        <v>6845371</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4937,22 +4928,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124501563</v>
+        <v>124487567</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4965,34 +4956,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524245</v>
+        <v>525000</v>
       </c>
       <c r="R43" t="n">
-        <v>6845371</v>
+        <v>6845201</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5051,10 +5042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124487567</v>
+        <v>124486962</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5063,41 +5054,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525000</v>
+        <v>524859</v>
       </c>
       <c r="R44" t="n">
-        <v>6845201</v>
+        <v>6845148</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5141,12 +5141,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124491917</v>
+        <v>124490527</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9181,37 +9181,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524852</v>
+        <v>525139</v>
       </c>
       <c r="R83" t="n">
-        <v>6845214</v>
+        <v>6845241</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9241,6 +9246,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9255,19 +9265,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124486895</v>
+        <v>124502522</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9303,14 +9313,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524856</v>
+        <v>524234</v>
       </c>
       <c r="R84" t="n">
-        <v>6845128</v>
+        <v>6845053</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9471,7 +9481,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124490965</v>
+        <v>124486895</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9511,13 +9521,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525081</v>
+        <v>524856</v>
       </c>
       <c r="R86" t="n">
-        <v>6845283</v>
+        <v>6845128</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9561,22 +9571,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124490527</v>
+        <v>124490965</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9589,39 +9599,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525139</v>
+        <v>525081</v>
       </c>
       <c r="R87" t="n">
-        <v>6845241</v>
+        <v>6845283</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9654,11 +9659,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9685,10 +9685,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124502522</v>
+        <v>124501662</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9697,38 +9697,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524234</v>
+        <v>524272</v>
       </c>
       <c r="R88" t="n">
-        <v>6845053</v>
+        <v>6845365</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9775,22 +9784,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124501662</v>
+        <v>124498529</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9799,47 +9808,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524272</v>
+        <v>524365</v>
       </c>
       <c r="R89" t="n">
-        <v>6845365</v>
+        <v>6845310</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9886,22 +9886,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124489748</v>
+        <v>124491917</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9910,47 +9910,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525230</v>
+        <v>524852</v>
       </c>
       <c r="R90" t="n">
-        <v>6845187</v>
+        <v>6845214</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -10009,10 +10000,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124498529</v>
+        <v>124489748</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10021,38 +10012,47 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524365</v>
+        <v>525230</v>
       </c>
       <c r="R91" t="n">
-        <v>6845310</v>
+        <v>6845187</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -10111,7 +10111,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124504662</v>
+        <v>124491387</v>
       </c>
       <c r="B92" t="n">
         <v>78810</v>
@@ -10147,17 +10147,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524244</v>
+        <v>524949</v>
       </c>
       <c r="R92" t="n">
-        <v>6844920</v>
+        <v>6845252</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124491387</v>
+        <v>124503027</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10331,34 +10331,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524949</v>
+        <v>524345</v>
       </c>
       <c r="R94" t="n">
-        <v>6845252</v>
+        <v>6845032</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10417,7 +10417,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124492717</v>
+        <v>124504662</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10453,17 +10453,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524757</v>
+        <v>524244</v>
       </c>
       <c r="R95" t="n">
-        <v>6845190</v>
+        <v>6844920</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124503027</v>
+        <v>124492717</v>
       </c>
       <c r="B96" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10535,34 +10535,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524345</v>
+        <v>524757</v>
       </c>
       <c r="R96" t="n">
-        <v>6845032</v>
+        <v>6845190</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -11895,7 +11895,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124487689</v>
+        <v>124487317</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524780</v>
+        <v>524829</v>
       </c>
       <c r="R109" t="n">
-        <v>6845188</v>
+        <v>6845141</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11997,7 +11997,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124492513</v>
+        <v>124487689</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524774</v>
+        <v>524780</v>
       </c>
       <c r="R110" t="n">
-        <v>6845100</v>
+        <v>6845188</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12087,19 +12087,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124487317</v>
+        <v>124492513</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -12139,13 +12139,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524829</v>
+        <v>524774</v>
       </c>
       <c r="R111" t="n">
-        <v>6845141</v>
+        <v>6845100</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12189,22 +12189,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124504354</v>
+        <v>124490555</v>
       </c>
       <c r="B112" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12213,47 +12213,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524274</v>
+        <v>525142</v>
       </c>
       <c r="R112" t="n">
-        <v>6844889</v>
+        <v>6845241</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12286,6 +12277,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12312,10 +12308,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124500926</v>
+        <v>124498544</v>
       </c>
       <c r="B113" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12328,21 +12324,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12352,13 +12348,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524345</v>
+        <v>524364</v>
       </c>
       <c r="R113" t="n">
-        <v>6845461</v>
+        <v>6845312</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12414,10 +12410,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124492807</v>
+        <v>124491246</v>
       </c>
       <c r="B114" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12430,21 +12426,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12454,13 +12450,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524696</v>
+        <v>525065</v>
       </c>
       <c r="R114" t="n">
-        <v>6845140</v>
+        <v>6845243</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12504,19 +12500,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124490428</v>
+        <v>124492000</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -12556,10 +12552,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>525133</v>
+        <v>524901</v>
       </c>
       <c r="R115" t="n">
-        <v>6845201</v>
+        <v>6845216</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12618,10 +12614,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124486832</v>
+        <v>124492807</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12634,21 +12630,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12658,13 +12654,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524856</v>
+        <v>524696</v>
       </c>
       <c r="R116" t="n">
-        <v>6845111</v>
+        <v>6845140</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12708,19 +12704,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124490555</v>
+        <v>124491531</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -12760,13 +12756,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>525142</v>
+        <v>524919</v>
       </c>
       <c r="R117" t="n">
-        <v>6845241</v>
+        <v>6845253</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12796,11 +12792,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12815,19 +12806,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124491246</v>
+        <v>124490428</v>
       </c>
       <c r="B118" t="n">
         <v>78810</v>
@@ -12867,10 +12858,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>525065</v>
+        <v>525133</v>
       </c>
       <c r="R118" t="n">
-        <v>6845243</v>
+        <v>6845201</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12929,7 +12920,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124491531</v>
+        <v>124486832</v>
       </c>
       <c r="B119" t="n">
         <v>78810</v>
@@ -12969,13 +12960,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524919</v>
+        <v>524856</v>
       </c>
       <c r="R119" t="n">
-        <v>6845253</v>
+        <v>6845111</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13031,10 +13022,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124498544</v>
+        <v>124504354</v>
       </c>
       <c r="B120" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13043,41 +13034,50 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524364</v>
+        <v>524274</v>
       </c>
       <c r="R120" t="n">
-        <v>6845312</v>
+        <v>6844889</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13121,22 +13121,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124492000</v>
+        <v>124500926</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13149,37 +13149,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524901</v>
+        <v>524345</v>
       </c>
       <c r="R121" t="n">
-        <v>6845216</v>
+        <v>6845461</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124491428</v>
+        <v>124504054</v>
       </c>
       <c r="B134" t="n">
         <v>98101</v>
@@ -14535,7 +14535,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14545,14 +14545,14 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524954</v>
+        <v>524683</v>
       </c>
       <c r="R134" t="n">
-        <v>6845241</v>
+        <v>6844956</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14611,7 +14611,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124504054</v>
+        <v>124502783</v>
       </c>
       <c r="B135" t="n">
         <v>98101</v>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524683</v>
+        <v>524254</v>
       </c>
       <c r="R135" t="n">
-        <v>6844956</v>
+        <v>6845067</v>
       </c>
       <c r="S135" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14710,19 +14710,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124502783</v>
+        <v>124491428</v>
       </c>
       <c r="B136" t="n">
         <v>98101</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524254</v>
+        <v>524954</v>
       </c>
       <c r="R136" t="n">
-        <v>6845067</v>
+        <v>6845241</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14821,12 +14821,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124490978</v>
+        <v>124487604</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525086</v>
+        <v>524781</v>
       </c>
       <c r="R2" t="n">
-        <v>6845224</v>
+        <v>6845167</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124500794</v>
+        <v>124488103</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524370</v>
+        <v>525146</v>
       </c>
       <c r="R3" t="n">
-        <v>6845393</v>
+        <v>6845150</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124489002</v>
+        <v>124487317</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525277</v>
+        <v>524829</v>
       </c>
       <c r="R4" t="n">
-        <v>6845196</v>
+        <v>6845141</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124490720</v>
+        <v>124499838</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,41 +993,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525133</v>
+        <v>524478</v>
       </c>
       <c r="R5" t="n">
-        <v>6845307</v>
+        <v>6845426</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124487514</v>
+        <v>124505389</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1104,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525016</v>
+        <v>524115</v>
       </c>
       <c r="R6" t="n">
-        <v>6845190</v>
+        <v>6845050</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124488923</v>
+        <v>124504513</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,41 +1215,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525312</v>
+        <v>524245</v>
       </c>
       <c r="R7" t="n">
-        <v>6845166</v>
+        <v>6844924</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,22 +1302,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124499127</v>
+        <v>124498936</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1330,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524559</v>
+        <v>524415</v>
       </c>
       <c r="R8" t="n">
-        <v>6845427</v>
+        <v>6845335</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1404,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124500909</v>
+        <v>124490527</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,37 +1432,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524346</v>
+        <v>525139</v>
       </c>
       <c r="R9" t="n">
-        <v>6845458</v>
+        <v>6845241</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,6 +1497,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,19 +1516,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124492032</v>
+        <v>124489670</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1531,7 +1563,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1545,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524881</v>
+        <v>525247</v>
       </c>
       <c r="R10" t="n">
-        <v>6845143</v>
+        <v>6845194</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497941</v>
+        <v>124487293</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,41 +1651,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524344</v>
+        <v>524948</v>
       </c>
       <c r="R11" t="n">
-        <v>6845182</v>
+        <v>6845179</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1697,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124501831</v>
+        <v>124499713</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524268</v>
+        <v>524311</v>
       </c>
       <c r="R12" t="n">
-        <v>6845351</v>
+        <v>6845368</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1799,19 +1840,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124487283</v>
+        <v>124492717</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1851,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524836</v>
+        <v>524757</v>
       </c>
       <c r="R13" t="n">
-        <v>6845119</v>
+        <v>6845190</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1913,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124504651</v>
+        <v>124491805</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,50 +1966,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524234</v>
+        <v>524880</v>
       </c>
       <c r="R14" t="n">
-        <v>6844921</v>
+        <v>6845212</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2024,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124501516</v>
+        <v>124491294</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2060,17 +2092,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524237</v>
+        <v>525063</v>
       </c>
       <c r="R15" t="n">
-        <v>6845433</v>
+        <v>6845234</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2114,22 +2146,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124492635</v>
+        <v>124491300</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,13 +2198,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524790</v>
+        <v>525015</v>
       </c>
       <c r="R16" t="n">
-        <v>6845219</v>
+        <v>6845263</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2221,19 +2248,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124500965</v>
+        <v>124498466</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2273,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524308</v>
+        <v>524369</v>
       </c>
       <c r="R17" t="n">
-        <v>6845471</v>
+        <v>6845293</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2335,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124503276</v>
+        <v>124504860</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524472</v>
+        <v>524224</v>
       </c>
       <c r="R18" t="n">
-        <v>6845023</v>
+        <v>6844971</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124487121</v>
+        <v>124502991</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2473,14 +2500,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524844</v>
+        <v>524280</v>
       </c>
       <c r="R19" t="n">
-        <v>6845169</v>
+        <v>6845054</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2527,19 +2554,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124498760</v>
+        <v>124502605</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2579,13 +2606,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524388</v>
+        <v>524259</v>
       </c>
       <c r="R20" t="n">
-        <v>6845283</v>
+        <v>6845061</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2629,22 +2656,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124499713</v>
+        <v>124503227</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,13 +2708,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524311</v>
+        <v>524472</v>
       </c>
       <c r="R21" t="n">
-        <v>6845368</v>
+        <v>6845023</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2743,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124504151</v>
+        <v>124504250</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,25 +2782,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,13 +2810,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524256</v>
+        <v>524436</v>
       </c>
       <c r="R22" t="n">
-        <v>6844925</v>
+        <v>6844930</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,6 +2846,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2833,22 +2865,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124490097</v>
+        <v>124499480</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,41 +2889,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525147</v>
+        <v>524365</v>
       </c>
       <c r="R23" t="n">
-        <v>6845208</v>
+        <v>6845400</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2921,6 +2962,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2935,22 +2981,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124491320</v>
+        <v>124486962</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,38 +3005,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525017</v>
+        <v>524859</v>
       </c>
       <c r="R24" t="n">
-        <v>6845257</v>
+        <v>6845148</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3037,19 +3092,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124500867</v>
+        <v>124500865</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3089,13 +3144,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524343</v>
+        <v>524350</v>
       </c>
       <c r="R25" t="n">
-        <v>6845433</v>
+        <v>6845399</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3139,22 +3194,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124490692</v>
+        <v>124502522</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,38 +3218,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525103</v>
+        <v>524234</v>
       </c>
       <c r="R26" t="n">
-        <v>6845194</v>
+        <v>6845053</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3253,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124493108</v>
+        <v>124491765</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3269,21 +3324,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3348,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524776</v>
+        <v>524904</v>
       </c>
       <c r="R27" t="n">
-        <v>6845248</v>
+        <v>6845207</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3329,11 +3384,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3360,7 +3410,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124491294</v>
+        <v>124491531</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3400,13 +3450,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525063</v>
+        <v>524919</v>
       </c>
       <c r="R28" t="n">
-        <v>6845234</v>
+        <v>6845253</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3462,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124505389</v>
+        <v>124498794</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3474,47 +3524,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524115</v>
+        <v>524383</v>
       </c>
       <c r="R29" t="n">
-        <v>6845050</v>
+        <v>6845264</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3573,7 +3614,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124502475</v>
+        <v>124486832</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3609,17 +3650,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524197</v>
+        <v>524856</v>
       </c>
       <c r="R30" t="n">
-        <v>6845056</v>
+        <v>6845111</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3663,22 +3704,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124500069</v>
+        <v>124487374</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3687,50 +3728,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524370</v>
+        <v>524974</v>
       </c>
       <c r="R31" t="n">
-        <v>6845396</v>
+        <v>6845191</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3760,11 +3792,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3779,22 +3806,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124491477</v>
+        <v>124500112</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3807,37 +3834,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524920</v>
+        <v>524447</v>
       </c>
       <c r="R32" t="n">
-        <v>6845260</v>
+        <v>6845417</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3881,22 +3908,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124498936</v>
+        <v>124505582</v>
       </c>
       <c r="B33" t="n">
-        <v>78546</v>
+        <v>91032</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3909,21 +3936,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3933,13 +3960,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524415</v>
+        <v>524121</v>
       </c>
       <c r="R33" t="n">
-        <v>6845335</v>
+        <v>6845117</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3995,10 +4022,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124504769</v>
+        <v>124490965</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4007,50 +4034,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524231</v>
+        <v>525081</v>
       </c>
       <c r="R34" t="n">
-        <v>6844957</v>
+        <v>6845283</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4094,19 +4112,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124487564</v>
+        <v>124486895</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4146,10 +4164,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524773</v>
+        <v>524856</v>
       </c>
       <c r="R35" t="n">
-        <v>6845141</v>
+        <v>6845128</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4208,10 +4226,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124498165</v>
+        <v>124490692</v>
       </c>
       <c r="B36" t="n">
-        <v>78546</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4220,38 +4238,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524349</v>
+        <v>525103</v>
       </c>
       <c r="R36" t="n">
-        <v>6845225</v>
+        <v>6845194</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4310,7 +4328,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124486839</v>
+        <v>124500867</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4346,17 +4364,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524872</v>
+        <v>524343</v>
       </c>
       <c r="R37" t="n">
-        <v>6845107</v>
+        <v>6845433</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4400,19 +4418,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124492194</v>
+        <v>124487564</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4452,10 +4470,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524798</v>
+        <v>524773</v>
       </c>
       <c r="R38" t="n">
-        <v>6845206</v>
+        <v>6845141</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4514,10 +4532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124504945</v>
+        <v>124491917</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4530,34 +4548,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524203</v>
+        <v>524852</v>
       </c>
       <c r="R39" t="n">
-        <v>6844991</v>
+        <v>6845214</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4616,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124506146</v>
+        <v>124491619</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4628,47 +4646,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524148</v>
+        <v>524906</v>
       </c>
       <c r="R40" t="n">
-        <v>6845027</v>
+        <v>6845220</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4727,10 +4736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124504089</v>
+        <v>124503785</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4739,47 +4748,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524238</v>
+        <v>524244</v>
       </c>
       <c r="R41" t="n">
-        <v>6844930</v>
+        <v>6845004</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4838,10 +4838,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124501563</v>
+        <v>124502910</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4850,38 +4850,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524245</v>
+        <v>524247</v>
       </c>
       <c r="R42" t="n">
-        <v>6845371</v>
+        <v>6845069</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4940,10 +4949,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124487567</v>
+        <v>124506146</v>
       </c>
       <c r="B43" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4952,41 +4961,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525000</v>
+        <v>524148</v>
       </c>
       <c r="R43" t="n">
-        <v>6845201</v>
+        <v>6845027</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5030,19 +5048,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124486962</v>
+        <v>124489748</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5077,7 +5095,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5091,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524859</v>
+        <v>525230</v>
       </c>
       <c r="R44" t="n">
-        <v>6845148</v>
+        <v>6845187</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5153,7 +5171,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124492072</v>
+        <v>124499832</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5188,7 +5206,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5198,14 +5216,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524828</v>
+        <v>524327</v>
       </c>
       <c r="R45" t="n">
-        <v>6845147</v>
+        <v>6845386</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5264,10 +5282,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124487775</v>
+        <v>124492032</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5276,38 +5294,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525079</v>
+        <v>524881</v>
       </c>
       <c r="R46" t="n">
-        <v>6845164</v>
+        <v>6845143</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5366,7 +5393,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124489815</v>
+        <v>124490428</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5406,10 +5433,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525208</v>
+        <v>525133</v>
       </c>
       <c r="R47" t="n">
-        <v>6845169</v>
+        <v>6845201</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5468,7 +5495,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124499873</v>
+        <v>124490978</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5504,17 +5531,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524451</v>
+        <v>525086</v>
       </c>
       <c r="R48" t="n">
-        <v>6845435</v>
+        <v>6845224</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5558,19 +5585,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124487771</v>
+        <v>124498760</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5606,14 +5633,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524761</v>
+        <v>524388</v>
       </c>
       <c r="R49" t="n">
-        <v>6845213</v>
+        <v>6845283</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5672,10 +5699,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124487604</v>
+        <v>124503388</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5684,38 +5711,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524781</v>
+        <v>524214</v>
       </c>
       <c r="R50" t="n">
-        <v>6845167</v>
+        <v>6844996</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5762,19 +5798,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124489866</v>
+        <v>124492513</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5814,10 +5850,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525217</v>
+        <v>524774</v>
       </c>
       <c r="R51" t="n">
-        <v>6845195</v>
+        <v>6845100</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5876,10 +5912,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124504860</v>
+        <v>124492635</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5892,34 +5928,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524224</v>
+        <v>524790</v>
       </c>
       <c r="R52" t="n">
-        <v>6844971</v>
+        <v>6845219</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5952,6 +5988,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5978,10 +6019,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124504321</v>
+        <v>124493358</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5994,37 +6035,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524276</v>
+        <v>524793</v>
       </c>
       <c r="R53" t="n">
-        <v>6844888</v>
+        <v>6845243</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6068,22 +6109,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124504704</v>
+        <v>124487771</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6092,47 +6133,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524238</v>
+        <v>524761</v>
       </c>
       <c r="R54" t="n">
-        <v>6844943</v>
+        <v>6845213</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6191,7 +6223,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124491548</v>
+        <v>124490720</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6231,13 +6263,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524916</v>
+        <v>525133</v>
       </c>
       <c r="R55" t="n">
-        <v>6845244</v>
+        <v>6845307</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6281,22 +6313,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124491619</v>
+        <v>124501719</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6309,37 +6341,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524906</v>
+        <v>524232</v>
       </c>
       <c r="R56" t="n">
-        <v>6845220</v>
+        <v>6845349</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6383,22 +6415,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124504916</v>
+        <v>124504321</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6407,50 +6439,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524219</v>
+        <v>524276</v>
       </c>
       <c r="R57" t="n">
-        <v>6844970</v>
+        <v>6844888</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6494,22 +6517,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124491427</v>
+        <v>124504545</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6518,41 +6541,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524946</v>
+        <v>524237</v>
       </c>
       <c r="R58" t="n">
-        <v>6845286</v>
+        <v>6844919</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6596,22 +6628,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124488326</v>
+        <v>124501039</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6620,41 +6652,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524734</v>
+        <v>524281</v>
       </c>
       <c r="R59" t="n">
-        <v>6845219</v>
+        <v>6845383</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6698,19 +6739,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124499895</v>
+        <v>124500201</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6745,7 +6786,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6759,10 +6800,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524362</v>
+        <v>524390</v>
       </c>
       <c r="R60" t="n">
-        <v>6845391</v>
+        <v>6845406</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6799,7 +6840,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>I avverkningsanmälan A 8590.</t>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6826,10 +6867,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124490165</v>
+        <v>124504485</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6838,38 +6879,47 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525151</v>
+        <v>524261</v>
       </c>
       <c r="R61" t="n">
-        <v>6845190</v>
+        <v>6844909</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6928,10 +6978,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124493358</v>
+        <v>124500909</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6944,37 +6994,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524793</v>
+        <v>524346</v>
       </c>
       <c r="R62" t="n">
-        <v>6845243</v>
+        <v>6845458</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7030,10 +7080,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124504565</v>
+        <v>124503504</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7042,47 +7092,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524227</v>
+        <v>524511</v>
       </c>
       <c r="R63" t="n">
-        <v>6844932</v>
+        <v>6845029</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7141,10 +7182,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124503227</v>
+        <v>124504151</v>
       </c>
       <c r="B64" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7153,25 +7194,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7181,13 +7222,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524472</v>
+        <v>524256</v>
       </c>
       <c r="R64" t="n">
-        <v>6845023</v>
+        <v>6844925</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7231,22 +7272,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124501577</v>
+        <v>124491246</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7255,47 +7296,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524252</v>
+        <v>525065</v>
       </c>
       <c r="R65" t="n">
-        <v>6845387</v>
+        <v>6845243</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7354,10 +7386,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124493648</v>
+        <v>124491822</v>
       </c>
       <c r="B66" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7366,50 +7398,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524762</v>
+        <v>524857</v>
       </c>
       <c r="R66" t="n">
-        <v>6845231</v>
+        <v>6845201</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7465,10 +7488,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124503002</v>
+        <v>124489792</v>
       </c>
       <c r="B67" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7477,38 +7500,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524333</v>
+        <v>525215</v>
       </c>
       <c r="R67" t="n">
-        <v>6845022</v>
+        <v>6845178</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7567,7 +7599,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124491822</v>
+        <v>124491387</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7607,10 +7639,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524857</v>
+        <v>524949</v>
       </c>
       <c r="R68" t="n">
-        <v>6845201</v>
+        <v>6845252</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7657,22 +7689,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124487039</v>
+        <v>124487775</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7681,47 +7713,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524908</v>
+        <v>525079</v>
       </c>
       <c r="R69" t="n">
-        <v>6845155</v>
+        <v>6845164</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7780,10 +7803,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124499838</v>
+        <v>124490097</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7792,50 +7815,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524478</v>
+        <v>525147</v>
       </c>
       <c r="R70" t="n">
-        <v>6845426</v>
+        <v>6845208</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7891,10 +7905,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124488157</v>
+        <v>124492000</v>
       </c>
       <c r="B71" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7907,21 +7921,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7931,10 +7945,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524731</v>
+        <v>524901</v>
       </c>
       <c r="R71" t="n">
-        <v>6845235</v>
+        <v>6845216</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7993,10 +8007,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124503504</v>
+        <v>124500926</v>
       </c>
       <c r="B72" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8009,21 +8023,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8033,13 +8047,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524511</v>
+        <v>524345</v>
       </c>
       <c r="R72" t="n">
-        <v>6845029</v>
+        <v>6845461</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8095,7 +8109,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124500201</v>
+        <v>124500069</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8130,7 +8144,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8144,10 +8158,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524390</v>
+        <v>524370</v>
       </c>
       <c r="R73" t="n">
-        <v>6845406</v>
+        <v>6845396</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8184,7 +8198,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Fyra meters hänsyn har tagits.</t>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8211,10 +8225,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124499475</v>
+        <v>124491320</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8223,50 +8237,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524510</v>
+        <v>525017</v>
       </c>
       <c r="R74" t="n">
-        <v>6845430</v>
+        <v>6845257</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8322,10 +8327,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124489983</v>
+        <v>124487039</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8334,41 +8339,50 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>525195</v>
+        <v>524908</v>
       </c>
       <c r="R75" t="n">
-        <v>6845198</v>
+        <v>6845155</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8412,22 +8426,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124487467</v>
+        <v>124503002</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8440,34 +8454,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524805</v>
+        <v>524333</v>
       </c>
       <c r="R76" t="n">
-        <v>6845150</v>
+        <v>6845022</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8526,7 +8540,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124489670</v>
+        <v>124504565</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8561,7 +8575,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8571,17 +8585,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525247</v>
+        <v>524227</v>
       </c>
       <c r="R77" t="n">
-        <v>6845194</v>
+        <v>6844932</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8625,22 +8639,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124488103</v>
+        <v>124504704</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8649,41 +8663,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525146</v>
+        <v>524238</v>
       </c>
       <c r="R78" t="n">
-        <v>6845150</v>
+        <v>6844943</v>
       </c>
       <c r="S78" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8727,19 +8750,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124504485</v>
+        <v>124499895</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8774,7 +8797,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8788,10 +8811,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524261</v>
+        <v>524362</v>
       </c>
       <c r="R79" t="n">
-        <v>6844909</v>
+        <v>6845391</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8824,6 +8847,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8850,7 +8878,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124502991</v>
+        <v>124488657</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8886,17 +8914,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524280</v>
+        <v>525312</v>
       </c>
       <c r="R80" t="n">
-        <v>6845054</v>
+        <v>6845117</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8952,10 +8980,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124504513</v>
+        <v>124489002</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8964,50 +8992,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524245</v>
+        <v>525277</v>
       </c>
       <c r="R81" t="n">
-        <v>6844924</v>
+        <v>6845196</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9037,6 +9056,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9051,19 +9075,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124491805</v>
+        <v>124499873</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9099,17 +9123,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524880</v>
+        <v>524451</v>
       </c>
       <c r="R82" t="n">
-        <v>6845212</v>
+        <v>6845435</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9153,22 +9177,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124490527</v>
+        <v>124492072</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9177,31 +9201,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9210,13 +9238,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525139</v>
+        <v>524828</v>
       </c>
       <c r="R83" t="n">
-        <v>6845241</v>
+        <v>6845147</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9246,11 +9274,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9265,22 +9288,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124502522</v>
+        <v>124503027</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9293,21 +9316,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9317,10 +9340,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524234</v>
+        <v>524345</v>
       </c>
       <c r="R84" t="n">
-        <v>6845053</v>
+        <v>6845032</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9379,7 +9402,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124498466</v>
+        <v>124500965</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9419,10 +9442,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524369</v>
+        <v>524308</v>
       </c>
       <c r="R85" t="n">
-        <v>6845293</v>
+        <v>6845471</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9481,10 +9504,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124486895</v>
+        <v>124501563</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9497,37 +9520,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524856</v>
+        <v>524245</v>
       </c>
       <c r="R86" t="n">
-        <v>6845128</v>
+        <v>6845371</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9571,22 +9594,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124490965</v>
+        <v>124504354</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9595,38 +9618,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525081</v>
+        <v>524274</v>
       </c>
       <c r="R87" t="n">
-        <v>6845283</v>
+        <v>6844889</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9685,7 +9717,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124501662</v>
+        <v>124504916</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9720,7 +9752,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9734,10 +9766,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524272</v>
+        <v>524219</v>
       </c>
       <c r="R88" t="n">
-        <v>6845365</v>
+        <v>6844970</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9784,19 +9816,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124498529</v>
+        <v>124503680</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -9836,10 +9868,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524365</v>
+        <v>524648</v>
       </c>
       <c r="R89" t="n">
-        <v>6845310</v>
+        <v>6845029</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9898,10 +9930,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124491917</v>
+        <v>124488157</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9914,21 +9946,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9938,10 +9970,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524852</v>
+        <v>524731</v>
       </c>
       <c r="R90" t="n">
-        <v>6845214</v>
+        <v>6845235</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -10000,10 +10032,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124489748</v>
+        <v>124487514</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10012,50 +10044,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525230</v>
+        <v>525016</v>
       </c>
       <c r="R91" t="n">
-        <v>6845187</v>
+        <v>6845190</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10099,22 +10122,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124491387</v>
+        <v>124492807</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10127,21 +10150,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10151,13 +10174,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>524949</v>
+        <v>524696</v>
       </c>
       <c r="R92" t="n">
-        <v>6845252</v>
+        <v>6845140</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10201,19 +10224,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124502605</v>
+        <v>124486839</v>
       </c>
       <c r="B93" t="n">
         <v>78810</v>
@@ -10249,14 +10272,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524259</v>
+        <v>524872</v>
       </c>
       <c r="R93" t="n">
-        <v>6845061</v>
+        <v>6845107</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10315,10 +10338,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124503027</v>
+        <v>124493648</v>
       </c>
       <c r="B94" t="n">
-        <v>78546</v>
+        <v>92293</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10327,41 +10350,50 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524345</v>
+        <v>524762</v>
       </c>
       <c r="R94" t="n">
-        <v>6845032</v>
+        <v>6845231</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10405,22 +10437,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124504662</v>
+        <v>124499475</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10429,41 +10461,50 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524244</v>
+        <v>524510</v>
       </c>
       <c r="R95" t="n">
-        <v>6844920</v>
+        <v>6845430</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10507,22 +10548,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124492717</v>
+        <v>124501662</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10531,38 +10572,47 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524757</v>
+        <v>524272</v>
       </c>
       <c r="R96" t="n">
-        <v>6845190</v>
+        <v>6845365</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10609,22 +10659,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124489792</v>
+        <v>124491427</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10633,50 +10683,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525215</v>
+        <v>524946</v>
       </c>
       <c r="R97" t="n">
-        <v>6845178</v>
+        <v>6845286</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10720,19 +10761,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124491765</v>
+        <v>124498529</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10768,14 +10809,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524904</v>
+        <v>524365</v>
       </c>
       <c r="R98" t="n">
-        <v>6845207</v>
+        <v>6845310</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10834,7 +10875,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124487374</v>
+        <v>124499127</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10870,14 +10911,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524974</v>
+        <v>524559</v>
       </c>
       <c r="R99" t="n">
-        <v>6845191</v>
+        <v>6845427</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10936,7 +10977,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124490091</v>
+        <v>124490555</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -10976,13 +11017,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>525149</v>
+        <v>525142</v>
       </c>
       <c r="R100" t="n">
-        <v>6845210</v>
+        <v>6845241</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11012,6 +11053,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11026,22 +11072,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124500865</v>
+        <v>124503276</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11054,21 +11100,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11078,13 +11124,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524350</v>
+        <v>524472</v>
       </c>
       <c r="R101" t="n">
-        <v>6845399</v>
+        <v>6845023</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11128,22 +11174,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124488535</v>
+        <v>124500794</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11152,38 +11198,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>525311</v>
+        <v>524370</v>
       </c>
       <c r="R102" t="n">
-        <v>6845039</v>
+        <v>6845393</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11242,10 +11288,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124501039</v>
+        <v>124488923</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11254,50 +11300,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524281</v>
+        <v>525312</v>
       </c>
       <c r="R103" t="n">
-        <v>6845383</v>
+        <v>6845166</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11353,10 +11390,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124499480</v>
+        <v>124489983</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11365,47 +11402,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524365</v>
+        <v>525195</v>
       </c>
       <c r="R104" t="n">
-        <v>6845400</v>
+        <v>6845198</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11438,11 +11466,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11469,10 +11492,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124504973</v>
+        <v>124498165</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11481,47 +11504,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524210</v>
+        <v>524349</v>
       </c>
       <c r="R105" t="n">
-        <v>6844954</v>
+        <v>6845225</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11580,10 +11594,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124487293</v>
+        <v>124488326</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11592,50 +11606,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524948</v>
+        <v>524734</v>
       </c>
       <c r="R106" t="n">
-        <v>6845179</v>
+        <v>6845219</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11679,22 +11684,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124500112</v>
+        <v>124493108</v>
       </c>
       <c r="B107" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11707,37 +11712,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524447</v>
+        <v>524776</v>
       </c>
       <c r="R107" t="n">
-        <v>6845417</v>
+        <v>6845248</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11767,6 +11772,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11781,22 +11791,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124498070</v>
+        <v>124504769</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11805,38 +11815,47 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524353</v>
+        <v>524231</v>
       </c>
       <c r="R108" t="n">
-        <v>6845201</v>
+        <v>6844957</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11895,10 +11914,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124487317</v>
+        <v>124504089</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11907,38 +11926,47 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524829</v>
+        <v>524238</v>
       </c>
       <c r="R109" t="n">
-        <v>6845141</v>
+        <v>6844930</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11985,19 +12013,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124487689</v>
+        <v>124501831</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -12033,17 +12061,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524780</v>
+        <v>524268</v>
       </c>
       <c r="R110" t="n">
-        <v>6845188</v>
+        <v>6845351</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12087,19 +12115,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124492513</v>
+        <v>124501516</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -12135,14 +12163,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524774</v>
+        <v>524237</v>
       </c>
       <c r="R111" t="n">
-        <v>6845100</v>
+        <v>6845433</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12201,7 +12229,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124490555</v>
+        <v>124504662</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -12237,17 +12265,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>525142</v>
+        <v>524244</v>
       </c>
       <c r="R112" t="n">
-        <v>6845241</v>
+        <v>6844920</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12277,11 +12305,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12296,22 +12319,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124498544</v>
+        <v>124504651</v>
       </c>
       <c r="B113" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12320,41 +12343,50 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524364</v>
+        <v>524234</v>
       </c>
       <c r="R113" t="n">
-        <v>6845312</v>
+        <v>6844921</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12410,10 +12442,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124491246</v>
+        <v>124497941</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12426,37 +12458,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>525065</v>
+        <v>524344</v>
       </c>
       <c r="R114" t="n">
-        <v>6845243</v>
+        <v>6845182</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12512,7 +12544,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124492000</v>
+        <v>124489866</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -12552,13 +12584,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524901</v>
+        <v>525217</v>
       </c>
       <c r="R115" t="n">
-        <v>6845216</v>
+        <v>6845195</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12602,22 +12634,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124492807</v>
+        <v>124498544</v>
       </c>
       <c r="B116" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12630,37 +12662,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524696</v>
+        <v>524364</v>
       </c>
       <c r="R116" t="n">
-        <v>6845140</v>
+        <v>6845312</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12704,19 +12736,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124491531</v>
+        <v>124492194</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -12756,13 +12788,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524919</v>
+        <v>524798</v>
       </c>
       <c r="R117" t="n">
-        <v>6845253</v>
+        <v>6845206</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12818,7 +12850,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124490428</v>
+        <v>124489815</v>
       </c>
       <c r="B118" t="n">
         <v>78810</v>
@@ -12858,10 +12890,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>525133</v>
+        <v>525208</v>
       </c>
       <c r="R118" t="n">
-        <v>6845201</v>
+        <v>6845169</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12920,7 +12952,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124486832</v>
+        <v>124491548</v>
       </c>
       <c r="B119" t="n">
         <v>78810</v>
@@ -12960,10 +12992,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524856</v>
+        <v>524916</v>
       </c>
       <c r="R119" t="n">
-        <v>6845111</v>
+        <v>6845244</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13022,7 +13054,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124504354</v>
+        <v>124491428</v>
       </c>
       <c r="B120" t="n">
         <v>98101</v>
@@ -13057,7 +13089,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13067,17 +13099,17 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524274</v>
+        <v>524954</v>
       </c>
       <c r="R120" t="n">
-        <v>6844889</v>
+        <v>6845241</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13121,22 +13153,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124500926</v>
+        <v>124487567</v>
       </c>
       <c r="B121" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13149,37 +13181,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524345</v>
+        <v>525000</v>
       </c>
       <c r="R121" t="n">
-        <v>6845461</v>
+        <v>6845201</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13223,22 +13255,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124498794</v>
+        <v>124504054</v>
       </c>
       <c r="B122" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13247,38 +13279,47 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524383</v>
+        <v>524683</v>
       </c>
       <c r="R122" t="n">
-        <v>6845264</v>
+        <v>6844956</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13337,7 +13378,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124504545</v>
+        <v>124502783</v>
       </c>
       <c r="B123" t="n">
         <v>98101</v>
@@ -13372,7 +13413,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13386,13 +13427,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524237</v>
+        <v>524254</v>
       </c>
       <c r="R123" t="n">
-        <v>6844919</v>
+        <v>6845067</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13436,19 +13477,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124503388</v>
+        <v>124501577</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -13483,7 +13524,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13497,10 +13538,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524214</v>
+        <v>524252</v>
       </c>
       <c r="R124" t="n">
-        <v>6844996</v>
+        <v>6845387</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13547,22 +13588,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124503680</v>
+        <v>124504945</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13575,21 +13616,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13599,10 +13640,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524648</v>
+        <v>524203</v>
       </c>
       <c r="R125" t="n">
-        <v>6845029</v>
+        <v>6844991</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13661,10 +13702,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124505582</v>
+        <v>124490091</v>
       </c>
       <c r="B126" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13677,37 +13718,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524121</v>
+        <v>525149</v>
       </c>
       <c r="R126" t="n">
-        <v>6845117</v>
+        <v>6845210</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13763,10 +13804,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124503785</v>
+        <v>124498070</v>
       </c>
       <c r="B127" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13779,21 +13820,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13803,10 +13844,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524244</v>
+        <v>524353</v>
       </c>
       <c r="R127" t="n">
-        <v>6845004</v>
+        <v>6845201</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13853,22 +13894,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124502910</v>
+        <v>124487121</v>
       </c>
       <c r="B128" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13877,50 +13918,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524247</v>
+        <v>524844</v>
       </c>
       <c r="R128" t="n">
-        <v>6845069</v>
+        <v>6845169</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13964,22 +13996,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124501719</v>
+        <v>124490165</v>
       </c>
       <c r="B129" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13992,37 +14024,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524232</v>
+        <v>525151</v>
       </c>
       <c r="R129" t="n">
-        <v>6845349</v>
+        <v>6845190</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14066,22 +14098,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124504250</v>
+        <v>124488535</v>
       </c>
       <c r="B130" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14090,41 +14122,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524436</v>
+        <v>525311</v>
       </c>
       <c r="R130" t="n">
-        <v>6844930</v>
+        <v>6845039</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14154,11 +14186,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14173,19 +14200,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124488657</v>
+        <v>124487689</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14225,13 +14252,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>525312</v>
+        <v>524780</v>
       </c>
       <c r="R131" t="n">
-        <v>6845117</v>
+        <v>6845188</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14275,19 +14302,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124491300</v>
+        <v>124487283</v>
       </c>
       <c r="B132" t="n">
         <v>78810</v>
@@ -14327,13 +14354,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>525015</v>
+        <v>524836</v>
       </c>
       <c r="R132" t="n">
-        <v>6845263</v>
+        <v>6845119</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14377,22 +14404,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124499832</v>
+        <v>124502475</v>
       </c>
       <c r="B133" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14401,50 +14428,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524327</v>
+        <v>524197</v>
       </c>
       <c r="R133" t="n">
-        <v>6845386</v>
+        <v>6845056</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14488,19 +14506,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124504054</v>
+        <v>124504973</v>
       </c>
       <c r="B134" t="n">
         <v>98101</v>
@@ -14535,7 +14553,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14549,10 +14567,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524683</v>
+        <v>524210</v>
       </c>
       <c r="R134" t="n">
-        <v>6844956</v>
+        <v>6844954</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -14611,10 +14629,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124502783</v>
+        <v>124491477</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14623,50 +14641,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524254</v>
+        <v>524920</v>
       </c>
       <c r="R135" t="n">
-        <v>6845067</v>
+        <v>6845260</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14710,22 +14719,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124491428</v>
+        <v>124487467</v>
       </c>
       <c r="B136" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14734,47 +14743,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524954</v>
+        <v>524805</v>
       </c>
       <c r="R136" t="n">
-        <v>6845241</v>
+        <v>6845150</v>
       </c>
       <c r="S136" t="n">
         <v>20</v>
@@ -14830,6 +14830,108 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>124486958</v>
+      </c>
+      <c r="B137" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>524876</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6845153</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -3104,7 +3104,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124500865</v>
+        <v>124491765</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3140,17 +3140,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524350</v>
+        <v>524904</v>
       </c>
       <c r="R25" t="n">
-        <v>6845399</v>
+        <v>6845207</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3194,19 +3194,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124502522</v>
+        <v>124491531</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3242,17 +3242,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524234</v>
+        <v>524919</v>
       </c>
       <c r="R26" t="n">
-        <v>6845053</v>
+        <v>6845253</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124491765</v>
+        <v>124498794</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3320,38 +3320,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524904</v>
+        <v>524383</v>
       </c>
       <c r="R27" t="n">
-        <v>6845207</v>
+        <v>6845264</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124491531</v>
+        <v>124486832</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3450,13 +3450,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524919</v>
+        <v>524856</v>
       </c>
       <c r="R28" t="n">
-        <v>6845253</v>
+        <v>6845111</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124498794</v>
+        <v>124487374</v>
       </c>
       <c r="B29" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3524,41 +3524,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524383</v>
+        <v>524974</v>
       </c>
       <c r="R29" t="n">
-        <v>6845264</v>
+        <v>6845191</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3602,19 +3602,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124486832</v>
+        <v>124500865</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3650,17 +3650,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524856</v>
+        <v>524350</v>
       </c>
       <c r="R30" t="n">
-        <v>6845111</v>
+        <v>6845399</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3704,19 +3704,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124487374</v>
+        <v>124502522</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3752,17 +3752,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524974</v>
+        <v>524234</v>
       </c>
       <c r="R31" t="n">
-        <v>6845191</v>
+        <v>6845053</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124500112</v>
+        <v>124490965</v>
       </c>
       <c r="B32" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3834,34 +3834,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524447</v>
+        <v>525081</v>
       </c>
       <c r="R32" t="n">
-        <v>6845417</v>
+        <v>6845283</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3920,10 +3920,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124505582</v>
+        <v>124486895</v>
       </c>
       <c r="B33" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3936,37 +3936,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524121</v>
+        <v>524856</v>
       </c>
       <c r="R33" t="n">
-        <v>6845117</v>
+        <v>6845128</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124490965</v>
+        <v>124490692</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4034,25 +4034,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4062,13 +4062,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525081</v>
+        <v>525103</v>
       </c>
       <c r="R34" t="n">
-        <v>6845283</v>
+        <v>6845194</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4112,22 +4112,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124486895</v>
+        <v>124500112</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4140,37 +4140,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524856</v>
+        <v>524447</v>
       </c>
       <c r="R35" t="n">
-        <v>6845128</v>
+        <v>6845417</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4214,22 +4214,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124490692</v>
+        <v>124505582</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>91032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4238,41 +4238,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525103</v>
+        <v>524121</v>
       </c>
       <c r="R36" t="n">
-        <v>6845194</v>
+        <v>6845117</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124500867</v>
+        <v>124487564</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4364,17 +4364,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524343</v>
+        <v>524773</v>
       </c>
       <c r="R37" t="n">
-        <v>6845433</v>
+        <v>6845141</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124487564</v>
+        <v>124491917</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524773</v>
+        <v>524852</v>
       </c>
       <c r="R38" t="n">
-        <v>6845141</v>
+        <v>6845214</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124491917</v>
+        <v>124491619</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524852</v>
+        <v>524906</v>
       </c>
       <c r="R39" t="n">
-        <v>6845214</v>
+        <v>6845220</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124491619</v>
+        <v>124503785</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4650,34 +4650,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524906</v>
+        <v>524244</v>
       </c>
       <c r="R40" t="n">
-        <v>6845220</v>
+        <v>6845004</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4724,22 +4724,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124503785</v>
+        <v>124500867</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524244</v>
+        <v>524343</v>
       </c>
       <c r="R41" t="n">
-        <v>6845004</v>
+        <v>6845433</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4826,12 +4826,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -8438,10 +8438,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124503002</v>
+        <v>124504565</v>
       </c>
       <c r="B76" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8450,38 +8450,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524333</v>
+        <v>524227</v>
       </c>
       <c r="R76" t="n">
-        <v>6845022</v>
+        <v>6844932</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8540,7 +8549,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124504565</v>
+        <v>124504704</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8575,7 +8584,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8589,10 +8598,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524227</v>
+        <v>524238</v>
       </c>
       <c r="R77" t="n">
-        <v>6844932</v>
+        <v>6844943</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8651,7 +8660,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124504704</v>
+        <v>124499895</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8686,7 +8695,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8700,10 +8709,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524238</v>
+        <v>524362</v>
       </c>
       <c r="R78" t="n">
-        <v>6844943</v>
+        <v>6845391</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8736,6 +8745,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8762,10 +8776,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124499895</v>
+        <v>124503002</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8774,47 +8788,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524362</v>
+        <v>524333</v>
       </c>
       <c r="R79" t="n">
-        <v>6845391</v>
+        <v>6845022</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8847,11 +8852,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8878,10 +8878,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124488657</v>
+        <v>124504354</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8890,38 +8890,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525312</v>
+        <v>524274</v>
       </c>
       <c r="R80" t="n">
-        <v>6845117</v>
+        <v>6844889</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8980,10 +8989,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124489002</v>
+        <v>124504916</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8992,41 +9001,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525277</v>
+        <v>524219</v>
       </c>
       <c r="R81" t="n">
-        <v>6845196</v>
+        <v>6844970</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9056,11 +9074,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9075,19 +9088,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124499873</v>
+        <v>124488657</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9123,14 +9136,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524451</v>
+        <v>525312</v>
       </c>
       <c r="R82" t="n">
-        <v>6845435</v>
+        <v>6845117</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9189,10 +9202,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124492072</v>
+        <v>124489002</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9201,50 +9214,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524828</v>
+        <v>525277</v>
       </c>
       <c r="R83" t="n">
-        <v>6845147</v>
+        <v>6845196</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9274,6 +9278,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9288,22 +9297,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124503027</v>
+        <v>124499873</v>
       </c>
       <c r="B84" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9316,21 +9325,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9340,13 +9349,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524345</v>
+        <v>524451</v>
       </c>
       <c r="R84" t="n">
-        <v>6845032</v>
+        <v>6845435</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9390,22 +9399,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124500965</v>
+        <v>124503027</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9418,21 +9427,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9442,10 +9451,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524308</v>
+        <v>524345</v>
       </c>
       <c r="R85" t="n">
-        <v>6845471</v>
+        <v>6845032</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9504,10 +9513,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124501563</v>
+        <v>124500965</v>
       </c>
       <c r="B86" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9520,21 +9529,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9544,13 +9553,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524245</v>
+        <v>524308</v>
       </c>
       <c r="R86" t="n">
-        <v>6845371</v>
+        <v>6845471</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9594,22 +9603,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124504354</v>
+        <v>124501563</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9618,47 +9627,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524274</v>
+        <v>524245</v>
       </c>
       <c r="R87" t="n">
-        <v>6844889</v>
+        <v>6845371</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124504916</v>
+        <v>124492072</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9762,14 +9762,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524219</v>
+        <v>524828</v>
       </c>
       <c r="R88" t="n">
-        <v>6844970</v>
+        <v>6845147</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -12442,10 +12442,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124497941</v>
+        <v>124489866</v>
       </c>
       <c r="B114" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12458,37 +12458,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524344</v>
+        <v>525217</v>
       </c>
       <c r="R114" t="n">
-        <v>6845182</v>
+        <v>6845195</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12532,22 +12532,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124489866</v>
+        <v>124498544</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12560,37 +12560,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>525217</v>
+        <v>524364</v>
       </c>
       <c r="R115" t="n">
-        <v>6845195</v>
+        <v>6845312</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12634,22 +12634,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124498544</v>
+        <v>124492194</v>
       </c>
       <c r="B116" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12662,34 +12662,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524364</v>
+        <v>524798</v>
       </c>
       <c r="R116" t="n">
-        <v>6845312</v>
+        <v>6845206</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12748,7 +12748,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124492194</v>
+        <v>124489815</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -12788,10 +12788,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524798</v>
+        <v>525208</v>
       </c>
       <c r="R117" t="n">
-        <v>6845206</v>
+        <v>6845169</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124489815</v>
+        <v>124491548</v>
       </c>
       <c r="B118" t="n">
         <v>78810</v>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>525208</v>
+        <v>524916</v>
       </c>
       <c r="R118" t="n">
-        <v>6845169</v>
+        <v>6845244</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12952,10 +12952,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124491548</v>
+        <v>124497941</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12968,37 +12968,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524916</v>
+        <v>524344</v>
       </c>
       <c r="R119" t="n">
-        <v>6845244</v>
+        <v>6845182</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13489,10 +13489,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124501577</v>
+        <v>124490091</v>
       </c>
       <c r="B124" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13501,47 +13501,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524252</v>
+        <v>525149</v>
       </c>
       <c r="R124" t="n">
-        <v>6845387</v>
+        <v>6845210</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13600,10 +13591,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124504945</v>
+        <v>124498070</v>
       </c>
       <c r="B125" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13616,21 +13607,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13640,10 +13631,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524203</v>
+        <v>524353</v>
       </c>
       <c r="R125" t="n">
-        <v>6844991</v>
+        <v>6845201</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13702,7 +13693,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124490091</v>
+        <v>124487121</v>
       </c>
       <c r="B126" t="n">
         <v>78810</v>
@@ -13742,10 +13733,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>525149</v>
+        <v>524844</v>
       </c>
       <c r="R126" t="n">
-        <v>6845210</v>
+        <v>6845169</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13804,7 +13795,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124498070</v>
+        <v>124490165</v>
       </c>
       <c r="B127" t="n">
         <v>78810</v>
@@ -13840,14 +13831,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524353</v>
+        <v>525151</v>
       </c>
       <c r="R127" t="n">
-        <v>6845201</v>
+        <v>6845190</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13906,7 +13897,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124487121</v>
+        <v>124488535</v>
       </c>
       <c r="B128" t="n">
         <v>78810</v>
@@ -13946,13 +13937,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524844</v>
+        <v>525311</v>
       </c>
       <c r="R128" t="n">
-        <v>6845169</v>
+        <v>6845039</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13996,19 +13987,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124490165</v>
+        <v>124487689</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14048,10 +14039,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>525151</v>
+        <v>524780</v>
       </c>
       <c r="R129" t="n">
-        <v>6845190</v>
+        <v>6845188</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14110,7 +14101,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124488535</v>
+        <v>124487283</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14150,13 +14141,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>525311</v>
+        <v>524836</v>
       </c>
       <c r="R130" t="n">
-        <v>6845039</v>
+        <v>6845119</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14200,22 +14191,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124487689</v>
+        <v>124504945</v>
       </c>
       <c r="B131" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14228,34 +14219,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524780</v>
+        <v>524203</v>
       </c>
       <c r="R131" t="n">
-        <v>6845188</v>
+        <v>6844991</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14314,10 +14305,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124487283</v>
+        <v>124501577</v>
       </c>
       <c r="B132" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14326,38 +14317,47 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524836</v>
+        <v>524252</v>
       </c>
       <c r="R132" t="n">
-        <v>6845119</v>
+        <v>6845387</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>

--- a/artfynd/A 8590-2025 artfynd.xlsx
+++ b/artfynd/A 8590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124487604</v>
+        <v>124489748</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524781</v>
+        <v>525230</v>
       </c>
       <c r="R2" t="n">
-        <v>6845167</v>
+        <v>6845187</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124488103</v>
+        <v>124492072</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +798,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525146</v>
+        <v>524828</v>
       </c>
       <c r="R3" t="n">
-        <v>6845150</v>
+        <v>6845147</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124487317</v>
+        <v>124490428</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524829</v>
+        <v>525133</v>
       </c>
       <c r="R4" t="n">
-        <v>6845141</v>
+        <v>6845201</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124499838</v>
+        <v>124498760</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +1011,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524478</v>
+        <v>524388</v>
       </c>
       <c r="R5" t="n">
-        <v>6845426</v>
+        <v>6845283</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124505389</v>
+        <v>124499873</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,50 +1113,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524115</v>
+        <v>524451</v>
       </c>
       <c r="R6" t="n">
-        <v>6845050</v>
+        <v>6845435</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124504513</v>
+        <v>124501563</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,37 +1215,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
@@ -1255,10 +1246,10 @@
         <v>524245</v>
       </c>
       <c r="R7" t="n">
-        <v>6844924</v>
+        <v>6845371</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,22 +1293,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124498936</v>
+        <v>124489866</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,37 +1321,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524415</v>
+        <v>525217</v>
       </c>
       <c r="R8" t="n">
-        <v>6845335</v>
+        <v>6845195</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124490527</v>
+        <v>124498165</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,42 +1423,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525139</v>
+        <v>524349</v>
       </c>
       <c r="R9" t="n">
-        <v>6845241</v>
+        <v>6845225</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,11 +1483,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,22 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124489670</v>
+        <v>124501719</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,47 +1521,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525247</v>
+        <v>524232</v>
       </c>
       <c r="R10" t="n">
-        <v>6845194</v>
+        <v>6845349</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1639,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124487293</v>
+        <v>124504769</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1674,7 +1646,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1684,17 +1656,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524948</v>
+        <v>524231</v>
       </c>
       <c r="R11" t="n">
-        <v>6845179</v>
+        <v>6844957</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,22 +1710,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124499713</v>
+        <v>124500201</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,38 +1734,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524311</v>
+        <v>524390</v>
       </c>
       <c r="R12" t="n">
-        <v>6845368</v>
+        <v>6845406</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1826,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124492717</v>
+        <v>124487293</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,41 +1850,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524757</v>
+        <v>524948</v>
       </c>
       <c r="R13" t="n">
-        <v>6845190</v>
+        <v>6845179</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,19 +1937,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124491805</v>
+        <v>124491917</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524880</v>
+        <v>524852</v>
       </c>
       <c r="R14" t="n">
-        <v>6845212</v>
+        <v>6845214</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2056,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124491294</v>
+        <v>124489815</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525063</v>
+        <v>525208</v>
       </c>
       <c r="R15" t="n">
-        <v>6845234</v>
+        <v>6845169</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2158,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124491300</v>
+        <v>124499127</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2194,17 +2189,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525015</v>
+        <v>524559</v>
       </c>
       <c r="R16" t="n">
-        <v>6845263</v>
+        <v>6845427</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2260,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124498466</v>
+        <v>124487283</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2296,14 +2291,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524369</v>
+        <v>524836</v>
       </c>
       <c r="R17" t="n">
-        <v>6845293</v>
+        <v>6845119</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2362,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124504860</v>
+        <v>124503388</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,38 +2369,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524224</v>
+        <v>524214</v>
       </c>
       <c r="R18" t="n">
-        <v>6844971</v>
+        <v>6844996</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2452,22 +2456,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124502991</v>
+        <v>124505389</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,38 +2480,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524280</v>
+        <v>524115</v>
       </c>
       <c r="R19" t="n">
-        <v>6845054</v>
+        <v>6845050</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2554,22 +2567,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124502605</v>
+        <v>124504916</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,41 +2591,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524259</v>
+        <v>524219</v>
       </c>
       <c r="R20" t="n">
-        <v>6845061</v>
+        <v>6844970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2656,22 +2678,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124503227</v>
+        <v>124504662</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2706,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524472</v>
+        <v>524244</v>
       </c>
       <c r="R21" t="n">
-        <v>6845023</v>
+        <v>6844920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124504250</v>
+        <v>124503504</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,25 +2804,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2810,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524436</v>
+        <v>524511</v>
       </c>
       <c r="R22" t="n">
-        <v>6844930</v>
+        <v>6845029</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2846,11 +2868,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2877,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124499480</v>
+        <v>124502605</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,50 +2906,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524365</v>
+        <v>524259</v>
       </c>
       <c r="R23" t="n">
-        <v>6845400</v>
+        <v>6845061</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2962,11 +2970,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2981,22 +2984,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124486962</v>
+        <v>124500867</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,50 +3008,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524859</v>
+        <v>524343</v>
       </c>
       <c r="R24" t="n">
-        <v>6845148</v>
+        <v>6845433</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3104,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124491765</v>
+        <v>124499480</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3116,38 +3110,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524904</v>
+        <v>524365</v>
       </c>
       <c r="R25" t="n">
-        <v>6845207</v>
+        <v>6845400</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3180,6 +3183,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590-2025.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3206,10 +3214,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124491531</v>
+        <v>124504151</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3218,41 +3226,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524919</v>
+        <v>524256</v>
       </c>
       <c r="R26" t="n">
-        <v>6845253</v>
+        <v>6844925</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3296,22 +3304,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124498794</v>
+        <v>124487039</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3320,41 +3328,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524383</v>
+        <v>524908</v>
       </c>
       <c r="R27" t="n">
-        <v>6845264</v>
+        <v>6845155</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3398,19 +3415,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124486832</v>
+        <v>124490091</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3450,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524856</v>
+        <v>525149</v>
       </c>
       <c r="R28" t="n">
-        <v>6845111</v>
+        <v>6845210</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3512,7 +3529,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124487374</v>
+        <v>124488923</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3552,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524974</v>
+        <v>525312</v>
       </c>
       <c r="R29" t="n">
-        <v>6845191</v>
+        <v>6845166</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124500865</v>
+        <v>124491294</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3650,17 +3667,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524350</v>
+        <v>525063</v>
       </c>
       <c r="R30" t="n">
-        <v>6845399</v>
+        <v>6845234</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3704,19 +3721,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124502522</v>
+        <v>124491548</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3752,14 +3769,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524234</v>
+        <v>524916</v>
       </c>
       <c r="R31" t="n">
-        <v>6845053</v>
+        <v>6845244</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3818,7 +3835,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124490965</v>
+        <v>124487317</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3858,13 +3875,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525081</v>
+        <v>524829</v>
       </c>
       <c r="R32" t="n">
-        <v>6845283</v>
+        <v>6845141</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3908,19 +3925,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124486895</v>
+        <v>124500965</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3956,14 +3973,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524856</v>
+        <v>524308</v>
       </c>
       <c r="R33" t="n">
-        <v>6845128</v>
+        <v>6845471</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4022,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124490692</v>
+        <v>124503276</v>
       </c>
       <c r="B34" t="n">
-        <v>90977</v>
+        <v>78546</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4034,41 +4051,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525103</v>
+        <v>524472</v>
       </c>
       <c r="R34" t="n">
-        <v>6845194</v>
+        <v>6845023</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4124,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124500112</v>
+        <v>124503227</v>
       </c>
       <c r="B35" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4140,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4164,13 +4181,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524447</v>
+        <v>524472</v>
       </c>
       <c r="R35" t="n">
-        <v>6845417</v>
+        <v>6845023</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4214,22 +4231,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124505582</v>
+        <v>124500112</v>
       </c>
       <c r="B36" t="n">
-        <v>91032</v>
+        <v>79892</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4242,21 +4259,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4266,13 +4283,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524121</v>
+        <v>524447</v>
       </c>
       <c r="R36" t="n">
-        <v>6845117</v>
+        <v>6845417</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4316,19 +4333,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124487564</v>
+        <v>124487775</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4368,13 +4385,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524773</v>
+        <v>525079</v>
       </c>
       <c r="R37" t="n">
-        <v>6845141</v>
+        <v>6845164</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4418,19 +4435,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124491917</v>
+        <v>124491619</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4470,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524852</v>
+        <v>524906</v>
       </c>
       <c r="R38" t="n">
-        <v>6845214</v>
+        <v>6845220</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4532,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124491619</v>
+        <v>124493358</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,21 +4565,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4572,10 +4589,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524906</v>
+        <v>524793</v>
       </c>
       <c r="R39" t="n">
-        <v>6845220</v>
+        <v>6845243</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4634,10 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124503785</v>
+        <v>124503002</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>78546</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4650,21 +4667,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4674,10 +4691,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524244</v>
+        <v>524333</v>
       </c>
       <c r="R40" t="n">
-        <v>6845004</v>
+        <v>6845022</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4724,22 +4741,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124500867</v>
+        <v>124504250</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4748,25 +4765,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4776,13 +4793,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524343</v>
+        <v>524436</v>
       </c>
       <c r="R41" t="n">
-        <v>6845433</v>
+        <v>6844930</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4812,6 +4829,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spillning under tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4838,10 +4860,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124502910</v>
+        <v>124491805</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4850,50 +4872,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524247</v>
+        <v>524880</v>
       </c>
       <c r="R42" t="n">
-        <v>6845069</v>
+        <v>6845212</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4937,22 +4950,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124506146</v>
+        <v>124498794</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4961,47 +4974,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524148</v>
+        <v>524383</v>
       </c>
       <c r="R43" t="n">
-        <v>6845027</v>
+        <v>6845264</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5060,10 +5064,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124489748</v>
+        <v>124488535</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5072,50 +5076,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525230</v>
+        <v>525311</v>
       </c>
       <c r="R44" t="n">
-        <v>6845187</v>
+        <v>6845039</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5159,22 +5154,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124499832</v>
+        <v>124504945</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5183,47 +5178,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524327</v>
+        <v>524203</v>
       </c>
       <c r="R45" t="n">
-        <v>6845386</v>
+        <v>6844991</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5282,7 +5268,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124492032</v>
+        <v>124504565</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5317,7 +5303,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5327,17 +5313,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524881</v>
+        <v>524227</v>
       </c>
       <c r="R46" t="n">
-        <v>6845143</v>
+        <v>6844932</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5381,22 +5367,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124490428</v>
+        <v>124497941</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5409,37 +5395,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525133</v>
+        <v>524344</v>
       </c>
       <c r="R47" t="n">
-        <v>6845201</v>
+        <v>6845182</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5495,7 +5481,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124490978</v>
+        <v>124501831</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5531,17 +5517,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525086</v>
+        <v>524268</v>
       </c>
       <c r="R48" t="n">
-        <v>6845224</v>
+        <v>6845351</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5585,19 +5571,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124498760</v>
+        <v>124502475</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5637,13 +5623,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524388</v>
+        <v>524197</v>
       </c>
       <c r="R49" t="n">
-        <v>6845283</v>
+        <v>6845056</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5687,22 +5673,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124503388</v>
+        <v>124491246</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5711,47 +5697,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524214</v>
+        <v>525065</v>
       </c>
       <c r="R50" t="n">
-        <v>6844996</v>
+        <v>6845243</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5798,19 +5775,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124492513</v>
+        <v>124491427</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5850,10 +5827,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524774</v>
+        <v>524946</v>
       </c>
       <c r="R51" t="n">
-        <v>6845100</v>
+        <v>6845286</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5912,10 +5889,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124492635</v>
+        <v>124490978</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5928,21 +5905,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5952,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524790</v>
+        <v>525086</v>
       </c>
       <c r="R52" t="n">
-        <v>6845219</v>
+        <v>6845224</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5988,11 +5965,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6019,10 +5991,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124493358</v>
+        <v>124492000</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6035,21 +6007,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6059,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524793</v>
+        <v>524901</v>
       </c>
       <c r="R53" t="n">
-        <v>6845243</v>
+        <v>6845216</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6121,10 +6093,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124487771</v>
+        <v>124499895</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6133,38 +6105,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524761</v>
+        <v>524362</v>
       </c>
       <c r="R54" t="n">
-        <v>6845213</v>
+        <v>6845391</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6197,6 +6178,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6223,10 +6209,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124490720</v>
+        <v>124493108</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6239,21 +6225,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6263,13 +6249,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525133</v>
+        <v>524776</v>
       </c>
       <c r="R55" t="n">
-        <v>6845307</v>
+        <v>6845248</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6299,6 +6285,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på död tall. En tredjedel av tallen barklös.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6313,22 +6304,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124501719</v>
+        <v>124487564</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6341,37 +6332,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524232</v>
+        <v>524773</v>
       </c>
       <c r="R56" t="n">
-        <v>6845349</v>
+        <v>6845141</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6415,19 +6406,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124504321</v>
+        <v>124490097</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6463,14 +6454,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524276</v>
+        <v>525147</v>
       </c>
       <c r="R57" t="n">
-        <v>6844888</v>
+        <v>6845208</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6529,7 +6520,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124504545</v>
+        <v>124504651</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6578,13 +6569,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524237</v>
+        <v>524234</v>
       </c>
       <c r="R58" t="n">
-        <v>6844919</v>
+        <v>6844921</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6640,7 +6631,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124501039</v>
+        <v>124504973</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6675,7 +6666,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6689,13 +6680,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524281</v>
+        <v>524210</v>
       </c>
       <c r="R59" t="n">
-        <v>6845383</v>
+        <v>6844954</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6739,19 +6730,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124500201</v>
+        <v>124504485</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6786,7 +6777,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6800,10 +6791,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524390</v>
+        <v>524261</v>
       </c>
       <c r="R60" t="n">
-        <v>6845406</v>
+        <v>6844909</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6836,11 +6827,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Fyra meters hänsyn har tagits.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6867,7 +6853,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124504485</v>
+        <v>124500069</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6902,7 +6888,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6916,10 +6902,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524261</v>
+        <v>524370</v>
       </c>
       <c r="R61" t="n">
-        <v>6844909</v>
+        <v>6845396</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6952,6 +6938,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6978,7 +6969,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124500909</v>
+        <v>124487604</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7014,17 +7005,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524346</v>
+        <v>524781</v>
       </c>
       <c r="R62" t="n">
-        <v>6845458</v>
+        <v>6845167</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7080,10 +7071,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124503504</v>
+        <v>124486839</v>
       </c>
       <c r="B63" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7096,37 +7087,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524511</v>
+        <v>524872</v>
       </c>
       <c r="R63" t="n">
-        <v>6845029</v>
+        <v>6845107</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7170,22 +7161,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124504151</v>
+        <v>124491531</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7194,41 +7185,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524256</v>
+        <v>524919</v>
       </c>
       <c r="R64" t="n">
-        <v>6844925</v>
+        <v>6845253</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7272,19 +7263,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124491246</v>
+        <v>124492194</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7324,10 +7315,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525065</v>
+        <v>524798</v>
       </c>
       <c r="R65" t="n">
-        <v>6845243</v>
+        <v>6845206</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7386,7 +7377,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124491822</v>
+        <v>124489983</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7426,10 +7417,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524857</v>
+        <v>525195</v>
       </c>
       <c r="R66" t="n">
-        <v>6845201</v>
+        <v>6845198</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7476,22 +7467,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124489792</v>
+        <v>124491300</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7500,50 +7491,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525215</v>
+        <v>525015</v>
       </c>
       <c r="R67" t="n">
-        <v>6845178</v>
+        <v>6845263</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7587,19 +7569,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124491387</v>
+        <v>124500909</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7635,17 +7617,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524949</v>
+        <v>524346</v>
       </c>
       <c r="R68" t="n">
-        <v>6845252</v>
+        <v>6845458</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7701,10 +7683,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124487775</v>
+        <v>124501039</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7713,38 +7695,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525079</v>
+        <v>524281</v>
       </c>
       <c r="R69" t="n">
-        <v>6845164</v>
+        <v>6845383</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7803,10 +7794,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124490097</v>
+        <v>124504354</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7815,38 +7806,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525147</v>
+        <v>524274</v>
       </c>
       <c r="R70" t="n">
-        <v>6845208</v>
+        <v>6844889</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124492000</v>
+        <v>124503027</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7921,34 +7921,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524901</v>
+        <v>524345</v>
       </c>
       <c r="R71" t="n">
-        <v>6845216</v>
+        <v>6845032</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8007,10 +8007,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124500926</v>
+        <v>124491477</v>
       </c>
       <c r="B72" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8023,37 +8023,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524345</v>
+        <v>524920</v>
       </c>
       <c r="R72" t="n">
-        <v>6845461</v>
+        <v>6845260</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124500069</v>
+        <v>124503785</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8121,47 +8121,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524370</v>
+        <v>524244</v>
       </c>
       <c r="R73" t="n">
-        <v>6845396</v>
+        <v>6845004</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8196,11 +8187,6 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Mitt i avverkning. Fler plantor under fällda tallstockar.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8213,22 +8199,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124491320</v>
+        <v>124500926</v>
       </c>
       <c r="B74" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8237,41 +8223,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525017</v>
+        <v>524345</v>
       </c>
       <c r="R74" t="n">
-        <v>6845257</v>
+        <v>6845461</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8315,22 +8301,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124487039</v>
+        <v>124503680</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8339,50 +8325,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524908</v>
+        <v>524648</v>
       </c>
       <c r="R75" t="n">
-        <v>6845155</v>
+        <v>6845029</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8426,22 +8403,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124504565</v>
+        <v>124492513</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8450,50 +8427,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524227</v>
+        <v>524774</v>
       </c>
       <c r="R76" t="n">
-        <v>6844932</v>
+        <v>6845100</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8537,22 +8505,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124504704</v>
+        <v>124498070</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8561,47 +8529,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524238</v>
+        <v>524353</v>
       </c>
       <c r="R77" t="n">
-        <v>6844943</v>
+        <v>6845201</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8660,10 +8619,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124499895</v>
+        <v>124490165</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8672,47 +8631,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524362</v>
+        <v>525151</v>
       </c>
       <c r="R78" t="n">
-        <v>6845391</v>
+        <v>6845190</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8745,11 +8695,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan A 8590.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8776,10 +8721,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124503002</v>
+        <v>124487689</v>
       </c>
       <c r="B79" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8792,34 +8737,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524333</v>
+        <v>524780</v>
       </c>
       <c r="R79" t="n">
-        <v>6845022</v>
+        <v>6845188</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8878,10 +8823,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124504354</v>
+        <v>124498466</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8890,50 +8835,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524274</v>
+        <v>524369</v>
       </c>
       <c r="R80" t="n">
-        <v>6844889</v>
+        <v>6845293</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8977,19 +8913,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124504916</v>
+        <v>124499838</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -9024,7 +8960,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9038,13 +8974,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524219</v>
+        <v>524478</v>
       </c>
       <c r="R81" t="n">
-        <v>6844970</v>
+        <v>6845426</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9088,19 +9024,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124488657</v>
+        <v>124504321</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9136,14 +9072,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Karis brännan, Stor-Karis brännan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525312</v>
+        <v>524276</v>
       </c>
       <c r="R82" t="n">
-        <v>6845117</v>
+        <v>6844888</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9202,7 +9138,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124489002</v>
+        <v>124491822</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9242,13 +9178,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525277</v>
+        <v>524857</v>
       </c>
       <c r="R83" t="n">
-        <v>6845196</v>
+        <v>6845201</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9278,11 +9214,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9309,7 +9240,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124499873</v>
+        <v>124498529</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9349,13 +9280,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524451</v>
+        <v>524365</v>
       </c>
       <c r="R84" t="n">
-        <v>6845435</v>
+        <v>6845310</v>
       </c>
       <c r="S84" t="n">
